--- a/examples/interwar_poland/market_access/outputs/checks/unit_weighted_domestic_access_1924_1938.xlsx
+++ b/examples/interwar_poland/market_access/outputs/checks/unit_weighted_domestic_access_1924_1938.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D989"/>
+  <dimension ref="A1:E989"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +449,11 @@
           <t>unit_weighted_domestic_access</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>avg_inverse_distance</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,9 @@
       <c r="D2" t="n">
         <v>0.0002096947565989865</v>
       </c>
+      <c r="E2" t="n">
+        <v>0.003529727028549723</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -485,6 +493,9 @@
       <c r="D3" t="n">
         <v>0.0003174611319868462</v>
       </c>
+      <c r="E3" t="n">
+        <v>0.003977064595392107</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -503,6 +514,9 @@
       <c r="D4" t="n">
         <v>0.001110951939681252</v>
       </c>
+      <c r="E4" t="n">
+        <v>0.00543499873645822</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -521,6 +535,9 @@
       <c r="D5" t="n">
         <v>0.0003735859434325331</v>
       </c>
+      <c r="E5" t="n">
+        <v>0.005208684538144874</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -539,6 +556,9 @@
       <c r="D6" t="n">
         <v>0.0004363175499406497</v>
       </c>
+      <c r="E6" t="n">
+        <v>0.004845301923607056</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -557,6 +577,9 @@
       <c r="D7" t="n">
         <v>0.0002750287529006221</v>
       </c>
+      <c r="E7" t="n">
+        <v>0.004735839539037447</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -575,6 +598,9 @@
       <c r="D8" t="n">
         <v>0.0009190623749554181</v>
       </c>
+      <c r="E8" t="n">
+        <v>0.005228211697860671</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -593,6 +619,9 @@
       <c r="D9" t="n">
         <v>0.0003112002484343299</v>
       </c>
+      <c r="E9" t="n">
+        <v>0.004925441698897414</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -611,6 +640,9 @@
       <c r="D10" t="n">
         <v>0.0009422422482749458</v>
       </c>
+      <c r="E10" t="n">
+        <v>0.005700602187542488</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -629,6 +661,9 @@
       <c r="D11" t="n">
         <v>0.000182499412146071</v>
       </c>
+      <c r="E11" t="n">
+        <v>0.003469464017681089</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -647,6 +682,9 @@
       <c r="D12" t="n">
         <v>3.856426112375519e-05</v>
       </c>
+      <c r="E12" t="n">
+        <v>0.002366038878105913</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -665,6 +703,9 @@
       <c r="D13" t="n">
         <v>0.0005534271106360958</v>
       </c>
+      <c r="E13" t="n">
+        <v>0.00515469845913397</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -683,6 +724,9 @@
       <c r="D14" t="n">
         <v>0.0002950086976407838</v>
       </c>
+      <c r="E14" t="n">
+        <v>0.004806004653955109</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -701,6 +745,9 @@
       <c r="D15" t="n">
         <v>0.001203228030129315</v>
       </c>
+      <c r="E15" t="n">
+        <v>0.005647497574377197</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -719,6 +766,9 @@
       <c r="D16" t="n">
         <v>0.0004070157605657917</v>
       </c>
+      <c r="E16" t="n">
+        <v>0.005263393168302922</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -737,6 +787,9 @@
       <c r="D17" t="n">
         <v>0.0009700795754959774</v>
       </c>
+      <c r="E17" t="n">
+        <v>0.006187150218696666</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -755,6 +808,9 @@
       <c r="D18" t="n">
         <v>0.001067770483060809</v>
       </c>
+      <c r="E18" t="n">
+        <v>0.005046983454967185</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -773,6 +829,9 @@
       <c r="D19" t="n">
         <v>0.0004138430597051253</v>
       </c>
+      <c r="E19" t="n">
+        <v>0.005062448047442335</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -791,6 +850,9 @@
       <c r="D20" t="n">
         <v>0.0007148069382880479</v>
       </c>
+      <c r="E20" t="n">
+        <v>0.004465605874459311</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -809,6 +871,9 @@
       <c r="D21" t="n">
         <v>0.0008198982572725052</v>
       </c>
+      <c r="E21" t="n">
+        <v>0.005311546050857084</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -827,6 +892,9 @@
       <c r="D22" t="n">
         <v>0.0007768503235618358</v>
       </c>
+      <c r="E22" t="n">
+        <v>0.005307010211890463</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -845,6 +913,9 @@
       <c r="D23" t="n">
         <v>0.0004045743775981452</v>
       </c>
+      <c r="E23" t="n">
+        <v>0.005653476397055861</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -863,6 +934,9 @@
       <c r="D24" t="n">
         <v>0.0004990317968070631</v>
       </c>
+      <c r="E24" t="n">
+        <v>0.005369340637250635</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -881,6 +955,9 @@
       <c r="D25" t="n">
         <v>0.0005396906435100251</v>
       </c>
+      <c r="E25" t="n">
+        <v>0.00492373003927194</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -899,6 +976,9 @@
       <c r="D26" t="n">
         <v>0.0004938568245189313</v>
       </c>
+      <c r="E26" t="n">
+        <v>0.005559717396265502</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -917,6 +997,9 @@
       <c r="D27" t="n">
         <v>0.0005932561337451001</v>
       </c>
+      <c r="E27" t="n">
+        <v>0.004697123141272627</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -935,6 +1018,9 @@
       <c r="D28" t="n">
         <v>0.0005464007277509142</v>
       </c>
+      <c r="E28" t="n">
+        <v>0.004415199218430886</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -953,6 +1039,9 @@
       <c r="D29" t="n">
         <v>0.008670563714179657</v>
       </c>
+      <c r="E29" t="n">
+        <v>0.007281471987719291</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -971,6 +1060,9 @@
       <c r="D30" t="n">
         <v>0.0009674781569323833</v>
       </c>
+      <c r="E30" t="n">
+        <v>0.005987368122010789</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -989,6 +1081,9 @@
       <c r="D31" t="n">
         <v>0.0004430048057627781</v>
       </c>
+      <c r="E31" t="n">
+        <v>0.005239931681158785</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1007,6 +1102,9 @@
       <c r="D32" t="n">
         <v>0.0004919068987662834</v>
       </c>
+      <c r="E32" t="n">
+        <v>0.004686089665955752</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1025,6 +1123,9 @@
       <c r="D33" t="n">
         <v>0.0003769907258555173</v>
       </c>
+      <c r="E33" t="n">
+        <v>0.004253576863289791</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1043,6 +1144,9 @@
       <c r="D34" t="n">
         <v>0.001187209318278715</v>
       </c>
+      <c r="E34" t="n">
+        <v>0.004553548190668175</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1061,6 +1165,9 @@
       <c r="D35" t="n">
         <v>0.0003098017708006323</v>
       </c>
+      <c r="E35" t="n">
+        <v>0.0051728762363953</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1079,6 +1186,9 @@
       <c r="D36" t="n">
         <v>0.0005307114083317808</v>
       </c>
+      <c r="E36" t="n">
+        <v>0.005336278021127436</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1097,6 +1207,9 @@
       <c r="D37" t="n">
         <v>0.0004965526219683272</v>
       </c>
+      <c r="E37" t="n">
+        <v>0.004842631172563612</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1115,6 +1228,9 @@
       <c r="D38" t="n">
         <v>0.0001919056507294093</v>
       </c>
+      <c r="E38" t="n">
+        <v>0.004009015308672882</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1133,6 +1249,9 @@
       <c r="D39" t="n">
         <v>0.0008190889982935311</v>
       </c>
+      <c r="E39" t="n">
+        <v>0.005452548113302701</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1151,6 +1270,9 @@
       <c r="D40" t="n">
         <v>0.0002160183534536201</v>
       </c>
+      <c r="E40" t="n">
+        <v>0.004314420264758406</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1169,6 +1291,9 @@
       <c r="D41" t="n">
         <v>0.000265226037370187</v>
       </c>
+      <c r="E41" t="n">
+        <v>0.004864375109071319</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1187,6 +1312,9 @@
       <c r="D42" t="n">
         <v>0.0001035627550589079</v>
       </c>
+      <c r="E42" t="n">
+        <v>0.002535490177408771</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1205,6 +1333,9 @@
       <c r="D43" t="n">
         <v>0.001004031498375481</v>
       </c>
+      <c r="E43" t="n">
+        <v>0.005622217497283565</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1223,6 +1354,9 @@
       <c r="D44" t="n">
         <v>0.000438557975803792</v>
       </c>
+      <c r="E44" t="n">
+        <v>0.005643041871986667</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1241,6 +1375,9 @@
       <c r="D45" t="n">
         <v>0.001222884269838282</v>
       </c>
+      <c r="E45" t="n">
+        <v>0.005898294432716725</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1259,6 +1396,9 @@
       <c r="D46" t="n">
         <v>0.0007686043014516628</v>
       </c>
+      <c r="E46" t="n">
+        <v>0.005422498675527013</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1277,6 +1417,9 @@
       <c r="D47" t="n">
         <v>0.0006717302689646738</v>
       </c>
+      <c r="E47" t="n">
+        <v>0.005334060285385279</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1295,6 +1438,9 @@
       <c r="D48" t="n">
         <v>0.001078309031835993</v>
       </c>
+      <c r="E48" t="n">
+        <v>0.005153981931799554</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1313,6 +1459,9 @@
       <c r="D49" t="n">
         <v>0.0002229618483275556</v>
       </c>
+      <c r="E49" t="n">
+        <v>0.004022461547233162</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1331,6 +1480,9 @@
       <c r="D50" t="n">
         <v>0.000841145348036726</v>
       </c>
+      <c r="E50" t="n">
+        <v>0.005266608492948535</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1349,6 +1501,9 @@
       <c r="D51" t="n">
         <v>0.001251357899912936</v>
       </c>
+      <c r="E51" t="n">
+        <v>0.005791925688145094</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1367,6 +1522,9 @@
       <c r="D52" t="n">
         <v>0.0003638700181774505</v>
       </c>
+      <c r="E52" t="n">
+        <v>0.005060297753760877</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1385,6 +1543,9 @@
       <c r="D53" t="n">
         <v>9.715186655459785e-05</v>
       </c>
+      <c r="E53" t="n">
+        <v>0.004383243506370678</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1403,6 +1564,9 @@
       <c r="D54" t="n">
         <v>0.0004541298715294166</v>
       </c>
+      <c r="E54" t="n">
+        <v>0.003962462380882554</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1421,6 +1585,9 @@
       <c r="D55" t="n">
         <v>0.0004081858170585826</v>
       </c>
+      <c r="E55" t="n">
+        <v>0.00490828352978066</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1439,6 +1606,9 @@
       <c r="D56" t="n">
         <v>0.0008347102146395993</v>
       </c>
+      <c r="E56" t="n">
+        <v>0.005429984405781685</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1457,6 +1627,9 @@
       <c r="D57" t="n">
         <v>0.0001720153340882423</v>
       </c>
+      <c r="E57" t="n">
+        <v>0.00392302414616869</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1475,6 +1648,9 @@
       <c r="D58" t="n">
         <v>0.0003988744719745703</v>
       </c>
+      <c r="E58" t="n">
+        <v>0.005489457327215333</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1493,6 +1669,9 @@
       <c r="D59" t="n">
         <v>0.0003250292848908075</v>
       </c>
+      <c r="E59" t="n">
+        <v>0.005638064812983782</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1511,6 +1690,9 @@
       <c r="D60" t="n">
         <v>0.0008435573846801778</v>
       </c>
+      <c r="E60" t="n">
+        <v>0.005390629197070221</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1529,6 +1711,9 @@
       <c r="D61" t="n">
         <v>0.0009705640947476603</v>
       </c>
+      <c r="E61" t="n">
+        <v>0.006011275375102831</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1547,6 +1732,9 @@
       <c r="D62" t="n">
         <v>0.0009727919213404713</v>
       </c>
+      <c r="E62" t="n">
+        <v>0.005493970945443856</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1565,6 +1753,9 @@
       <c r="D63" t="n">
         <v>0.0005901645138169543</v>
       </c>
+      <c r="E63" t="n">
+        <v>0.005068534748521255</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1583,6 +1774,9 @@
       <c r="D64" t="n">
         <v>0.0005236723294153528</v>
       </c>
+      <c r="E64" t="n">
+        <v>0.005615191834422185</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1601,6 +1795,9 @@
       <c r="D65" t="n">
         <v>0.0002146864209485292</v>
       </c>
+      <c r="E65" t="n">
+        <v>0.004784440345779533</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1619,6 +1816,9 @@
       <c r="D66" t="n">
         <v>0.0007045246271428697</v>
       </c>
+      <c r="E66" t="n">
+        <v>0.005504051669898882</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1637,6 +1837,9 @@
       <c r="D67" t="n">
         <v>0.0003032814142547978</v>
       </c>
+      <c r="E67" t="n">
+        <v>0.003575027984592325</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1655,6 +1858,9 @@
       <c r="D68" t="n">
         <v>0.004346470052549058</v>
       </c>
+      <c r="E68" t="n">
+        <v>0.006414894348209245</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1673,6 +1879,9 @@
       <c r="D69" t="n">
         <v>0.0004344752821648739</v>
       </c>
+      <c r="E69" t="n">
+        <v>0.004633740461632506</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1691,6 +1900,9 @@
       <c r="D70" t="n">
         <v>0.0005423095489514299</v>
       </c>
+      <c r="E70" t="n">
+        <v>0.005761257770470984</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1709,6 +1921,9 @@
       <c r="D71" t="n">
         <v>0.0002599803882558001</v>
       </c>
+      <c r="E71" t="n">
+        <v>0.004454278024505289</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1727,6 +1942,9 @@
       <c r="D72" t="n">
         <v>0.0005437092915271067</v>
       </c>
+      <c r="E72" t="n">
+        <v>0.005267639038142327</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1745,6 +1963,9 @@
       <c r="D73" t="n">
         <v>0.0005261830955515446</v>
       </c>
+      <c r="E73" t="n">
+        <v>0.005628574411131764</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1763,6 +1984,9 @@
       <c r="D74" t="n">
         <v>0.00055745492018051</v>
       </c>
+      <c r="E74" t="n">
+        <v>0.005784692601684993</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1781,6 +2005,9 @@
       <c r="D75" t="n">
         <v>0.0003249657076860776</v>
       </c>
+      <c r="E75" t="n">
+        <v>0.005325907285843794</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1799,6 +2026,9 @@
       <c r="D76" t="n">
         <v>0.001087359391529069</v>
       </c>
+      <c r="E76" t="n">
+        <v>0.004480808419653054</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1817,6 +2047,9 @@
       <c r="D77" t="n">
         <v>0.0002071406227481234</v>
       </c>
+      <c r="E77" t="n">
+        <v>0.003627074684387098</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1835,6 +2068,9 @@
       <c r="D78" t="n">
         <v>0.0001876186834234149</v>
       </c>
+      <c r="E78" t="n">
+        <v>0.003879792076407563</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1853,6 +2089,9 @@
       <c r="D79" t="n">
         <v>6.422960795356418e-05</v>
       </c>
+      <c r="E79" t="n">
+        <v>0.003277791348291767</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1871,6 +2110,9 @@
       <c r="D80" t="n">
         <v>0.0002562650629241592</v>
       </c>
+      <c r="E80" t="n">
+        <v>0.004822743609870303</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1889,6 +2131,9 @@
       <c r="D81" t="n">
         <v>0.0003416362954531821</v>
       </c>
+      <c r="E81" t="n">
+        <v>0.005505289153948207</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1907,6 +2152,9 @@
       <c r="D82" t="n">
         <v>0.0006488206824830266</v>
       </c>
+      <c r="E82" t="n">
+        <v>0.004452046716725676</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1925,6 +2173,9 @@
       <c r="D83" t="n">
         <v>0.001338521359388369</v>
       </c>
+      <c r="E83" t="n">
+        <v>0.005265361971736496</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1943,6 +2194,9 @@
       <c r="D84" t="n">
         <v>0.0003649279982796448</v>
       </c>
+      <c r="E84" t="n">
+        <v>0.0038604604810721</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1961,6 +2215,9 @@
       <c r="D85" t="n">
         <v>0.01308219620728806</v>
       </c>
+      <c r="E85" t="n">
+        <v>0.006327972447624566</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1979,6 +2236,9 @@
       <c r="D86" t="n">
         <v>0.01308570486960742</v>
       </c>
+      <c r="E86" t="n">
+        <v>0.00633329584081989</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1997,6 +2257,9 @@
       <c r="D87" t="n">
         <v>0.0004705838834679662</v>
       </c>
+      <c r="E87" t="n">
+        <v>0.005401911025917049</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2015,6 +2278,9 @@
       <c r="D88" t="n">
         <v>0.000780798549294413</v>
       </c>
+      <c r="E88" t="n">
+        <v>0.005252263517998434</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2033,6 +2299,9 @@
       <c r="D89" t="n">
         <v>0.0007971461488427773</v>
       </c>
+      <c r="E89" t="n">
+        <v>0.00527534951939903</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2051,6 +2320,9 @@
       <c r="D90" t="n">
         <v>0.0001596241111379621</v>
       </c>
+      <c r="E90" t="n">
+        <v>0.003865202894929595</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2069,6 +2341,9 @@
       <c r="D91" t="n">
         <v>0.001018292142968529</v>
       </c>
+      <c r="E91" t="n">
+        <v>0.006130837502207331</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2087,6 +2362,9 @@
       <c r="D92" t="n">
         <v>0.0002655115005189205</v>
       </c>
+      <c r="E92" t="n">
+        <v>0.004440659002506743</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2105,6 +2383,9 @@
       <c r="D93" t="n">
         <v>0.0002132812428666431</v>
       </c>
+      <c r="E93" t="n">
+        <v>0.004184451267676556</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2123,6 +2404,9 @@
       <c r="D94" t="n">
         <v>0.001129692618099165</v>
       </c>
+      <c r="E94" t="n">
+        <v>0.005020453009521485</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2141,6 +2425,9 @@
       <c r="D95" t="n">
         <v>0.0001857730337117061</v>
       </c>
+      <c r="E95" t="n">
+        <v>0.003699996954852592</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2159,6 +2446,9 @@
       <c r="D96" t="n">
         <v>0.0005346902285034596</v>
       </c>
+      <c r="E96" t="n">
+        <v>0.004980411019816891</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2177,6 +2467,9 @@
       <c r="D97" t="n">
         <v>0.0001767320704935316</v>
       </c>
+      <c r="E97" t="n">
+        <v>0.003881242579063649</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2195,6 +2488,9 @@
       <c r="D98" t="n">
         <v>0.0002601573782361295</v>
       </c>
+      <c r="E98" t="n">
+        <v>0.004615136348621382</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2213,6 +2509,9 @@
       <c r="D99" t="n">
         <v>0.0006308822491063074</v>
       </c>
+      <c r="E99" t="n">
+        <v>0.005660589928945919</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2231,6 +2530,9 @@
       <c r="D100" t="n">
         <v>0.0002521735506934619</v>
       </c>
+      <c r="E100" t="n">
+        <v>0.004613394526042138</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2249,6 +2551,9 @@
       <c r="D101" t="n">
         <v>0.0007490377836137413</v>
       </c>
+      <c r="E101" t="n">
+        <v>0.006036203022145263</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2267,6 +2572,9 @@
       <c r="D102" t="n">
         <v>0.0002683511081505308</v>
       </c>
+      <c r="E102" t="n">
+        <v>0.004526247486457069</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2285,6 +2593,9 @@
       <c r="D103" t="n">
         <v>0.0002654013952445952</v>
       </c>
+      <c r="E103" t="n">
+        <v>0.004786501328281187</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2303,6 +2614,9 @@
       <c r="D104" t="n">
         <v>0.0149343636114524</v>
       </c>
+      <c r="E104" t="n">
+        <v>0.006998228090665987</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2321,6 +2635,9 @@
       <c r="D105" t="n">
         <v>0.01549888952620185</v>
       </c>
+      <c r="E105" t="n">
+        <v>0.007390239422842248</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2339,6 +2656,9 @@
       <c r="D106" t="n">
         <v>0.001672551533604284</v>
       </c>
+      <c r="E106" t="n">
+        <v>0.006443920602358332</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2357,6 +2677,9 @@
       <c r="D107" t="n">
         <v>0.0001222540351379553</v>
       </c>
+      <c r="E107" t="n">
+        <v>0.003982499667036932</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2375,6 +2698,9 @@
       <c r="D108" t="n">
         <v>0.0003694172006441572</v>
       </c>
+      <c r="E108" t="n">
+        <v>0.005083082264454132</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2393,6 +2719,9 @@
       <c r="D109" t="n">
         <v>0.0009606240741504159</v>
       </c>
+      <c r="E109" t="n">
+        <v>0.005978253014460307</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2411,6 +2740,9 @@
       <c r="D110" t="n">
         <v>0.0003743618748641922</v>
       </c>
+      <c r="E110" t="n">
+        <v>0.004083185355749554</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2429,6 +2761,9 @@
       <c r="D111" t="n">
         <v>0.0007593223912696569</v>
       </c>
+      <c r="E111" t="n">
+        <v>0.006025158633442575</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2447,6 +2782,9 @@
       <c r="D112" t="n">
         <v>0.0007312724151927992</v>
       </c>
+      <c r="E112" t="n">
+        <v>0.005196341526207598</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2465,6 +2803,9 @@
       <c r="D113" t="n">
         <v>0.0001026160207466984</v>
       </c>
+      <c r="E113" t="n">
+        <v>0.00301553911124778</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2483,6 +2824,9 @@
       <c r="D114" t="n">
         <v>0.0002309698118162815</v>
       </c>
+      <c r="E114" t="n">
+        <v>0.003056796403788469</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2501,6 +2845,9 @@
       <c r="D115" t="n">
         <v>0.0005953400454786626</v>
       </c>
+      <c r="E115" t="n">
+        <v>0.005426336819289736</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2519,6 +2866,9 @@
       <c r="D116" t="n">
         <v>0.0004480858200732736</v>
       </c>
+      <c r="E116" t="n">
+        <v>0.004794306309338327</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2537,6 +2887,9 @@
       <c r="D117" t="n">
         <v>0.0003673894592579148</v>
       </c>
+      <c r="E117" t="n">
+        <v>0.005003720161355483</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2555,6 +2908,9 @@
       <c r="D118" t="n">
         <v>0.0004631667733544153</v>
       </c>
+      <c r="E118" t="n">
+        <v>0.00423567557785494</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2573,6 +2929,9 @@
       <c r="D119" t="n">
         <v>0.0004249366478626648</v>
       </c>
+      <c r="E119" t="n">
+        <v>0.005513701372992923</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2591,6 +2950,9 @@
       <c r="D120" t="n">
         <v>0.0001835324508067539</v>
       </c>
+      <c r="E120" t="n">
+        <v>0.003501106401807212</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2609,6 +2971,9 @@
       <c r="D121" t="n">
         <v>0.0005615872993624315</v>
       </c>
+      <c r="E121" t="n">
+        <v>0.005782933977513421</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2627,6 +2992,9 @@
       <c r="D122" t="n">
         <v>0.0002005164059060071</v>
       </c>
+      <c r="E122" t="n">
+        <v>0.003526917471503535</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2645,6 +3013,9 @@
       <c r="D123" t="n">
         <v>0.0006663989758629662</v>
       </c>
+      <c r="E123" t="n">
+        <v>0.005195894680527963</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2663,6 +3034,9 @@
       <c r="D124" t="n">
         <v>0.0004502666857084545</v>
       </c>
+      <c r="E124" t="n">
+        <v>0.004762216932184977</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2681,6 +3055,9 @@
       <c r="D125" t="n">
         <v>0.000514280256101958</v>
       </c>
+      <c r="E125" t="n">
+        <v>0.004415000691865205</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2699,6 +3076,9 @@
       <c r="D126" t="n">
         <v>0.001190609324209765</v>
       </c>
+      <c r="E126" t="n">
+        <v>0.00530135459906003</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2717,6 +3097,9 @@
       <c r="D127" t="n">
         <v>0.0003424555115497181</v>
       </c>
+      <c r="E127" t="n">
+        <v>0.005383037982814084</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2735,6 +3118,9 @@
       <c r="D128" t="n">
         <v>0.0004110724649045178</v>
       </c>
+      <c r="E128" t="n">
+        <v>0.005597835842870543</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -2753,6 +3139,9 @@
       <c r="D129" t="n">
         <v>0.0006276291916475625</v>
       </c>
+      <c r="E129" t="n">
+        <v>0.005819985773141492</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -2771,6 +3160,9 @@
       <c r="D130" t="n">
         <v>0.0004147777407640055</v>
       </c>
+      <c r="E130" t="n">
+        <v>0.00509131869058463</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -2789,6 +3181,9 @@
       <c r="D131" t="n">
         <v>0.0005622694804301054</v>
       </c>
+      <c r="E131" t="n">
+        <v>0.005279686227743294</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -2807,6 +3202,9 @@
       <c r="D132" t="n">
         <v>0.0003272139318984047</v>
       </c>
+      <c r="E132" t="n">
+        <v>0.004689172382579182</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -2825,6 +3223,9 @@
       <c r="D133" t="n">
         <v>7.840190064172289e-05</v>
       </c>
+      <c r="E133" t="n">
+        <v>0.002647575847410403</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2843,6 +3244,9 @@
       <c r="D134" t="n">
         <v>0.000453017746896143</v>
       </c>
+      <c r="E134" t="n">
+        <v>0.005412146838155584</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -2861,6 +3265,9 @@
       <c r="D135" t="n">
         <v>0.0002621954584885054</v>
       </c>
+      <c r="E135" t="n">
+        <v>0.004628667338778467</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2879,6 +3286,9 @@
       <c r="D136" t="n">
         <v>0.0001438903611711849</v>
       </c>
+      <c r="E136" t="n">
+        <v>0.003700747466316331</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -2897,6 +3307,9 @@
       <c r="D137" t="n">
         <v>0.0008590803765589887</v>
       </c>
+      <c r="E137" t="n">
+        <v>0.004774979206932107</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -2915,6 +3328,9 @@
       <c r="D138" t="n">
         <v>0.0001192091147490614</v>
       </c>
+      <c r="E138" t="n">
+        <v>0.00259397363525905</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -2933,6 +3349,9 @@
       <c r="D139" t="n">
         <v>0.02160698852408633</v>
       </c>
+      <c r="E139" t="n">
+        <v>0.006668235600639313</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -2951,6 +3370,9 @@
       <c r="D140" t="n">
         <v>0.02138311325337231</v>
       </c>
+      <c r="E140" t="n">
+        <v>0.006540654005125271</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -2969,6 +3391,9 @@
       <c r="D141" t="n">
         <v>0.0001780119441551317</v>
       </c>
+      <c r="E141" t="n">
+        <v>0.004213196546871988</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -2987,6 +3412,9 @@
       <c r="D142" t="n">
         <v>0.0001342604815096694</v>
       </c>
+      <c r="E142" t="n">
+        <v>0.00399427819558875</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3005,6 +3433,9 @@
       <c r="D143" t="n">
         <v>0.0009880130072765021</v>
       </c>
+      <c r="E143" t="n">
+        <v>0.006044237340389758</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3023,6 +3454,9 @@
       <c r="D144" t="n">
         <v>0.0006056231881428641</v>
       </c>
+      <c r="E144" t="n">
+        <v>0.005227983284813805</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3041,6 +3475,9 @@
       <c r="D145" t="n">
         <v>0.0009637749339608424</v>
       </c>
+      <c r="E145" t="n">
+        <v>0.00594429432235138</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3059,6 +3496,9 @@
       <c r="D146" t="n">
         <v>0.001292973685002282</v>
       </c>
+      <c r="E146" t="n">
+        <v>0.005762122141044855</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3077,6 +3517,9 @@
       <c r="D147" t="n">
         <v>0.0003205881557435947</v>
       </c>
+      <c r="E147" t="n">
+        <v>0.005336576853522842</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -3095,6 +3538,9 @@
       <c r="D148" t="n">
         <v>0.0002984213002506911</v>
       </c>
+      <c r="E148" t="n">
+        <v>0.004966959499284061</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -3113,6 +3559,9 @@
       <c r="D149" t="n">
         <v>0.0004250421428152648</v>
       </c>
+      <c r="E149" t="n">
+        <v>0.004901366783861468</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -3131,6 +3580,9 @@
       <c r="D150" t="n">
         <v>0.0003438581706014339</v>
       </c>
+      <c r="E150" t="n">
+        <v>0.004966749767483236</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3149,6 +3601,9 @@
       <c r="D151" t="n">
         <v>0.0003601666661971685</v>
       </c>
+      <c r="E151" t="n">
+        <v>0.005657758967762709</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3167,6 +3622,9 @@
       <c r="D152" t="n">
         <v>0.0003879780782671794</v>
       </c>
+      <c r="E152" t="n">
+        <v>0.005212525385645138</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3185,6 +3643,9 @@
       <c r="D153" t="n">
         <v>0.0002677578694603806</v>
       </c>
+      <c r="E153" t="n">
+        <v>0.004548886824146346</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -3203,6 +3664,9 @@
       <c r="D154" t="n">
         <v>0.0008171408148454954</v>
       </c>
+      <c r="E154" t="n">
+        <v>0.005990885051816042</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3221,6 +3685,9 @@
       <c r="D155" t="n">
         <v>0.000467296325412658</v>
       </c>
+      <c r="E155" t="n">
+        <v>0.005488393677888702</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3239,6 +3706,9 @@
       <c r="D156" t="n">
         <v>0.0009380856313274643</v>
       </c>
+      <c r="E156" t="n">
+        <v>0.004943233603334024</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3257,6 +3727,9 @@
       <c r="D157" t="n">
         <v>0.0003902681838869695</v>
       </c>
+      <c r="E157" t="n">
+        <v>0.00527118451514075</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3275,6 +3748,9 @@
       <c r="D158" t="n">
         <v>0.0004773004611183203</v>
       </c>
+      <c r="E158" t="n">
+        <v>0.005368291373593793</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3293,6 +3769,9 @@
       <c r="D159" t="n">
         <v>0.0007537403471612459</v>
       </c>
+      <c r="E159" t="n">
+        <v>0.004985760444695526</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3311,6 +3790,9 @@
       <c r="D160" t="n">
         <v>0.001012759222834301</v>
       </c>
+      <c r="E160" t="n">
+        <v>0.006067591469033237</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3329,6 +3811,9 @@
       <c r="D161" t="n">
         <v>0.0006185898707451237</v>
       </c>
+      <c r="E161" t="n">
+        <v>0.005479770900658026</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3347,6 +3832,9 @@
       <c r="D162" t="n">
         <v>0.0005324917916936625</v>
       </c>
+      <c r="E162" t="n">
+        <v>0.004873631595158053</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3365,6 +3853,9 @@
       <c r="D163" t="n">
         <v>0.0002097302910227415</v>
       </c>
+      <c r="E163" t="n">
+        <v>0.003921181401864682</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3383,6 +3874,9 @@
       <c r="D164" t="n">
         <v>0.0006584255713136454</v>
       </c>
+      <c r="E164" t="n">
+        <v>0.005740926144409885</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3401,6 +3895,9 @@
       <c r="D165" t="n">
         <v>0.0002341391924296649</v>
       </c>
+      <c r="E165" t="n">
+        <v>0.0041289385468056</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3419,6 +3916,9 @@
       <c r="D166" t="n">
         <v>0.0009040950660464993</v>
       </c>
+      <c r="E166" t="n">
+        <v>0.005877117029169873</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -3437,6 +3937,9 @@
       <c r="D167" t="n">
         <v>0.0001903044985013103</v>
       </c>
+      <c r="E167" t="n">
+        <v>0.004844389777188411</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -3455,6 +3958,9 @@
       <c r="D168" t="n">
         <v>0.0003364492294165963</v>
       </c>
+      <c r="E168" t="n">
+        <v>0.004700663691692694</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -3473,6 +3979,9 @@
       <c r="D169" t="n">
         <v>0.0001593894419938046</v>
       </c>
+      <c r="E169" t="n">
+        <v>0.003894415118896421</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -3491,6 +4000,9 @@
       <c r="D170" t="n">
         <v>0.0006320940322342269</v>
       </c>
+      <c r="E170" t="n">
+        <v>0.005747387967909815</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -3509,6 +4021,9 @@
       <c r="D171" t="n">
         <v>0.0006192282118591715</v>
       </c>
+      <c r="E171" t="n">
+        <v>0.005449796758089644</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -3527,6 +4042,9 @@
       <c r="D172" t="n">
         <v>0.0002498696464306034</v>
       </c>
+      <c r="E172" t="n">
+        <v>0.004162464187554672</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -3545,6 +4063,9 @@
       <c r="D173" t="n">
         <v>0.000312705811578149</v>
       </c>
+      <c r="E173" t="n">
+        <v>0.003980006891171064</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -3563,6 +4084,9 @@
       <c r="D174" t="n">
         <v>0.001113800960197291</v>
       </c>
+      <c r="E174" t="n">
+        <v>0.00621326255571527</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -3581,6 +4105,9 @@
       <c r="D175" t="n">
         <v>0.0005390832655312055</v>
       </c>
+      <c r="E175" t="n">
+        <v>0.005671617884229583</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -3599,6 +4126,9 @@
       <c r="D176" t="n">
         <v>0.0003695217053371347</v>
       </c>
+      <c r="E176" t="n">
+        <v>0.005161045273196322</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -3617,6 +4147,9 @@
       <c r="D177" t="n">
         <v>0.000807548900927084</v>
       </c>
+      <c r="E177" t="n">
+        <v>0.005472886504215735</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -3635,6 +4168,9 @@
       <c r="D178" t="n">
         <v>0.0002942471730617423</v>
       </c>
+      <c r="E178" t="n">
+        <v>0.004347420651393393</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -3653,6 +4189,9 @@
       <c r="D179" t="n">
         <v>0.0008880248028829103</v>
       </c>
+      <c r="E179" t="n">
+        <v>0.005078000568890852</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -3671,6 +4210,9 @@
       <c r="D180" t="n">
         <v>0.0003744245469163843</v>
       </c>
+      <c r="E180" t="n">
+        <v>0.004277860671285011</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -3689,6 +4231,9 @@
       <c r="D181" t="n">
         <v>0.000122796226058209</v>
       </c>
+      <c r="E181" t="n">
+        <v>0.0035151376935886</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -3707,6 +4252,9 @@
       <c r="D182" t="n">
         <v>0.0001812100533842004</v>
       </c>
+      <c r="E182" t="n">
+        <v>0.004765243351466467</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -3725,6 +4273,9 @@
       <c r="D183" t="n">
         <v>0.0001050948256882306</v>
       </c>
+      <c r="E183" t="n">
+        <v>0.003247219880431243</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -3743,6 +4294,9 @@
       <c r="D184" t="n">
         <v>0.0005416774749299511</v>
       </c>
+      <c r="E184" t="n">
+        <v>0.00493842361911646</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -3761,6 +4315,9 @@
       <c r="D185" t="n">
         <v>0.0001824088940724315</v>
       </c>
+      <c r="E185" t="n">
+        <v>0.00332688872969455</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -3779,6 +4336,9 @@
       <c r="D186" t="n">
         <v>0.0006050305763385983</v>
       </c>
+      <c r="E186" t="n">
+        <v>0.004622578705284835</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -3797,6 +4357,9 @@
       <c r="D187" t="n">
         <v>0.0001305131083220482</v>
       </c>
+      <c r="E187" t="n">
+        <v>0.003793936831900681</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -3815,6 +4378,9 @@
       <c r="D188" t="n">
         <v>0.0001643848594526636</v>
       </c>
+      <c r="E188" t="n">
+        <v>0.003787020476174951</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -3833,6 +4399,9 @@
       <c r="D189" t="n">
         <v>0.001149695847050662</v>
       </c>
+      <c r="E189" t="n">
+        <v>0.005493353740822523</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -3851,6 +4420,9 @@
       <c r="D190" t="n">
         <v>0.0006478903760449114</v>
       </c>
+      <c r="E190" t="n">
+        <v>0.004782606251090559</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -3869,6 +4441,9 @@
       <c r="D191" t="n">
         <v>0.0002235470280220287</v>
       </c>
+      <c r="E191" t="n">
+        <v>0.003921211105092393</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -3887,6 +4462,9 @@
       <c r="D192" t="n">
         <v>0.0006831893375695448</v>
       </c>
+      <c r="E192" t="n">
+        <v>0.006137598642256468</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -3905,6 +4483,9 @@
       <c r="D193" t="n">
         <v>0.001707428079345343</v>
       </c>
+      <c r="E193" t="n">
+        <v>0.005770582884037785</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -3923,6 +4504,9 @@
       <c r="D194" t="n">
         <v>0.001063238037872163</v>
       </c>
+      <c r="E194" t="n">
+        <v>0.004823824772434167</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -3941,6 +4525,9 @@
       <c r="D195" t="n">
         <v>0.001794602210824269</v>
       </c>
+      <c r="E195" t="n">
+        <v>0.00616974144240913</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -3959,6 +4546,9 @@
       <c r="D196" t="n">
         <v>0.0002478800043563056</v>
       </c>
+      <c r="E196" t="n">
+        <v>0.003954130484214044</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -3977,6 +4567,9 @@
       <c r="D197" t="n">
         <v>0.0002323248435243569</v>
       </c>
+      <c r="E197" t="n">
+        <v>0.004418541806568816</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -3995,6 +4588,9 @@
       <c r="D198" t="n">
         <v>0.00088266530147904</v>
       </c>
+      <c r="E198" t="n">
+        <v>0.005701885697094238</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -4013,6 +4609,9 @@
       <c r="D199" t="n">
         <v>0.0008746403732371296</v>
       </c>
+      <c r="E199" t="n">
+        <v>0.004585553455355855</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -4031,6 +4630,9 @@
       <c r="D200" t="n">
         <v>0.0006148954630939968</v>
       </c>
+      <c r="E200" t="n">
+        <v>0.00468926964447388</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -4049,6 +4651,9 @@
       <c r="D201" t="n">
         <v>0.0003468642955288266</v>
       </c>
+      <c r="E201" t="n">
+        <v>0.004721104345872905</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -4067,6 +4672,9 @@
       <c r="D202" t="n">
         <v>0.0001234072089349207</v>
       </c>
+      <c r="E202" t="n">
+        <v>0.004095334341249084</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -4085,6 +4693,9 @@
       <c r="D203" t="n">
         <v>0.0007770874024196251</v>
       </c>
+      <c r="E203" t="n">
+        <v>0.004735704168633909</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -4103,6 +4714,9 @@
       <c r="D204" t="n">
         <v>0.0009553551596615781</v>
       </c>
+      <c r="E204" t="n">
+        <v>0.005594919168748545</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -4121,6 +4735,9 @@
       <c r="D205" t="n">
         <v>0.001463640027829313</v>
       </c>
+      <c r="E205" t="n">
+        <v>0.006209023932602365</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -4139,6 +4756,9 @@
       <c r="D206" t="n">
         <v>5.7703452367241e-05</v>
       </c>
+      <c r="E206" t="n">
+        <v>0.003503055597510714</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -4157,6 +4777,9 @@
       <c r="D207" t="n">
         <v>0.0002058348341785911</v>
       </c>
+      <c r="E207" t="n">
+        <v>0.002912934806447916</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -4175,6 +4798,9 @@
       <c r="D208" t="n">
         <v>0.0007828220212718971</v>
       </c>
+      <c r="E208" t="n">
+        <v>0.003345944967226473</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -4193,6 +4819,9 @@
       <c r="D209" t="n">
         <v>0.0008079973165156653</v>
       </c>
+      <c r="E209" t="n">
+        <v>0.003472892715719334</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -4211,6 +4840,9 @@
       <c r="D210" t="n">
         <v>0.0007011216311719314</v>
       </c>
+      <c r="E210" t="n">
+        <v>0.00465136524050766</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -4229,6 +4861,9 @@
       <c r="D211" t="n">
         <v>0.0002340208493137255</v>
       </c>
+      <c r="E211" t="n">
+        <v>0.004323988899160104</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -4247,6 +4882,9 @@
       <c r="D212" t="n">
         <v>0.0001047645164884609</v>
       </c>
+      <c r="E212" t="n">
+        <v>0.003002472238858838</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -4265,6 +4903,9 @@
       <c r="D213" t="n">
         <v>0.001007664027470871</v>
       </c>
+      <c r="E213" t="n">
+        <v>0.005753510774220174</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -4283,6 +4924,9 @@
       <c r="D214" t="n">
         <v>0.0006816527887277569</v>
       </c>
+      <c r="E214" t="n">
+        <v>0.004992269959657262</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -4301,6 +4945,9 @@
       <c r="D215" t="n">
         <v>0.0003269613756564203</v>
       </c>
+      <c r="E215" t="n">
+        <v>0.004692369813318748</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -4319,6 +4966,9 @@
       <c r="D216" t="n">
         <v>0.0006811916903099345</v>
       </c>
+      <c r="E216" t="n">
+        <v>0.005251954646821422</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -4337,6 +4987,9 @@
       <c r="D217" t="n">
         <v>0.001104691778927141</v>
       </c>
+      <c r="E217" t="n">
+        <v>0.00540567473139178</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -4355,6 +5008,9 @@
       <c r="D218" t="n">
         <v>0.0006544101410517034</v>
       </c>
+      <c r="E218" t="n">
+        <v>0.005123781404860327</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -4373,6 +5029,9 @@
       <c r="D219" t="n">
         <v>0.0005124995752137127</v>
       </c>
+      <c r="E219" t="n">
+        <v>0.005528980771566605</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -4391,6 +5050,9 @@
       <c r="D220" t="n">
         <v>0.0002278491886384861</v>
       </c>
+      <c r="E220" t="n">
+        <v>0.004811475889214075</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -4409,6 +5071,9 @@
       <c r="D221" t="n">
         <v>0.000322602502637072</v>
       </c>
+      <c r="E221" t="n">
+        <v>0.005050472678696493</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -4427,6 +5092,9 @@
       <c r="D222" t="n">
         <v>0.0002534859290661337</v>
       </c>
+      <c r="E222" t="n">
+        <v>0.004911010603800755</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -4445,6 +5113,9 @@
       <c r="D223" t="n">
         <v>0.0004709964964626211</v>
       </c>
+      <c r="E223" t="n">
+        <v>0.0039376495258709</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -4463,6 +5134,9 @@
       <c r="D224" t="n">
         <v>0.0005801961704131941</v>
       </c>
+      <c r="E224" t="n">
+        <v>0.005550428596472127</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -4481,6 +5155,9 @@
       <c r="D225" t="n">
         <v>0.000681084043648123</v>
       </c>
+      <c r="E225" t="n">
+        <v>0.004365356433854312</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -4499,6 +5176,9 @@
       <c r="D226" t="n">
         <v>0.0005257790682944679</v>
       </c>
+      <c r="E226" t="n">
+        <v>0.004692667953688796</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -4517,6 +5197,9 @@
       <c r="D227" t="n">
         <v>0.0001647764974192835</v>
       </c>
+      <c r="E227" t="n">
+        <v>0.00391584148121049</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -4535,6 +5218,9 @@
       <c r="D228" t="n">
         <v>0.0006777028103838159</v>
       </c>
+      <c r="E228" t="n">
+        <v>0.005139647608063529</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -4553,6 +5239,9 @@
       <c r="D229" t="n">
         <v>0.0006884925207601022</v>
       </c>
+      <c r="E229" t="n">
+        <v>0.005462549792354581</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -4571,6 +5260,9 @@
       <c r="D230" t="n">
         <v>0.0005811389547690279</v>
       </c>
+      <c r="E230" t="n">
+        <v>0.005761179069595813</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -4589,6 +5281,9 @@
       <c r="D231" t="n">
         <v>0.0002314284213061036</v>
       </c>
+      <c r="E231" t="n">
+        <v>0.004375243363112551</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -4607,6 +5302,9 @@
       <c r="D232" t="n">
         <v>0.001200434981056168</v>
       </c>
+      <c r="E232" t="n">
+        <v>0.006445789783713339</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -4625,6 +5323,9 @@
       <c r="D233" t="n">
         <v>0.0001632513453690358</v>
       </c>
+      <c r="E233" t="n">
+        <v>0.004151960693977624</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -4643,6 +5344,9 @@
       <c r="D234" t="n">
         <v>0.0005677912554374103</v>
       </c>
+      <c r="E234" t="n">
+        <v>0.005673404964962771</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -4661,6 +5365,9 @@
       <c r="D235" t="n">
         <v>0.0001420753498018478</v>
       </c>
+      <c r="E235" t="n">
+        <v>0.003577666393808835</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -4679,6 +5386,9 @@
       <c r="D236" t="n">
         <v>0.001610254149874439</v>
       </c>
+      <c r="E236" t="n">
+        <v>0.006317951777381817</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -4697,6 +5407,9 @@
       <c r="D237" t="n">
         <v>0.00158536304621549</v>
       </c>
+      <c r="E237" t="n">
+        <v>0.006185551968623893</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -4715,6 +5428,9 @@
       <c r="D238" t="n">
         <v>0.0007174041023420456</v>
       </c>
+      <c r="E238" t="n">
+        <v>0.005883876754106828</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -4733,6 +5449,9 @@
       <c r="D239" t="n">
         <v>0.0003015951285725737</v>
       </c>
+      <c r="E239" t="n">
+        <v>0.003778947951707784</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -4751,6 +5470,9 @@
       <c r="D240" t="n">
         <v>0.0009833104759321787</v>
       </c>
+      <c r="E240" t="n">
+        <v>0.005250663604717718</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -4769,6 +5491,9 @@
       <c r="D241" t="n">
         <v>0.0006430228809584078</v>
       </c>
+      <c r="E241" t="n">
+        <v>0.004694868244160224</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -4787,6 +5512,9 @@
       <c r="D242" t="n">
         <v>0.0008105846231087631</v>
       </c>
+      <c r="E242" t="n">
+        <v>0.005138552892880741</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -4805,6 +5533,9 @@
       <c r="D243" t="n">
         <v>0.0001168085693505337</v>
       </c>
+      <c r="E243" t="n">
+        <v>0.002846645211120956</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -4823,6 +5554,9 @@
       <c r="D244" t="n">
         <v>0.006360412475720644</v>
       </c>
+      <c r="E244" t="n">
+        <v>0.007176569292617851</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -4841,6 +5575,9 @@
       <c r="D245" t="n">
         <v>0.001144642034094419</v>
       </c>
+      <c r="E245" t="n">
+        <v>0.005459266545598764</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -4859,6 +5596,9 @@
       <c r="D246" t="n">
         <v>0.0007974350506099042</v>
       </c>
+      <c r="E246" t="n">
+        <v>0.005334194579540037</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -4877,6 +5617,9 @@
       <c r="D247" t="n">
         <v>0.0007834764946445591</v>
       </c>
+      <c r="E247" t="n">
+        <v>0.005146919433044001</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -4895,6 +5638,9 @@
       <c r="D248" t="n">
         <v>0.0009730758326949688</v>
       </c>
+      <c r="E248" t="n">
+        <v>0.005781911125811215</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -4913,6 +5659,9 @@
       <c r="D249" t="n">
         <v>0.0002201467310663079</v>
       </c>
+      <c r="E249" t="n">
+        <v>0.003586997955553443</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -4931,6 +5680,9 @@
       <c r="D250" t="n">
         <v>0.0003288198198824561</v>
       </c>
+      <c r="E250" t="n">
+        <v>0.004019392839368576</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -4949,6 +5701,9 @@
       <c r="D251" t="n">
         <v>0.001246509641805405</v>
       </c>
+      <c r="E251" t="n">
+        <v>0.005757823424894984</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -4967,6 +5722,9 @@
       <c r="D252" t="n">
         <v>0.0003956604823030874</v>
       </c>
+      <c r="E252" t="n">
+        <v>0.0052814667024042</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -4985,6 +5743,9 @@
       <c r="D253" t="n">
         <v>0.0004548205745464412</v>
       </c>
+      <c r="E253" t="n">
+        <v>0.004943643732515851</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -5003,6 +5764,9 @@
       <c r="D254" t="n">
         <v>0.0002951936828141509</v>
       </c>
+      <c r="E254" t="n">
+        <v>0.004797534557857531</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -5021,6 +5785,9 @@
       <c r="D255" t="n">
         <v>0.001262377473890768</v>
       </c>
+      <c r="E255" t="n">
+        <v>0.005650764638298679</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -5039,6 +5806,9 @@
       <c r="D256" t="n">
         <v>0.0003541082985527106</v>
       </c>
+      <c r="E256" t="n">
+        <v>0.004960129853321613</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -5057,6 +5827,9 @@
       <c r="D257" t="n">
         <v>0.00102107722833835</v>
       </c>
+      <c r="E257" t="n">
+        <v>0.006026515009469422</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -5075,6 +5848,9 @@
       <c r="D258" t="n">
         <v>0.0001884667087693427</v>
       </c>
+      <c r="E258" t="n">
+        <v>0.003485537729003947</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -5093,6 +5869,9 @@
       <c r="D259" t="n">
         <v>5.066840054644925e-05</v>
       </c>
+      <c r="E259" t="n">
+        <v>0.002432181183726548</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -5111,6 +5890,9 @@
       <c r="D260" t="n">
         <v>0.000937741709793248</v>
       </c>
+      <c r="E260" t="n">
+        <v>0.005792367375742907</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -5129,6 +5911,9 @@
       <c r="D261" t="n">
         <v>0.0003403105411046972</v>
       </c>
+      <c r="E261" t="n">
+        <v>0.004825515500299084</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -5147,6 +5932,9 @@
       <c r="D262" t="n">
         <v>0.001262579726121193</v>
       </c>
+      <c r="E262" t="n">
+        <v>0.005787664646778266</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -5165,6 +5953,9 @@
       <c r="D263" t="n">
         <v>0.0004266359636342097</v>
       </c>
+      <c r="E263" t="n">
+        <v>0.005321842779490779</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -5183,6 +5974,9 @@
       <c r="D264" t="n">
         <v>0.001083429452502743</v>
       </c>
+      <c r="E264" t="n">
+        <v>0.006551545079005293</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -5201,6 +5995,9 @@
       <c r="D265" t="n">
         <v>0.001078713106486094</v>
       </c>
+      <c r="E265" t="n">
+        <v>0.005075460180533234</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -5219,6 +6016,9 @@
       <c r="D266" t="n">
         <v>0.0004323103665759832</v>
       </c>
+      <c r="E266" t="n">
+        <v>0.005120310999371652</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -5237,6 +6037,9 @@
       <c r="D267" t="n">
         <v>0.0007265617323216841</v>
       </c>
+      <c r="E267" t="n">
+        <v>0.004486944506137899</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -5255,6 +6058,9 @@
       <c r="D268" t="n">
         <v>0.00103118638066352</v>
       </c>
+      <c r="E268" t="n">
+        <v>0.005816451579070132</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -5273,6 +6079,9 @@
       <c r="D269" t="n">
         <v>0.0007596431983643837</v>
       </c>
+      <c r="E269" t="n">
+        <v>0.005301296132683509</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -5291,6 +6100,9 @@
       <c r="D270" t="n">
         <v>0.0009935631216456192</v>
       </c>
+      <c r="E270" t="n">
+        <v>0.006223018997189907</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -5309,6 +6121,9 @@
       <c r="D271" t="n">
         <v>0.00113876840653973</v>
       </c>
+      <c r="E271" t="n">
+        <v>0.006471316986997647</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -5327,6 +6142,9 @@
       <c r="D272" t="n">
         <v>0.0007016385021314307</v>
       </c>
+      <c r="E272" t="n">
+        <v>0.005417656572151318</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -5345,6 +6163,9 @@
       <c r="D273" t="n">
         <v>0.0005291365290673624</v>
       </c>
+      <c r="E273" t="n">
+        <v>0.00560628303292297</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -5363,6 +6184,9 @@
       <c r="D274" t="n">
         <v>0.0006312158039172137</v>
       </c>
+      <c r="E274" t="n">
+        <v>0.004979724367154967</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -5381,6 +6205,9 @@
       <c r="D275" t="n">
         <v>0.0005990584903954033</v>
       </c>
+      <c r="E275" t="n">
+        <v>0.004645406963538698</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -5399,6 +6226,9 @@
       <c r="D276" t="n">
         <v>0.01814756164033218</v>
       </c>
+      <c r="E276" t="n">
+        <v>0.007789876174208813</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -5417,6 +6247,9 @@
       <c r="D277" t="n">
         <v>0.001138426432008002</v>
       </c>
+      <c r="E277" t="n">
+        <v>0.0063119964909382</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -5435,6 +6268,9 @@
       <c r="D278" t="n">
         <v>0.000561951747000625</v>
       </c>
+      <c r="E278" t="n">
+        <v>0.005491939420349041</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -5453,6 +6289,9 @@
       <c r="D279" t="n">
         <v>0.0007622195371225038</v>
       </c>
+      <c r="E279" t="n">
+        <v>0.005090957658365871</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -5471,6 +6310,9 @@
       <c r="D280" t="n">
         <v>0.0003957186179269463</v>
       </c>
+      <c r="E280" t="n">
+        <v>0.004470141421399901</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -5489,6 +6331,9 @@
       <c r="D281" t="n">
         <v>0.001172634922939144</v>
       </c>
+      <c r="E281" t="n">
+        <v>0.004571702060604105</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -5507,6 +6352,9 @@
       <c r="D282" t="n">
         <v>0.000443511051700937</v>
       </c>
+      <c r="E282" t="n">
+        <v>0.005460016141436381</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -5525,6 +6373,9 @@
       <c r="D283" t="n">
         <v>0.0005342877186320783</v>
       </c>
+      <c r="E283" t="n">
+        <v>0.005362550699334724</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -5543,6 +6394,9 @@
       <c r="D284" t="n">
         <v>0.0004977041797984671</v>
       </c>
+      <c r="E284" t="n">
+        <v>0.004866212890167441</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -5561,6 +6415,9 @@
       <c r="D285" t="n">
         <v>0.0002019064238468526</v>
       </c>
+      <c r="E285" t="n">
+        <v>0.004044238039613751</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -5579,6 +6436,9 @@
       <c r="D286" t="n">
         <v>0.0008238372155483748</v>
       </c>
+      <c r="E286" t="n">
+        <v>0.005478193059645763</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -5597,6 +6457,9 @@
       <c r="D287" t="n">
         <v>0.0002730213711270896</v>
       </c>
+      <c r="E287" t="n">
+        <v>0.004345897539924402</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -5615,6 +6478,9 @@
       <c r="D288" t="n">
         <v>0.0004173229010899457</v>
       </c>
+      <c r="E288" t="n">
+        <v>0.005153334958549616</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -5633,6 +6499,9 @@
       <c r="D289" t="n">
         <v>0.0001051608731851225</v>
       </c>
+      <c r="E289" t="n">
+        <v>0.002565289807663753</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -5651,6 +6520,9 @@
       <c r="D290" t="n">
         <v>0.001079457010417011</v>
       </c>
+      <c r="E290" t="n">
+        <v>0.005753655799961237</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -5669,6 +6541,9 @@
       <c r="D291" t="n">
         <v>0.0005017340834818574</v>
       </c>
+      <c r="E291" t="n">
+        <v>0.005783235786438458</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -5687,6 +6562,9 @@
       <c r="D292" t="n">
         <v>0.00128923943268755</v>
       </c>
+      <c r="E292" t="n">
+        <v>0.006154218122670837</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -5705,6 +6583,9 @@
       <c r="D293" t="n">
         <v>0.0007904232726956303</v>
       </c>
+      <c r="E293" t="n">
+        <v>0.005542147073476832</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -5723,6 +6604,9 @@
       <c r="D294" t="n">
         <v>0.0008460219971461218</v>
       </c>
+      <c r="E294" t="n">
+        <v>0.005869117280950887</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -5741,6 +6625,9 @@
       <c r="D295" t="n">
         <v>0.001175167479082634</v>
       </c>
+      <c r="E295" t="n">
+        <v>0.005407703044291736</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -5759,6 +6646,9 @@
       <c r="D296" t="n">
         <v>0.0002306350186384196</v>
       </c>
+      <c r="E296" t="n">
+        <v>0.004078356647008754</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -5777,6 +6667,9 @@
       <c r="D297" t="n">
         <v>0.0009631538546518921</v>
       </c>
+      <c r="E297" t="n">
+        <v>0.005623884789267401</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -5795,6 +6688,9 @@
       <c r="D298" t="n">
         <v>0.001269094260097707</v>
       </c>
+      <c r="E298" t="n">
+        <v>0.005822522227761574</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -5813,6 +6709,9 @@
       <c r="D299" t="n">
         <v>0.0005564776135987643</v>
       </c>
+      <c r="E299" t="n">
+        <v>0.005849967308793062</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -5831,6 +6730,9 @@
       <c r="D300" t="n">
         <v>0.0002283177856919068</v>
       </c>
+      <c r="E300" t="n">
+        <v>0.004536942027045409</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -5849,6 +6751,9 @@
       <c r="D301" t="n">
         <v>0.0004646434579729217</v>
       </c>
+      <c r="E301" t="n">
+        <v>0.003982989911592964</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -5867,6 +6772,9 @@
       <c r="D302" t="n">
         <v>0.0004492611863813903</v>
       </c>
+      <c r="E302" t="n">
+        <v>0.004958610591222063</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -5885,6 +6793,9 @@
       <c r="D303" t="n">
         <v>0.001005062054895251</v>
       </c>
+      <c r="E303" t="n">
+        <v>0.006130710184450541</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -5903,6 +6814,9 @@
       <c r="D304" t="n">
         <v>0.0001819669223613119</v>
       </c>
+      <c r="E304" t="n">
+        <v>0.003959496021457273</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -5921,6 +6835,9 @@
       <c r="D305" t="n">
         <v>0.0004974486478240981</v>
       </c>
+      <c r="E305" t="n">
+        <v>0.005713688581817</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -5939,6 +6856,9 @@
       <c r="D306" t="n">
         <v>0.0004151182486857524</v>
       </c>
+      <c r="E306" t="n">
+        <v>0.005710973742284939</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -5957,6 +6877,9 @@
       <c r="D307" t="n">
         <v>0.00096442187033685</v>
       </c>
+      <c r="E307" t="n">
+        <v>0.005710345761462531</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -5975,6 +6898,9 @@
       <c r="D308" t="n">
         <v>0.0009065284739568638</v>
       </c>
+      <c r="E308" t="n">
+        <v>0.006013112418950987</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -5993,6 +6919,9 @@
       <c r="D309" t="n">
         <v>0.001007776906955059</v>
       </c>
+      <c r="E309" t="n">
+        <v>0.005591519146149977</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -6011,6 +6940,9 @@
       <c r="D310" t="n">
         <v>0.0006028538109818702</v>
       </c>
+      <c r="E310" t="n">
+        <v>0.00509211658891186</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -6029,6 +6961,9 @@
       <c r="D311" t="n">
         <v>0.0006810418729004051</v>
       </c>
+      <c r="E311" t="n">
+        <v>0.005937287719333501</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -6047,6 +6982,9 @@
       <c r="D312" t="n">
         <v>0.0003543308606326476</v>
       </c>
+      <c r="E312" t="n">
+        <v>0.005088194638959754</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -6065,6 +7003,9 @@
       <c r="D313" t="n">
         <v>0.0007313787751571888</v>
       </c>
+      <c r="E313" t="n">
+        <v>0.005526251624008584</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -6083,6 +7024,9 @@
       <c r="D314" t="n">
         <v>0.0003864118903773423</v>
       </c>
+      <c r="E314" t="n">
+        <v>0.003938619868825353</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -6101,6 +7045,9 @@
       <c r="D315" t="n">
         <v>0.004822706609333018</v>
       </c>
+      <c r="E315" t="n">
+        <v>0.006820889640498902</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -6119,6 +7066,9 @@
       <c r="D316" t="n">
         <v>0.0004365879871240402</v>
       </c>
+      <c r="E316" t="n">
+        <v>0.004655064020020797</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -6137,6 +7087,9 @@
       <c r="D317" t="n">
         <v>0.0006303998181222396</v>
       </c>
+      <c r="E317" t="n">
+        <v>0.006035728637507907</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -6155,6 +7108,9 @@
       <c r="D318" t="n">
         <v>0.0002715119728300797</v>
       </c>
+      <c r="E318" t="n">
+        <v>0.004491218992385733</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -6173,6 +7129,9 @@
       <c r="D319" t="n">
         <v>0.0003729516679312571</v>
       </c>
+      <c r="E319" t="n">
+        <v>0.005334229735779036</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -6191,6 +7150,9 @@
       <c r="D320" t="n">
         <v>0.0007769238008941972</v>
       </c>
+      <c r="E320" t="n">
+        <v>0.006288475729303606</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -6209,6 +7171,9 @@
       <c r="D321" t="n">
         <v>0.0006279187583116926</v>
       </c>
+      <c r="E321" t="n">
+        <v>0.006050370324069724</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -6227,6 +7192,9 @@
       <c r="D322" t="n">
         <v>0.0004428791677399923</v>
       </c>
+      <c r="E322" t="n">
+        <v>0.005652114255494869</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -6245,6 +7213,9 @@
       <c r="D323" t="n">
         <v>0.001045183263046629</v>
       </c>
+      <c r="E323" t="n">
+        <v>0.004474788329055015</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -6263,6 +7234,9 @@
       <c r="D324" t="n">
         <v>0.0002174674369866036</v>
       </c>
+      <c r="E324" t="n">
+        <v>0.003657900534899022</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -6281,6 +7255,9 @@
       <c r="D325" t="n">
         <v>0.0002117998826144409</v>
       </c>
+      <c r="E325" t="n">
+        <v>0.003943788046638683</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -6299,6 +7276,9 @@
       <c r="D326" t="n">
         <v>7.06191395801195e-05</v>
       </c>
+      <c r="E326" t="n">
+        <v>0.003305087480199269</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -6317,6 +7297,9 @@
       <c r="D327" t="n">
         <v>0.0002886208307947594</v>
       </c>
+      <c r="E327" t="n">
+        <v>0.004859512266791478</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -6335,6 +7318,9 @@
       <c r="D328" t="n">
         <v>0.0003810742580248419</v>
       </c>
+      <c r="E328" t="n">
+        <v>0.005604747899112549</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -6353,6 +7339,9 @@
       <c r="D329" t="n">
         <v>0.0006608671140877417</v>
       </c>
+      <c r="E329" t="n">
+        <v>0.004477146027893911</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -6371,6 +7360,9 @@
       <c r="D330" t="n">
         <v>0.001387400649128656</v>
       </c>
+      <c r="E330" t="n">
+        <v>0.005477375514307378</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -6389,6 +7381,9 @@
       <c r="D331" t="n">
         <v>0.0004442652767153996</v>
       </c>
+      <c r="E331" t="n">
+        <v>0.004265032692235346</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -6407,6 +7402,9 @@
       <c r="D332" t="n">
         <v>0.0130798796047678</v>
       </c>
+      <c r="E332" t="n">
+        <v>0.006810436719995931</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -6425,6 +7423,9 @@
       <c r="D333" t="n">
         <v>0.01308459565754903</v>
       </c>
+      <c r="E333" t="n">
+        <v>0.006818486261830371</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -6443,6 +7444,9 @@
       <c r="D334" t="n">
         <v>0.0005071569574128188</v>
       </c>
+      <c r="E334" t="n">
+        <v>0.005445324469943222</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -6461,6 +7465,9 @@
       <c r="D335" t="n">
         <v>0.0008755782033674026</v>
       </c>
+      <c r="E335" t="n">
+        <v>0.005535196831689114</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -6479,6 +7486,9 @@
       <c r="D336" t="n">
         <v>0.0008289065634831667</v>
       </c>
+      <c r="E336" t="n">
+        <v>0.005367011119916932</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -6497,6 +7507,9 @@
       <c r="D337" t="n">
         <v>0.0001921958584672636</v>
       </c>
+      <c r="E337" t="n">
+        <v>0.003893772660482941</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -6515,6 +7528,9 @@
       <c r="D338" t="n">
         <v>0.001422237094168873</v>
       </c>
+      <c r="E338" t="n">
+        <v>0.006657132381127129</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -6533,6 +7549,9 @@
       <c r="D339" t="n">
         <v>0.0003891050614627683</v>
       </c>
+      <c r="E339" t="n">
+        <v>0.005059882922721247</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -6551,6 +7570,9 @@
       <c r="D340" t="n">
         <v>0.0002237785445995131</v>
       </c>
+      <c r="E340" t="n">
+        <v>0.004234059394791286</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -6569,6 +7591,9 @@
       <c r="D341" t="n">
         <v>0.001182667106073879</v>
       </c>
+      <c r="E341" t="n">
+        <v>0.005238163345219459</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -6587,6 +7612,9 @@
       <c r="D342" t="n">
         <v>0.0001929915154938179</v>
       </c>
+      <c r="E342" t="n">
+        <v>0.003737794729427438</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -6605,6 +7633,9 @@
       <c r="D343" t="n">
         <v>0.0005554838601609137</v>
       </c>
+      <c r="E343" t="n">
+        <v>0.005152410085066135</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -6623,6 +7654,9 @@
       <c r="D344" t="n">
         <v>0.0005073163682378707</v>
       </c>
+      <c r="E344" t="n">
+        <v>0.005637018634976428</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -6641,6 +7675,9 @@
       <c r="D345" t="n">
         <v>0.0002860556408365083</v>
       </c>
+      <c r="E345" t="n">
+        <v>0.004635079367644429</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -6659,6 +7696,9 @@
       <c r="D346" t="n">
         <v>0.0006694197209799664</v>
       </c>
+      <c r="E346" t="n">
+        <v>0.005714027998444989</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -6677,6 +7717,9 @@
       <c r="D347" t="n">
         <v>0.0003177951395300584</v>
       </c>
+      <c r="E347" t="n">
+        <v>0.004840492113408656</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -6695,6 +7738,9 @@
       <c r="D348" t="n">
         <v>0.0008021354742025032</v>
       </c>
+      <c r="E348" t="n">
+        <v>0.00609921535766634</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -6713,6 +7759,9 @@
       <c r="D349" t="n">
         <v>0.0007869871216230225</v>
       </c>
+      <c r="E349" t="n">
+        <v>0.005735616199925827</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -6731,6 +7780,9 @@
       <c r="D350" t="n">
         <v>0.0002916060572443847</v>
       </c>
+      <c r="E350" t="n">
+        <v>0.004827972110464603</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -6749,6 +7801,9 @@
       <c r="D351" t="n">
         <v>0.01467916777181424</v>
       </c>
+      <c r="E351" t="n">
+        <v>0.007012594659001582</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -6767,6 +7822,9 @@
       <c r="D352" t="n">
         <v>0.01523601670986697</v>
       </c>
+      <c r="E352" t="n">
+        <v>0.007402150824727684</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -6785,6 +7843,9 @@
       <c r="D353" t="n">
         <v>0.007650344504387761</v>
       </c>
+      <c r="E353" t="n">
+        <v>0.007314702207326743</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -6803,6 +7864,9 @@
       <c r="D354" t="n">
         <v>0.000212341990012192</v>
       </c>
+      <c r="E354" t="n">
+        <v>0.004396837541097011</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -6821,6 +7885,9 @@
       <c r="D355" t="n">
         <v>0.0005575422631627162</v>
       </c>
+      <c r="E355" t="n">
+        <v>0.005700564771295315</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -6839,6 +7906,9 @@
       <c r="D356" t="n">
         <v>0.0008018743638299698</v>
       </c>
+      <c r="E356" t="n">
+        <v>0.005974869322068286</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -6857,6 +7927,9 @@
       <c r="D357" t="n">
         <v>0.0003993877974956159</v>
       </c>
+      <c r="E357" t="n">
+        <v>0.004260764289643881</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -6875,6 +7948,9 @@
       <c r="D358" t="n">
         <v>0.0009249688400802186</v>
       </c>
+      <c r="E358" t="n">
+        <v>0.006251302208516758</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -6893,6 +7969,9 @@
       <c r="D359" t="n">
         <v>0.0008328259549717416</v>
       </c>
+      <c r="E359" t="n">
+        <v>0.005746726696122873</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -6911,6 +7990,9 @@
       <c r="D360" t="n">
         <v>0.0001938573203574011</v>
       </c>
+      <c r="E360" t="n">
+        <v>0.003471345982248138</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -6929,6 +8011,9 @@
       <c r="D361" t="n">
         <v>0.0002509434404100856</v>
       </c>
+      <c r="E361" t="n">
+        <v>0.003096460258545793</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -6947,6 +8032,9 @@
       <c r="D362" t="n">
         <v>0.000603747526292076</v>
       </c>
+      <c r="E362" t="n">
+        <v>0.005464943462776204</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -6965,6 +8053,9 @@
       <c r="D363" t="n">
         <v>0.0004771799826811863</v>
       </c>
+      <c r="E363" t="n">
+        <v>0.00503211644263874</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -6983,6 +8074,9 @@
       <c r="D364" t="n">
         <v>0.0005056159412398744</v>
       </c>
+      <c r="E364" t="n">
+        <v>0.005219054819048529</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -7001,6 +8095,9 @@
       <c r="D365" t="n">
         <v>0.0004715615372462221</v>
       </c>
+      <c r="E365" t="n">
+        <v>0.004256764392330379</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -7019,6 +8116,9 @@
       <c r="D366" t="n">
         <v>0.0006366491954839694</v>
       </c>
+      <c r="E366" t="n">
+        <v>0.00597321021053751</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -7037,6 +8137,9 @@
       <c r="D367" t="n">
         <v>0.0001908542278309076</v>
       </c>
+      <c r="E367" t="n">
+        <v>0.003534934481552504</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -7055,6 +8158,9 @@
       <c r="D368" t="n">
         <v>0.0006587563268618694</v>
       </c>
+      <c r="E368" t="n">
+        <v>0.00589524956396882</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -7073,6 +8179,9 @@
       <c r="D369" t="n">
         <v>0.0002055602229511646</v>
       </c>
+      <c r="E369" t="n">
+        <v>0.003555762015688614</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -7091,6 +8200,9 @@
       <c r="D370" t="n">
         <v>0.000677477312689027</v>
       </c>
+      <c r="E370" t="n">
+        <v>0.005330248174722919</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -7109,6 +8221,9 @@
       <c r="D371" t="n">
         <v>0.0004733346409859235</v>
       </c>
+      <c r="E371" t="n">
+        <v>0.004982829998926474</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -7127,6 +8242,9 @@
       <c r="D372" t="n">
         <v>0.0005386119914222459</v>
       </c>
+      <c r="E372" t="n">
+        <v>0.004605968368597829</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -7145,6 +8263,9 @@
       <c r="D373" t="n">
         <v>0.001258281031614762</v>
       </c>
+      <c r="E373" t="n">
+        <v>0.005562249772595093</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -7163,6 +8284,9 @@
       <c r="D374" t="n">
         <v>0.0005203187450986809</v>
       </c>
+      <c r="E374" t="n">
+        <v>0.005687743554034476</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -7181,6 +8305,9 @@
       <c r="D375" t="n">
         <v>0.0005170265048143167</v>
       </c>
+      <c r="E375" t="n">
+        <v>0.005821101843913524</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -7199,6 +8326,9 @@
       <c r="D376" t="n">
         <v>0.0006948367128991969</v>
       </c>
+      <c r="E376" t="n">
+        <v>0.006088933954221189</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -7217,6 +8347,9 @@
       <c r="D377" t="n">
         <v>0.0004523105090805521</v>
       </c>
+      <c r="E377" t="n">
+        <v>0.005245092703312334</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -7235,6 +8368,9 @@
       <c r="D378" t="n">
         <v>0.0007075519126687373</v>
       </c>
+      <c r="E378" t="n">
+        <v>0.005644099500516854</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -7253,6 +8389,9 @@
       <c r="D379" t="n">
         <v>0.0003605831652058866</v>
       </c>
+      <c r="E379" t="n">
+        <v>0.004844368958896282</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -7271,6 +8410,9 @@
       <c r="D380" t="n">
         <v>8.265277113043336e-05</v>
       </c>
+      <c r="E380" t="n">
+        <v>0.0026706293279801</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -7289,6 +8431,9 @@
       <c r="D381" t="n">
         <v>0.0005225973474265889</v>
       </c>
+      <c r="E381" t="n">
+        <v>0.00568850396548282</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -7307,6 +8452,9 @@
       <c r="D382" t="n">
         <v>0.0003889293769379565</v>
       </c>
+      <c r="E382" t="n">
+        <v>0.005167054596188424</v>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -7325,6 +8473,9 @@
       <c r="D383" t="n">
         <v>0.0001533449650444442</v>
       </c>
+      <c r="E383" t="n">
+        <v>0.003739299627922853</v>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -7343,6 +8494,9 @@
       <c r="D384" t="n">
         <v>0.0008701931419139943</v>
       </c>
+      <c r="E384" t="n">
+        <v>0.004803417515029711</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -7361,6 +8515,9 @@
       <c r="D385" t="n">
         <v>0.0001228913318194459</v>
       </c>
+      <c r="E385" t="n">
+        <v>0.002633795226438657</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -7379,6 +8536,9 @@
       <c r="D386" t="n">
         <v>0.01975505944792119</v>
       </c>
+      <c r="E386" t="n">
+        <v>0.00689566095462664</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -7397,6 +8557,9 @@
       <c r="D387" t="n">
         <v>0.01951228824558588</v>
       </c>
+      <c r="E387" t="n">
+        <v>0.006756575659916905</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -7415,6 +8578,9 @@
       <c r="D388" t="n">
         <v>0.0001902752778429295</v>
       </c>
+      <c r="E388" t="n">
+        <v>0.004259521127963326</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -7433,6 +8599,9 @@
       <c r="D389" t="n">
         <v>0.0001634480202102617</v>
       </c>
+      <c r="E389" t="n">
+        <v>0.004153520389036004</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -7451,6 +8620,9 @@
       <c r="D390" t="n">
         <v>0.0009827081960921155</v>
       </c>
+      <c r="E390" t="n">
+        <v>0.006094440843671425</v>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -7469,6 +8641,9 @@
       <c r="D391" t="n">
         <v>0.0006257925664263574</v>
       </c>
+      <c r="E391" t="n">
+        <v>0.005261758948618986</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -7487,6 +8662,9 @@
       <c r="D392" t="n">
         <v>0.0009569969261629258</v>
       </c>
+      <c r="E392" t="n">
+        <v>0.006009513820682243</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -7505,6 +8683,9 @@
       <c r="D393" t="n">
         <v>0.001520247938472491</v>
       </c>
+      <c r="E393" t="n">
+        <v>0.00613923781475952</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -7523,6 +8704,9 @@
       <c r="D394" t="n">
         <v>0.0003574271734632872</v>
       </c>
+      <c r="E394" t="n">
+        <v>0.005411601709553224</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -7541,6 +8725,9 @@
       <c r="D395" t="n">
         <v>0.000403954776844521</v>
       </c>
+      <c r="E395" t="n">
+        <v>0.005331049289702058</v>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -7559,6 +8746,9 @@
       <c r="D396" t="n">
         <v>0.0006249531638640632</v>
       </c>
+      <c r="E396" t="n">
+        <v>0.005580339139560106</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -7577,6 +8767,9 @@
       <c r="D397" t="n">
         <v>0.0004699491656686247</v>
       </c>
+      <c r="E397" t="n">
+        <v>0.005612309219199498</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -7595,6 +8788,9 @@
       <c r="D398" t="n">
         <v>0.0004886134434347696</v>
       </c>
+      <c r="E398" t="n">
+        <v>0.006044447057044828</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -7613,6 +8809,9 @@
       <c r="D399" t="n">
         <v>0.000472223199469297</v>
       </c>
+      <c r="E399" t="n">
+        <v>0.005445590774778008</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -7631,6 +8830,9 @@
       <c r="D400" t="n">
         <v>0.0003158604362784262</v>
       </c>
+      <c r="E400" t="n">
+        <v>0.004720389638787017</v>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -7649,6 +8851,9 @@
       <c r="D401" t="n">
         <v>0.001136241207498042</v>
       </c>
+      <c r="E401" t="n">
+        <v>0.006381030838792414</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -7667,6 +8872,9 @@
       <c r="D402" t="n">
         <v>0.000497302836024632</v>
       </c>
+      <c r="E402" t="n">
+        <v>0.005565866979487985</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -7685,6 +8893,9 @@
       <c r="D403" t="n">
         <v>0.00100386499088313</v>
       </c>
+      <c r="E403" t="n">
+        <v>0.005175030589758116</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -7703,6 +8914,9 @@
       <c r="D404" t="n">
         <v>0.0004702574442004776</v>
       </c>
+      <c r="E404" t="n">
+        <v>0.005572386625193593</v>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -7721,6 +8935,9 @@
       <c r="D405" t="n">
         <v>0.0005190861595440067</v>
       </c>
+      <c r="E405" t="n">
+        <v>0.005391251124594347</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -7739,6 +8956,9 @@
       <c r="D406" t="n">
         <v>0.0007649101049933053</v>
       </c>
+      <c r="E406" t="n">
+        <v>0.005010623932330628</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -7757,6 +8977,9 @@
       <c r="D407" t="n">
         <v>0.001029511833325045</v>
       </c>
+      <c r="E407" t="n">
+        <v>0.006137744744319659</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -7775,6 +8998,9 @@
       <c r="D408" t="n">
         <v>0.000639962245258962</v>
       </c>
+      <c r="E408" t="n">
+        <v>0.005518108412808613</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -7793,6 +9019,9 @@
       <c r="D409" t="n">
         <v>0.0007071010775730184</v>
       </c>
+      <c r="E409" t="n">
+        <v>0.005283579404711025</v>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -7811,6 +9040,9 @@
       <c r="D410" t="n">
         <v>0.0008033563323299056</v>
       </c>
+      <c r="E410" t="n">
+        <v>0.005758570140979447</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -7829,6 +9061,9 @@
       <c r="D411" t="n">
         <v>0.0006839777149279963</v>
       </c>
+      <c r="E411" t="n">
+        <v>0.005805110760378525</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -7847,6 +9082,9 @@
       <c r="D412" t="n">
         <v>0.0002670618163000044</v>
       </c>
+      <c r="E412" t="n">
+        <v>0.004204341420137868</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -7865,6 +9103,9 @@
       <c r="D413" t="n">
         <v>0.0009230921380055503</v>
       </c>
+      <c r="E413" t="n">
+        <v>0.00592446917184974</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -7883,6 +9124,9 @@
       <c r="D414" t="n">
         <v>0.000255367358449476</v>
       </c>
+      <c r="E414" t="n">
+        <v>0.004964429011624074</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -7901,6 +9145,9 @@
       <c r="D415" t="n">
         <v>0.0003545285254810125</v>
       </c>
+      <c r="E415" t="n">
+        <v>0.004775350447004586</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -7919,6 +9166,9 @@
       <c r="D416" t="n">
         <v>0.0001752681658586191</v>
       </c>
+      <c r="E416" t="n">
+        <v>0.003925205702224708</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -7937,6 +9187,9 @@
       <c r="D417" t="n">
         <v>0.0006752361456439197</v>
       </c>
+      <c r="E417" t="n">
+        <v>0.005866558377440387</v>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -7955,6 +9208,9 @@
       <c r="D418" t="n">
         <v>0.0007326220283284666</v>
       </c>
+      <c r="E418" t="n">
+        <v>0.0059653821773964</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -7973,6 +9229,9 @@
       <c r="D419" t="n">
         <v>0.000583402015123648</v>
       </c>
+      <c r="E419" t="n">
+        <v>0.005590423081199575</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -7991,6 +9250,9 @@
       <c r="D420" t="n">
         <v>0.0003241689715134795</v>
       </c>
+      <c r="E420" t="n">
+        <v>0.003999736329042759</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -8009,6 +9271,9 @@
       <c r="D421" t="n">
         <v>0.001249755756059217</v>
       </c>
+      <c r="E421" t="n">
+        <v>0.006589409781166915</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -8027,6 +9292,9 @@
       <c r="D422" t="n">
         <v>0.0006121611777987891</v>
       </c>
+      <c r="E422" t="n">
+        <v>0.005839190760083539</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -8045,6 +9313,9 @@
       <c r="D423" t="n">
         <v>0.0004422649369088815</v>
       </c>
+      <c r="E423" t="n">
+        <v>0.005170068998126828</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -8063,6 +9334,9 @@
       <c r="D424" t="n">
         <v>0.0008516063857579344</v>
       </c>
+      <c r="E424" t="n">
+        <v>0.0055939825146129</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -8081,6 +9355,9 @@
       <c r="D425" t="n">
         <v>0.0003088185558040342</v>
       </c>
+      <c r="E425" t="n">
+        <v>0.004431172582183899</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -8099,6 +9376,9 @@
       <c r="D426" t="n">
         <v>0.0008989216425591068</v>
       </c>
+      <c r="E426" t="n">
+        <v>0.005102835211071846</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -8117,6 +9397,9 @@
       <c r="D427" t="n">
         <v>0.0004194564393051885</v>
       </c>
+      <c r="E427" t="n">
+        <v>0.004474502495213309</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -8135,6 +9418,9 @@
       <c r="D428" t="n">
         <v>0.0001343328373902252</v>
       </c>
+      <c r="E428" t="n">
+        <v>0.003555378015081413</v>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -8153,6 +9439,9 @@
       <c r="D429" t="n">
         <v>0.0002490759634614167</v>
       </c>
+      <c r="E429" t="n">
+        <v>0.004861907781046872</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -8171,6 +9460,9 @@
       <c r="D430" t="n">
         <v>0.0001103085128885213</v>
       </c>
+      <c r="E430" t="n">
+        <v>0.003277520760485448</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -8189,6 +9481,9 @@
       <c r="D431" t="n">
         <v>0.0005476039741122874</v>
       </c>
+      <c r="E431" t="n">
+        <v>0.004965662987078902</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -8207,6 +9502,9 @@
       <c r="D432" t="n">
         <v>0.000191083754631013</v>
       </c>
+      <c r="E432" t="n">
+        <v>0.003374004345075537</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -8225,6 +9523,9 @@
       <c r="D433" t="n">
         <v>0.0006421143134827664</v>
       </c>
+      <c r="E433" t="n">
+        <v>0.004832282559931842</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -8243,6 +9544,9 @@
       <c r="D434" t="n">
         <v>0.00014038401959563</v>
       </c>
+      <c r="E434" t="n">
+        <v>0.003861712888428563</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -8261,6 +9565,9 @@
       <c r="D435" t="n">
         <v>0.0001712685836940308</v>
       </c>
+      <c r="E435" t="n">
+        <v>0.003827518545399651</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -8279,6 +9586,9 @@
       <c r="D436" t="n">
         <v>0.001270022760603401</v>
       </c>
+      <c r="E436" t="n">
+        <v>0.005918793995994689</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -8297,6 +9607,9 @@
       <c r="D437" t="n">
         <v>0.0007015898548679001</v>
       </c>
+      <c r="E437" t="n">
+        <v>0.005055587338784063</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -8315,6 +9628,9 @@
       <c r="D438" t="n">
         <v>0.0002313963497449509</v>
       </c>
+      <c r="E438" t="n">
+        <v>0.003960313690396232</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -8333,6 +9649,9 @@
       <c r="D439" t="n">
         <v>0.0008569099696503811</v>
       </c>
+      <c r="E439" t="n">
+        <v>0.00630979678082535</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -8351,6 +9670,9 @@
       <c r="D440" t="n">
         <v>0.002532387314541318</v>
       </c>
+      <c r="E440" t="n">
+        <v>0.006475355319937647</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -8369,6 +9691,9 @@
       <c r="D441" t="n">
         <v>0.001086264519445011</v>
       </c>
+      <c r="E441" t="n">
+        <v>0.004847558787075807</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -8387,6 +9712,9 @@
       <c r="D442" t="n">
         <v>0.001910965213781301</v>
       </c>
+      <c r="E442" t="n">
+        <v>0.006340990241801453</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -8405,6 +9733,9 @@
       <c r="D443" t="n">
         <v>0.0002790753751715541</v>
       </c>
+      <c r="E443" t="n">
+        <v>0.004125079294388246</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -8423,6 +9754,9 @@
       <c r="D444" t="n">
         <v>0.0002622186705165203</v>
       </c>
+      <c r="E444" t="n">
+        <v>0.004458623014841804</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -8441,6 +9775,9 @@
       <c r="D445" t="n">
         <v>0.001087173587523177</v>
       </c>
+      <c r="E445" t="n">
+        <v>0.006235116844919624</v>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -8459,6 +9796,9 @@
       <c r="D446" t="n">
         <v>0.0008749279790148788</v>
       </c>
+      <c r="E446" t="n">
+        <v>0.004602503018194864</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -8477,6 +9817,9 @@
       <c r="D447" t="n">
         <v>0.000709628233054818</v>
       </c>
+      <c r="E447" t="n">
+        <v>0.005014801899597575</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -8495,6 +9838,9 @@
       <c r="D448" t="n">
         <v>0.0003617367367802704</v>
       </c>
+      <c r="E448" t="n">
+        <v>0.004757605476535787</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -8513,6 +9859,9 @@
       <c r="D449" t="n">
         <v>0.00017895096821584</v>
       </c>
+      <c r="E449" t="n">
+        <v>0.00429762215045697</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -8531,6 +9880,9 @@
       <c r="D450" t="n">
         <v>0.0007853118528464218</v>
       </c>
+      <c r="E450" t="n">
+        <v>0.00475716942009083</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -8549,6 +9901,9 @@
       <c r="D451" t="n">
         <v>0.001020532168698162</v>
       </c>
+      <c r="E451" t="n">
+        <v>0.005911555638440742</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -8567,6 +9922,9 @@
       <c r="D452" t="n">
         <v>0.007430116825084325</v>
       </c>
+      <c r="E452" t="n">
+        <v>0.007151691423879511</v>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -8585,6 +9943,9 @@
       <c r="D453" t="n">
         <v>0.0002581943483278331</v>
       </c>
+      <c r="E453" t="n">
+        <v>0.00495373066541729</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -8603,6 +9964,9 @@
       <c r="D454" t="n">
         <v>0.000223401188711108</v>
       </c>
+      <c r="E454" t="n">
+        <v>0.002943371018743193</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -8621,6 +9985,9 @@
       <c r="D455" t="n">
         <v>0.00125096731216226</v>
       </c>
+      <c r="E455" t="n">
+        <v>0.003453667563250198</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -8639,6 +10006,9 @@
       <c r="D456" t="n">
         <v>0.001273921281531663</v>
       </c>
+      <c r="E456" t="n">
+        <v>0.003567748370436596</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -8657,6 +10027,9 @@
       <c r="D457" t="n">
         <v>0.0007321908465458268</v>
       </c>
+      <c r="E457" t="n">
+        <v>0.0048390922137139</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -8675,6 +10048,9 @@
       <c r="D458" t="n">
         <v>0.0002436488472477019</v>
       </c>
+      <c r="E458" t="n">
+        <v>0.004375932264248334</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -8693,6 +10069,9 @@
       <c r="D459" t="n">
         <v>0.0001079026556507153</v>
       </c>
+      <c r="E459" t="n">
+        <v>0.003025206958344371</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -8711,6 +10090,9 @@
       <c r="D460" t="n">
         <v>0.001095655564685122</v>
       </c>
+      <c r="E460" t="n">
+        <v>0.006032681080523657</v>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -8729,6 +10111,9 @@
       <c r="D461" t="n">
         <v>0.0007521502377554763</v>
       </c>
+      <c r="E461" t="n">
+        <v>0.005302818691994123</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -8747,6 +10132,9 @@
       <c r="D462" t="n">
         <v>0.0003417367722850525</v>
       </c>
+      <c r="E462" t="n">
+        <v>0.00480162406716418</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -8765,6 +10153,9 @@
       <c r="D463" t="n">
         <v>0.0008017555916276193</v>
       </c>
+      <c r="E463" t="n">
+        <v>0.005621245972675986</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -8783,6 +10174,9 @@
       <c r="D464" t="n">
         <v>0.001179657596816032</v>
       </c>
+      <c r="E464" t="n">
+        <v>0.005708624694178961</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -8801,6 +10195,9 @@
       <c r="D465" t="n">
         <v>0.0006884263264168563</v>
       </c>
+      <c r="E465" t="n">
+        <v>0.005225039869678267</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -8819,6 +10216,9 @@
       <c r="D466" t="n">
         <v>0.0006445684637113781</v>
       </c>
+      <c r="E466" t="n">
+        <v>0.005894843546023718</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -8837,6 +10237,9 @@
       <c r="D467" t="n">
         <v>0.0002498772797080249</v>
       </c>
+      <c r="E467" t="n">
+        <v>0.004841818579097805</v>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -8855,6 +10258,9 @@
       <c r="D468" t="n">
         <v>0.0004041698329482804</v>
       </c>
+      <c r="E468" t="n">
+        <v>0.005111531241509819</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -8873,6 +10279,9 @@
       <c r="D469" t="n">
         <v>0.0003077990804131952</v>
       </c>
+      <c r="E469" t="n">
+        <v>0.005094265059532965</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -8891,6 +10300,9 @@
       <c r="D470" t="n">
         <v>0.0004816975622596887</v>
       </c>
+      <c r="E470" t="n">
+        <v>0.003957074679222254</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -8909,6 +10321,9 @@
       <c r="D471" t="n">
         <v>0.0006331220595205163</v>
       </c>
+      <c r="E471" t="n">
+        <v>0.005600163097482406</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -8927,6 +10342,9 @@
       <c r="D472" t="n">
         <v>0.0007039341996270609</v>
       </c>
+      <c r="E472" t="n">
+        <v>0.004388769150882503</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -8945,6 +10363,9 @@
       <c r="D473" t="n">
         <v>0.0005371372267570088</v>
       </c>
+      <c r="E473" t="n">
+        <v>0.004710106544323064</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -8963,6 +10384,9 @@
       <c r="D474" t="n">
         <v>0.0001919859275444395</v>
       </c>
+      <c r="E474" t="n">
+        <v>0.003967969731343598</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -8981,6 +10405,9 @@
       <c r="D475" t="n">
         <v>0.0006936447515280464</v>
       </c>
+      <c r="E475" t="n">
+        <v>0.005162042571177849</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -8999,6 +10426,9 @@
       <c r="D476" t="n">
         <v>0.0008393962377693991</v>
       </c>
+      <c r="E476" t="n">
+        <v>0.006074732958187788</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -9017,6 +10447,9 @@
       <c r="D477" t="n">
         <v>0.0006223068635283224</v>
       </c>
+      <c r="E477" t="n">
+        <v>0.005839732055267191</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -9035,6 +10468,9 @@
       <c r="D478" t="n">
         <v>0.0002528099925165013</v>
       </c>
+      <c r="E478" t="n">
+        <v>0.004501808656533491</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -9053,6 +10489,9 @@
       <c r="D479" t="n">
         <v>0.001285901914340964</v>
       </c>
+      <c r="E479" t="n">
+        <v>0.006622862490369359</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -9071,6 +10510,9 @@
       <c r="D480" t="n">
         <v>0.0002531930291208681</v>
       </c>
+      <c r="E480" t="n">
+        <v>0.004595264743068437</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -9089,6 +10531,9 @@
       <c r="D481" t="n">
         <v>0.0006012030395692363</v>
       </c>
+      <c r="E481" t="n">
+        <v>0.005769229527052919</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -9107,6 +10552,9 @@
       <c r="D482" t="n">
         <v>0.0001496325882752563</v>
       </c>
+      <c r="E482" t="n">
+        <v>0.003602917895644172</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -9125,6 +10573,9 @@
       <c r="D483" t="n">
         <v>0.00217893087424096</v>
       </c>
+      <c r="E483" t="n">
+        <v>0.006789581030984802</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -9143,6 +10594,9 @@
       <c r="D484" t="n">
         <v>0.002108694472757994</v>
       </c>
+      <c r="E484" t="n">
+        <v>0.006720064733328658</v>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -9161,6 +10615,9 @@
       <c r="D485" t="n">
         <v>0.001273203847864072</v>
       </c>
+      <c r="E485" t="n">
+        <v>0.006538806660858137</v>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -9179,6 +10636,9 @@
       <c r="D486" t="n">
         <v>0.0003099165168648085</v>
       </c>
+      <c r="E486" t="n">
+        <v>0.003800480716455717</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -9197,6 +10657,9 @@
       <c r="D487" t="n">
         <v>0.001046667557474259</v>
       </c>
+      <c r="E487" t="n">
+        <v>0.005492126135896274</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -9215,6 +10678,9 @@
       <c r="D488" t="n">
         <v>0.0006970302321951783</v>
       </c>
+      <c r="E488" t="n">
+        <v>0.004913415074084537</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -9233,6 +10699,9 @@
       <c r="D489" t="n">
         <v>0.0009007588229161686</v>
       </c>
+      <c r="E489" t="n">
+        <v>0.005430336230175769</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -9251,6 +10720,9 @@
       <c r="D490" t="n">
         <v>0.0001212161624888032</v>
       </c>
+      <c r="E490" t="n">
+        <v>0.002879280961633733</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -9269,6 +10741,9 @@
       <c r="D491" t="n">
         <v>0.01672083907769844</v>
       </c>
+      <c r="E491" t="n">
+        <v>0.007712404071105673</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -9287,6 +10762,9 @@
       <c r="D492" t="n">
         <v>0.001235938778018411</v>
       </c>
+      <c r="E492" t="n">
+        <v>0.005901200952537169</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -9305,6 +10783,9 @@
       <c r="D493" t="n">
         <v>0.0007946145230077746</v>
       </c>
+      <c r="E493" t="n">
+        <v>0.005356052406721166</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -9323,6 +10804,9 @@
       <c r="D494" t="n">
         <v>0.0008511651324362332</v>
       </c>
+      <c r="E494" t="n">
+        <v>0.005456713107177455</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -9341,6 +10825,9 @@
       <c r="D495" t="n">
         <v>0.0009903559788987128</v>
       </c>
+      <c r="E495" t="n">
+        <v>0.005799246719251065</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -9359,6 +10846,9 @@
       <c r="D496" t="n">
         <v>4.004505509889483e-07</v>
       </c>
+      <c r="E496" t="n">
+        <v>0.0004420650851949846</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -9377,6 +10867,9 @@
       <c r="D497" t="n">
         <v>6.991669427784588e-07</v>
       </c>
+      <c r="E497" t="n">
+        <v>0.0004986641415542902</v>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -9395,6 +10888,9 @@
       <c r="D498" t="n">
         <v>1.809319523670461e-06</v>
       </c>
+      <c r="E498" t="n">
+        <v>0.0006403291083923324</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -9413,6 +10909,9 @@
       <c r="D499" t="n">
         <v>1.01101888109062e-06</v>
       </c>
+      <c r="E499" t="n">
+        <v>0.0006493376398557493</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -9431,6 +10930,9 @@
       <c r="D500" t="n">
         <v>9.726093156109545e-07</v>
       </c>
+      <c r="E500" t="n">
+        <v>0.0006015749282412745</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -9449,6 +10951,9 @@
       <c r="D501" t="n">
         <v>7.384808851357297e-07</v>
       </c>
+      <c r="E501" t="n">
+        <v>0.0005836421556877448</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -9467,6 +10972,9 @@
       <c r="D502" t="n">
         <v>1.815136550832254e-06</v>
       </c>
+      <c r="E502" t="n">
+        <v>0.000638291310593703</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -9485,6 +10993,9 @@
       <c r="D503" t="n">
         <v>8.147800263607307e-07</v>
       </c>
+      <c r="E503" t="n">
+        <v>0.0006177076902893538</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -9503,6 +11014,9 @@
       <c r="D504" t="n">
         <v>2.602731301948068e-06</v>
       </c>
+      <c r="E504" t="n">
+        <v>0.0007232682003385251</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -9521,6 +11035,9 @@
       <c r="D505" t="n">
         <v>3.754811849295124e-07</v>
       </c>
+      <c r="E505" t="n">
+        <v>0.000414580934952227</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -9539,6 +11056,9 @@
       <c r="D506" t="n">
         <v>1.476725967003604e-07</v>
       </c>
+      <c r="E506" t="n">
+        <v>0.000317182947517043</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -9557,6 +11077,9 @@
       <c r="D507" t="n">
         <v>1.816233091810327e-06</v>
       </c>
+      <c r="E507" t="n">
+        <v>0.0006743430273642813</v>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -9575,6 +11098,9 @@
       <c r="D508" t="n">
         <v>1.033649231359548e-06</v>
       </c>
+      <c r="E508" t="n">
+        <v>0.0006158296680252172</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -9593,6 +11119,9 @@
       <c r="D509" t="n">
         <v>9.811451437851091e-07</v>
       </c>
+      <c r="E509" t="n">
+        <v>0.0006033237990769868</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -9611,6 +11140,9 @@
       <c r="D510" t="n">
         <v>1.191714113192325e-06</v>
       </c>
+      <c r="E510" t="n">
+        <v>0.0006694389628454004</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -9629,6 +11161,9 @@
       <c r="D511" t="n">
         <v>2.680790053561937e-06</v>
       </c>
+      <c r="E511" t="n">
+        <v>0.0007802286702902619</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -9647,6 +11182,9 @@
       <c r="D512" t="n">
         <v>1.49913306424037e-06</v>
       </c>
+      <c r="E512" t="n">
+        <v>0.0005916282165933562</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -9665,6 +11203,9 @@
       <c r="D513" t="n">
         <v>8.516798766269656e-07</v>
       </c>
+      <c r="E513" t="n">
+        <v>0.0006045898807407096</v>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -9683,6 +11224,9 @@
       <c r="D514" t="n">
         <v>1.4205965563934e-06</v>
       </c>
+      <c r="E514" t="n">
+        <v>0.0005421742854388116</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -9701,6 +11245,9 @@
       <c r="D515" t="n">
         <v>3.141392430568677e-06</v>
       </c>
+      <c r="E515" t="n">
+        <v>0.0007044456015764035</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -9719,6 +11266,9 @@
       <c r="D516" t="n">
         <v>1.011459781867838e-06</v>
       </c>
+      <c r="E516" t="n">
+        <v>0.0005832298973790375</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -9737,6 +11287,9 @@
       <c r="D517" t="n">
         <v>1.265712325030979e-06</v>
       </c>
+      <c r="E517" t="n">
+        <v>0.0007176247217460078</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -9755,6 +11308,9 @@
       <c r="D518" t="n">
         <v>1.61739904017605e-06</v>
       </c>
+      <c r="E518" t="n">
+        <v>0.0007025750574206009</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -9773,6 +11329,9 @@
       <c r="D519" t="n">
         <v>1.594626149791684e-06</v>
       </c>
+      <c r="E519" t="n">
+        <v>0.0006288150673342978</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -9791,6 +11350,9 @@
       <c r="D520" t="n">
         <v>1.244464127674797e-06</v>
       </c>
+      <c r="E520" t="n">
+        <v>0.0007002098386399395</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -9809,6 +11371,9 @@
       <c r="D521" t="n">
         <v>2.047149174139291e-06</v>
       </c>
+      <c r="E521" t="n">
+        <v>0.0006132652405759244</v>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
@@ -9827,6 +11392,9 @@
       <c r="D522" t="n">
         <v>9.208747345038145e-07</v>
       </c>
+      <c r="E522" t="n">
+        <v>0.0005232327210670607</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -9845,6 +11413,9 @@
       <c r="D523" t="n">
         <v>1.800386777130591e-05</v>
       </c>
+      <c r="E523" t="n">
+        <v>0.0008923004637561898</v>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -9863,6 +11434,9 @@
       <c r="D524" t="n">
         <v>3.046285641451778e-06</v>
       </c>
+      <c r="E524" t="n">
+        <v>0.0007613053082680187</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -9881,6 +11455,9 @@
       <c r="D525" t="n">
         <v>1.32330955860958e-06</v>
       </c>
+      <c r="E525" t="n">
+        <v>0.0006849954598029368</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -9899,6 +11476,9 @@
       <c r="D526" t="n">
         <v>1.562631908686012e-06</v>
       </c>
+      <c r="E526" t="n">
+        <v>0.0006193037107847044</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -9917,6 +11497,9 @@
       <c r="D527" t="n">
         <v>1.340695171883213e-06</v>
       </c>
+      <c r="E527" t="n">
+        <v>0.0005591339457766944</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -9935,6 +11518,9 @@
       <c r="D528" t="n">
         <v>1.995717696208877e-06</v>
       </c>
+      <c r="E528" t="n">
+        <v>0.0005562901953701689</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -9953,6 +11539,9 @@
       <c r="D529" t="n">
         <v>9.585402999990681e-07</v>
       </c>
+      <c r="E529" t="n">
+        <v>0.0006610333655808375</v>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -9971,6 +11560,9 @@
       <c r="D530" t="n">
         <v>1.109456912386409e-06</v>
       </c>
+      <c r="E530" t="n">
+        <v>0.0006231856873492574</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -9989,6 +11581,9 @@
       <c r="D531" t="n">
         <v>1.026472021325146e-06</v>
       </c>
+      <c r="E531" t="n">
+        <v>0.0005835305330462864</v>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -10007,6 +11602,9 @@
       <c r="D532" t="n">
         <v>4.27459401843453e-07</v>
       </c>
+      <c r="E532" t="n">
+        <v>0.0004866432176399521</v>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -10025,6 +11623,9 @@
       <c r="D533" t="n">
         <v>1.893210972539764e-06</v>
       </c>
+      <c r="E533" t="n">
+        <v>0.0006749395520084122</v>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -10043,6 +11644,9 @@
       <c r="D534" t="n">
         <v>3.958263065600109e-07</v>
       </c>
+      <c r="E534" t="n">
+        <v>0.0005265492201127387</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -10061,6 +11665,9 @@
       <c r="D535" t="n">
         <v>5.926575930174339e-07</v>
       </c>
+      <c r="E535" t="n">
+        <v>0.0005832186813310263</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -10079,6 +11686,9 @@
       <c r="D536" t="n">
         <v>1.883832329597343e-07</v>
       </c>
+      <c r="E536" t="n">
+        <v>0.0003208781337884773</v>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -10097,6 +11707,9 @@
       <c r="D537" t="n">
         <v>1.829113693371541e-06</v>
       </c>
+      <c r="E537" t="n">
+        <v>0.0006847897200825459</v>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -10115,6 +11728,9 @@
       <c r="D538" t="n">
         <v>9.400735321700585e-07</v>
       </c>
+      <c r="E538" t="n">
+        <v>0.0006567696396822965</v>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -10133,6 +11749,9 @@
       <c r="D539" t="n">
         <v>4.133027929328777e-06</v>
       </c>
+      <c r="E539" t="n">
+        <v>0.0007704469398817117</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -10151,6 +11770,9 @@
       <c r="D540" t="n">
         <v>1.811522250985547e-06</v>
       </c>
+      <c r="E540" t="n">
+        <v>0.0006703025268186097</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -10169,6 +11791,9 @@
       <c r="D541" t="n">
         <v>1.217384388944285e-06</v>
       </c>
+      <c r="E541" t="n">
+        <v>0.0006499109273064198</v>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
@@ -10187,6 +11812,9 @@
       <c r="D542" t="n">
         <v>3.832861617743426e-06</v>
       </c>
+      <c r="E542" t="n">
+        <v>0.0006810135056489959</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -10205,6 +11833,9 @@
       <c r="D543" t="n">
         <v>4.695576663207372e-07</v>
       </c>
+      <c r="E543" t="n">
+        <v>0.0004829487140965973</v>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -10223,6 +11854,9 @@
       <c r="D544" t="n">
         <v>2.473090464279591e-06</v>
       </c>
+      <c r="E544" t="n">
+        <v>0.0006794815147323933</v>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -10241,6 +11875,9 @@
       <c r="D545" t="n">
         <v>2.514252900972712e-06</v>
       </c>
+      <c r="E545" t="n">
+        <v>0.0006920095422884897</v>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -10259,6 +11896,9 @@
       <c r="D546" t="n">
         <v>1.17958467208628e-06</v>
       </c>
+      <c r="E546" t="n">
+        <v>0.0006470235848458918</v>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -10277,6 +11917,9 @@
       <c r="D547" t="n">
         <v>2.131744475081769e-07</v>
       </c>
+      <c r="E547" t="n">
+        <v>0.0004864589950853067</v>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -10295,6 +11938,9 @@
       <c r="D548" t="n">
         <v>6.537235421171823e-07</v>
       </c>
+      <c r="E548" t="n">
+        <v>0.0004617479985002741</v>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -10313,6 +11959,9 @@
       <c r="D549" t="n">
         <v>1.251562541426017e-06</v>
       </c>
+      <c r="E549" t="n">
+        <v>0.0006341617200981855</v>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -10331,6 +11980,9 @@
       <c r="D550" t="n">
         <v>1.956632609965177e-06</v>
       </c>
+      <c r="E550" t="n">
+        <v>0.0006613326584558226</v>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -10349,6 +12001,9 @@
       <c r="D551" t="n">
         <v>4.90782064124651e-07</v>
       </c>
+      <c r="E551" t="n">
+        <v>0.0004918499420682077</v>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
@@ -10367,6 +12022,9 @@
       <c r="D552" t="n">
         <v>6.157983641588466e-07</v>
       </c>
+      <c r="E552" t="n">
+        <v>0.0006245220505577281</v>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -10385,6 +12043,9 @@
       <c r="D553" t="n">
         <v>8.409365313735029e-07</v>
       </c>
+      <c r="E553" t="n">
+        <v>0.000682204517822094</v>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
@@ -10403,6 +12064,9 @@
       <c r="D554" t="n">
         <v>3.009895263135713e-06</v>
       </c>
+      <c r="E554" t="n">
+        <v>0.0007117122951111342</v>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
@@ -10421,6 +12085,9 @@
       <c r="D555" t="n">
         <v>2.149892527821531e-06</v>
       </c>
+      <c r="E555" t="n">
+        <v>0.0007367997844332595</v>
+      </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
@@ -10439,6 +12106,9 @@
       <c r="D556" t="n">
         <v>1.937817266414105e-06</v>
       </c>
+      <c r="E556" t="n">
+        <v>0.000675623227802576</v>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
@@ -10457,6 +12127,9 @@
       <c r="D557" t="n">
         <v>1.533834118564021e-06</v>
       </c>
+      <c r="E557" t="n">
+        <v>0.0006313282117531919</v>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
@@ -10475,6 +12148,9 @@
       <c r="D558" t="n">
         <v>1.474469219735966e-06</v>
       </c>
+      <c r="E558" t="n">
+        <v>0.0007255197672017526</v>
+      </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
@@ -10493,6 +12169,9 @@
       <c r="D559" t="n">
         <v>7.329849957308769e-07</v>
       </c>
+      <c r="E559" t="n">
+        <v>0.0006222373616250274</v>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
@@ -10511,6 +12190,9 @@
       <c r="D560" t="n">
         <v>1.409422361423772e-06</v>
       </c>
+      <c r="E560" t="n">
+        <v>0.000643648963158489</v>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -10529,6 +12211,9 @@
       <c r="D561" t="n">
         <v>6.171305096940548e-07</v>
       </c>
+      <c r="E561" t="n">
+        <v>0.0004553499813277047</v>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -10547,6 +12232,9 @@
       <c r="D562" t="n">
         <v>8.437778870584247e-06</v>
       </c>
+      <c r="E562" t="n">
+        <v>0.000783407733940444</v>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -10565,6 +12253,9 @@
       <c r="D563" t="n">
         <v>5.717546012547775e-07</v>
       </c>
+      <c r="E563" t="n">
+        <v>0.0005035068512081662</v>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -10583,6 +12274,9 @@
       <c r="D564" t="n">
         <v>1.478420377751252e-06</v>
       </c>
+      <c r="E564" t="n">
+        <v>0.0007263748828935426</v>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -10601,6 +12295,9 @@
       <c r="D565" t="n">
         <v>7.316372489262372e-07</v>
       </c>
+      <c r="E565" t="n">
+        <v>0.0005697239142832948</v>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
@@ -10619,6 +12316,9 @@
       <c r="D566" t="n">
         <v>5.015442145119313e-07</v>
       </c>
+      <c r="E566" t="n">
+        <v>0.00055221768081488</v>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
@@ -10637,6 +12337,9 @@
       <c r="D567" t="n">
         <v>1.460717532055256e-06</v>
       </c>
+      <c r="E567" t="n">
+        <v>0.0007126010642050339</v>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
@@ -10655,6 +12358,9 @@
       <c r="D568" t="n">
         <v>1.54994364427231e-06</v>
       </c>
+      <c r="E568" t="n">
+        <v>0.0007325611260793426</v>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
@@ -10673,6 +12379,9 @@
       <c r="D569" t="n">
         <v>8.933763736447659e-07</v>
       </c>
+      <c r="E569" t="n">
+        <v>0.000661777725656915</v>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -10691,6 +12400,9 @@
       <c r="D570" t="n">
         <v>1.647415300388146e-06</v>
       </c>
+      <c r="E570" t="n">
+        <v>0.0005367067352049193</v>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -10709,6 +12421,9 @@
       <c r="D571" t="n">
         <v>2.979462372953331e-07</v>
       </c>
+      <c r="E571" t="n">
+        <v>0.0004030638560671585</v>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -10727,6 +12442,9 @@
       <c r="D572" t="n">
         <v>3.446800042988449e-07</v>
       </c>
+      <c r="E572" t="n">
+        <v>0.0004675410622300316</v>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -10745,6 +12463,9 @@
       <c r="D573" t="n">
         <v>2.455445208604412e-07</v>
       </c>
+      <c r="E573" t="n">
+        <v>0.0004283589652017366</v>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -10763,6 +12484,9 @@
       <c r="D574" t="n">
         <v>6.202652973212326e-07</v>
       </c>
+      <c r="E574" t="n">
+        <v>0.0005804215246570346</v>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -10781,6 +12505,9 @@
       <c r="D575" t="n">
         <v>1.035990329167189e-06</v>
       </c>
+      <c r="E575" t="n">
+        <v>0.0006884911945437299</v>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
@@ -10799,6 +12526,9 @@
       <c r="D576" t="n">
         <v>1.408888178727042e-06</v>
       </c>
+      <c r="E576" t="n">
+        <v>0.0005534775352102443</v>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -10817,6 +12547,9 @@
       <c r="D577" t="n">
         <v>4.571941120311906e-06</v>
       </c>
+      <c r="E577" t="n">
+        <v>0.0006906241382762712</v>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -10835,6 +12568,9 @@
       <c r="D578" t="n">
         <v>7.792417920707516e-07</v>
       </c>
+      <c r="E578" t="n">
+        <v>0.0004903453395273709</v>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
@@ -10853,6 +12589,9 @@
       <c r="D579" t="n">
         <v>5.120898947795378e-06</v>
       </c>
+      <c r="E579" t="n">
+        <v>0.0007357393474824864</v>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
@@ -10871,6 +12610,9 @@
       <c r="D580" t="n">
         <v>5.101276876464492e-06</v>
       </c>
+      <c r="E580" t="n">
+        <v>0.0007348647339950579</v>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
@@ -10889,6 +12631,9 @@
       <c r="D581" t="n">
         <v>8.40468458755396e-07</v>
       </c>
+      <c r="E581" t="n">
+        <v>0.0006299009052370334</v>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
@@ -10907,6 +12652,9 @@
       <c r="D582" t="n">
         <v>2.237797956025509e-06</v>
       </c>
+      <c r="E582" t="n">
+        <v>0.0006647880764964235</v>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
@@ -10925,6 +12673,9 @@
       <c r="D583" t="n">
         <v>1.646816144727677e-06</v>
       </c>
+      <c r="E583" t="n">
+        <v>0.000655816326093311</v>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -10943,6 +12694,9 @@
       <c r="D584" t="n">
         <v>2.656090239771643e-07</v>
       </c>
+      <c r="E584" t="n">
+        <v>0.0004624410943794617</v>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -10961,6 +12715,9 @@
       <c r="D585" t="n">
         <v>2.583378911977413e-06</v>
       </c>
+      <c r="E585" t="n">
+        <v>0.0007790495338371898</v>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
@@ -10979,6 +12736,9 @@
       <c r="D586" t="n">
         <v>9.000540994406138e-07</v>
       </c>
+      <c r="E586" t="n">
+        <v>0.0005830303819547316</v>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
@@ -10997,6 +12757,9 @@
       <c r="D587" t="n">
         <v>5.267849614014427e-07</v>
       </c>
+      <c r="E587" t="n">
+        <v>0.0005123892268571852</v>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
@@ -11015,6 +12778,9 @@
       <c r="D588" t="n">
         <v>3.80108162837126e-06</v>
       </c>
+      <c r="E588" t="n">
+        <v>0.0006584481159817252</v>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
@@ -11033,6 +12799,9 @@
       <c r="D589" t="n">
         <v>5.234398132429696e-07</v>
       </c>
+      <c r="E589" t="n">
+        <v>0.0004645718899767051</v>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
@@ -11051,6 +12820,9 @@
       <c r="D590" t="n">
         <v>1.078147968750294e-06</v>
       </c>
+      <c r="E590" t="n">
+        <v>0.0006001676557078387</v>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
@@ -11069,6 +12841,9 @@
       <c r="D591" t="n">
         <v>6.712587630683478e-07</v>
       </c>
+      <c r="E591" t="n">
+        <v>0.0005252168727377115</v>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
@@ -11087,6 +12862,9 @@
       <c r="D592" t="n">
         <v>7.830616213378359e-07</v>
       </c>
+      <c r="E592" t="n">
+        <v>0.0005859442947649501</v>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
@@ -11105,6 +12883,9 @@
       <c r="D593" t="n">
         <v>1.484646597607164e-06</v>
       </c>
+      <c r="E593" t="n">
+        <v>0.0007168212188674179</v>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -11123,6 +12904,9 @@
       <c r="D594" t="n">
         <v>8.955170477771372e-07</v>
       </c>
+      <c r="E594" t="n">
+        <v>0.0006096171913233069</v>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
@@ -11141,6 +12925,9 @@
       <c r="D595" t="n">
         <v>1.642372298773796e-06</v>
       </c>
+      <c r="E595" t="n">
+        <v>0.0007472789229030983</v>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
@@ -11159,6 +12946,9 @@
       <c r="D596" t="n">
         <v>5.964282628862525e-07</v>
       </c>
+      <c r="E596" t="n">
+        <v>0.0005661101388861839</v>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
@@ -11177,6 +12967,9 @@
       <c r="D597" t="n">
         <v>5.623640653263523e-07</v>
       </c>
+      <c r="E597" t="n">
+        <v>0.0005664218967901771</v>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
@@ -11195,6 +12988,9 @@
       <c r="D598" t="n">
         <v>5.506748824186005e-06</v>
       </c>
+      <c r="E598" t="n">
+        <v>0.0007501738042427516</v>
+      </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
@@ -11213,6 +13009,9 @@
       <c r="D599" t="n">
         <v>7.687964834424928e-06</v>
       </c>
+      <c r="E599" t="n">
+        <v>0.0008528747464554386</v>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
@@ -11231,6 +13030,9 @@
       <c r="D600" t="n">
         <v>5.676991070711256e-06</v>
       </c>
+      <c r="E600" t="n">
+        <v>0.0008376680095307456</v>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
@@ -11249,6 +13051,9 @@
       <c r="D601" t="n">
         <v>3.818374273395897e-07</v>
       </c>
+      <c r="E601" t="n">
+        <v>0.0005064969680191703</v>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
@@ -11267,6 +13072,9 @@
       <c r="D602" t="n">
         <v>7.913311579830309e-07</v>
       </c>
+      <c r="E602" t="n">
+        <v>0.0006204841155205141</v>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
@@ -11285,6 +13093,9 @@
       <c r="D603" t="n">
         <v>1.957159315384076e-06</v>
       </c>
+      <c r="E603" t="n">
+        <v>0.0007470306641337032</v>
+      </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
@@ -11303,6 +13114,9 @@
       <c r="D604" t="n">
         <v>1.089745357652054e-06</v>
       </c>
+      <c r="E604" t="n">
+        <v>0.0005241823000479661</v>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -11321,6 +13135,9 @@
       <c r="D605" t="n">
         <v>1.848682747414745e-06</v>
       </c>
+      <c r="E605" t="n">
+        <v>0.0007372353811042312</v>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
@@ -11339,6 +13156,9 @@
       <c r="D606" t="n">
         <v>2.076547391724807e-06</v>
       </c>
+      <c r="E606" t="n">
+        <v>0.0006610184748077412</v>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
@@ -11357,6 +13177,9 @@
       <c r="D607" t="n">
         <v>3.881882328335662e-07</v>
       </c>
+      <c r="E607" t="n">
+        <v>0.0004133921120033722</v>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
@@ -11375,6 +13198,9 @@
       <c r="D608" t="n">
         <v>2.829141554276054e-07</v>
       </c>
+      <c r="E608" t="n">
+        <v>0.0003817306182613467</v>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
@@ -11393,6 +13219,9 @@
       <c r="D609" t="n">
         <v>9.185525237381114e-07</v>
       </c>
+      <c r="E609" t="n">
+        <v>0.0006070593652590545</v>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
@@ -11411,6 +13240,9 @@
       <c r="D610" t="n">
         <v>6.971087888062088e-07</v>
       </c>
+      <c r="E610" t="n">
+        <v>0.0005440017919316922</v>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
@@ -11429,6 +13261,9 @@
       <c r="D611" t="n">
         <v>8.31764583108147e-07</v>
       </c>
+      <c r="E611" t="n">
+        <v>0.0006139159084475482</v>
+      </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
@@ -11447,6 +13282,9 @@
       <c r="D612" t="n">
         <v>8.96349365879721e-07</v>
       </c>
+      <c r="E612" t="n">
+        <v>0.0005091599674002433</v>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
@@ -11465,6 +13303,9 @@
       <c r="D613" t="n">
         <v>1.403406744458064e-06</v>
       </c>
+      <c r="E613" t="n">
+        <v>0.0007216589324866878</v>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
@@ -11483,6 +13324,9 @@
       <c r="D614" t="n">
         <v>2.117941782640112e-07</v>
       </c>
+      <c r="E614" t="n">
+        <v>0.0003795941992188109</v>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
@@ -11501,6 +13345,9 @@
       <c r="D615" t="n">
         <v>7.59553007612739e-07</v>
       </c>
+      <c r="E615" t="n">
+        <v>0.0006506678943605101</v>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
@@ -11519,6 +13366,9 @@
       <c r="D616" t="n">
         <v>5.801879402748951e-07</v>
       </c>
+      <c r="E616" t="n">
+        <v>0.0004638873063506731</v>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
@@ -11537,6 +13387,9 @@
       <c r="D617" t="n">
         <v>1.478033000281294e-06</v>
       </c>
+      <c r="E617" t="n">
+        <v>0.0006413784540472928</v>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
@@ -11555,6 +13408,9 @@
       <c r="D618" t="n">
         <v>1.168210682183975e-06</v>
       </c>
+      <c r="E618" t="n">
+        <v>0.0006074846360562075</v>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
@@ -11573,6 +13429,9 @@
       <c r="D619" t="n">
         <v>1.837812645761503e-06</v>
       </c>
+      <c r="E619" t="n">
+        <v>0.0005809747803390375</v>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -11591,6 +13450,9 @@
       <c r="D620" t="n">
         <v>3.182332036987616e-06</v>
       </c>
+      <c r="E620" t="n">
+        <v>0.0006655206565253882</v>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
@@ -11609,6 +13471,9 @@
       <c r="D621" t="n">
         <v>7.633112852002919e-07</v>
       </c>
+      <c r="E621" t="n">
+        <v>0.0006353035596233265</v>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
@@ -11627,6 +13492,9 @@
       <c r="D622" t="n">
         <v>7.882497372721624e-07</v>
       </c>
+      <c r="E622" t="n">
+        <v>0.0006770289137177979</v>
+      </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
@@ -11645,6 +13513,9 @@
       <c r="D623" t="n">
         <v>1.926478360286671e-06</v>
       </c>
+      <c r="E623" t="n">
+        <v>0.000756722760403066</v>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
@@ -11663,6 +13534,9 @@
       <c r="D624" t="n">
         <v>1.081857000213194e-06</v>
       </c>
+      <c r="E624" t="n">
+        <v>0.0006359461314421073</v>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
@@ -11681,6 +13555,9 @@
       <c r="D625" t="n">
         <v>1.722820910534318e-06</v>
       </c>
+      <c r="E625" t="n">
+        <v>0.0006749986320485176</v>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
@@ -11699,6 +13576,9 @@
       <c r="D626" t="n">
         <v>7.883022027050089e-07</v>
       </c>
+      <c r="E626" t="n">
+        <v>0.0005768308067477347</v>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
@@ -11717,6 +13597,9 @@
       <c r="D627" t="n">
         <v>1.738623924150855e-07</v>
       </c>
+      <c r="E627" t="n">
+        <v>0.0003357060005300273</v>
+      </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
@@ -11735,6 +13618,9 @@
       <c r="D628" t="n">
         <v>1.215946636458124e-06</v>
       </c>
+      <c r="E628" t="n">
+        <v>0.0006715823130209321</v>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
@@ -11753,6 +13639,9 @@
       <c r="D629" t="n">
         <v>5.812041693237095e-07</v>
       </c>
+      <c r="E629" t="n">
+        <v>0.0005685969281412162</v>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
@@ -11771,6 +13660,9 @@
       <c r="D630" t="n">
         <v>4.322609518126785e-07</v>
       </c>
+      <c r="E630" t="n">
+        <v>0.0004788721558599942</v>
+      </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
@@ -11789,6 +13681,9 @@
       <c r="D631" t="n">
         <v>1.596893748613669e-06</v>
       </c>
+      <c r="E631" t="n">
+        <v>0.0006015013316455175</v>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
@@ -11807,6 +13702,9 @@
       <c r="D632" t="n">
         <v>2.147438747925054e-07</v>
       </c>
+      <c r="E632" t="n">
+        <v>0.0003284194793950002</v>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
@@ -11825,6 +13723,9 @@
       <c r="D633" t="n">
         <v>1.51538190343196e-05</v>
       </c>
+      <c r="E633" t="n">
+        <v>0.0008002403068220133</v>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
@@ -11843,6 +13744,9 @@
       <c r="D634" t="n">
         <v>1.406479145524384e-05</v>
       </c>
+      <c r="E634" t="n">
+        <v>0.0007700969861684005</v>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
@@ -11861,6 +13765,9 @@
       <c r="D635" t="n">
         <v>6.387661781919183e-07</v>
       </c>
+      <c r="E635" t="n">
+        <v>0.0005526458873164924</v>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
@@ -11879,6 +13786,9 @@
       <c r="D636" t="n">
         <v>4.357081824269881e-07</v>
       </c>
+      <c r="E636" t="n">
+        <v>0.0005068979610700659</v>
+      </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
@@ -11897,6 +13807,9 @@
       <c r="D637" t="n">
         <v>2.302971060216874e-06</v>
       </c>
+      <c r="E637" t="n">
+        <v>0.0007473590544221265</v>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
@@ -11915,6 +13828,9 @@
       <c r="D638" t="n">
         <v>1.486042339855912e-06</v>
       </c>
+      <c r="E638" t="n">
+        <v>0.0006343929809097898</v>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
@@ -11933,6 +13849,9 @@
       <c r="D639" t="n">
         <v>2.061474591033188e-06</v>
       </c>
+      <c r="E639" t="n">
+        <v>0.000733455961831905</v>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
@@ -11951,6 +13870,9 @@
       <c r="D640" t="n">
         <v>2.489674039598094e-06</v>
       </c>
+      <c r="E640" t="n">
+        <v>0.0006869194700843961</v>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
@@ -11969,6 +13891,9 @@
       <c r="D641" t="n">
         <v>8.612351122945498e-07</v>
       </c>
+      <c r="E641" t="n">
+        <v>0.0006554427637897562</v>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="inlineStr">
@@ -11987,6 +13912,9 @@
       <c r="D642" t="n">
         <v>7.204167662998107e-07</v>
       </c>
+      <c r="E642" t="n">
+        <v>0.0005900708538028599</v>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="inlineStr">
@@ -12005,6 +13933,9 @@
       <c r="D643" t="n">
         <v>8.02529182794549e-07</v>
       </c>
+      <c r="E643" t="n">
+        <v>0.0005947757440054025</v>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
@@ -12023,6 +13954,9 @@
       <c r="D644" t="n">
         <v>1.220570622610507e-06</v>
       </c>
+      <c r="E644" t="n">
+        <v>0.0006501581530227002</v>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
@@ -12041,6 +13975,9 @@
       <c r="D645" t="n">
         <v>1.134827912746674e-06</v>
       </c>
+      <c r="E645" t="n">
+        <v>0.0007120665883465395</v>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
@@ -12059,6 +13996,9 @@
       <c r="D646" t="n">
         <v>1.217716163985182e-06</v>
       </c>
+      <c r="E646" t="n">
+        <v>0.0006813799824726196</v>
+      </c>
     </row>
     <row r="647">
       <c r="A647" t="inlineStr">
@@ -12077,6 +14017,9 @@
       <c r="D647" t="n">
         <v>5.793265219861364e-07</v>
       </c>
+      <c r="E647" t="n">
+        <v>0.0005304357258757989</v>
+      </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
@@ -12095,6 +14038,9 @@
       <c r="D648" t="n">
         <v>2.798448685611265e-06</v>
       </c>
+      <c r="E648" t="n">
+        <v>0.0007790817111676792</v>
+      </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
@@ -12113,6 +14059,9 @@
       <c r="D649" t="n">
         <v>9.949749278393292e-07</v>
       </c>
+      <c r="E649" t="n">
+        <v>0.0006611062121619462</v>
+      </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
@@ -12131,6 +14080,9 @@
       <c r="D650" t="n">
         <v>3.327852349468482e-06</v>
       </c>
+      <c r="E650" t="n">
+        <v>0.0006579215071863755</v>
+      </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
@@ -12149,6 +14101,9 @@
       <c r="D651" t="n">
         <v>1.154903707751091e-06</v>
       </c>
+      <c r="E651" t="n">
+        <v>0.0006623179191017963</v>
+      </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
@@ -12167,6 +14122,9 @@
       <c r="D652" t="n">
         <v>1.350496032064355e-06</v>
       </c>
+      <c r="E652" t="n">
+        <v>0.0006728558135649811</v>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="inlineStr">
@@ -12185,6 +14143,9 @@
       <c r="D653" t="n">
         <v>1.106080298637762e-06</v>
       </c>
+      <c r="E653" t="n">
+        <v>0.0005680135814618317</v>
+      </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
@@ -12203,6 +14164,9 @@
       <c r="D654" t="n">
         <v>2.114171885979641e-06</v>
       </c>
+      <c r="E654" t="n">
+        <v>0.0007345495145226768</v>
+      </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
@@ -12221,6 +14185,9 @@
       <c r="D655" t="n">
         <v>9.28919750109549e-07</v>
       </c>
+      <c r="E655" t="n">
+        <v>0.0005976276538328894</v>
+      </c>
     </row>
     <row r="656">
       <c r="A656" t="inlineStr">
@@ -12239,6 +14206,9 @@
       <c r="D656" t="n">
         <v>1.713170205038945e-06</v>
       </c>
+      <c r="E656" t="n">
+        <v>0.0006389032028672746</v>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="inlineStr">
@@ -12257,6 +14227,9 @@
       <c r="D657" t="n">
         <v>7.262645199150935e-07</v>
       </c>
+      <c r="E657" t="n">
+        <v>0.0005295061489366862</v>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="inlineStr">
@@ -12275,6 +14248,9 @@
       <c r="D658" t="n">
         <v>1.698296408605676e-06</v>
       </c>
+      <c r="E658" t="n">
+        <v>0.0007043546094910609</v>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="inlineStr">
@@ -12293,6 +14269,9 @@
       <c r="D659" t="n">
         <v>3.750166425085689e-07</v>
       </c>
+      <c r="E659" t="n">
+        <v>0.0004875720877460962</v>
+      </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
@@ -12311,6 +14290,9 @@
       <c r="D660" t="n">
         <v>2.636220017572033e-06</v>
       </c>
+      <c r="E660" t="n">
+        <v>0.0007392557365231473</v>
+      </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
@@ -12329,6 +14311,9 @@
       <c r="D661" t="n">
         <v>4.228237091524865e-07</v>
       </c>
+      <c r="E661" t="n">
+        <v>0.0005736601407467577</v>
+      </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
@@ -12347,6 +14332,9 @@
       <c r="D662" t="n">
         <v>8.024271271582336e-07</v>
       </c>
+      <c r="E662" t="n">
+        <v>0.0005700612549159479</v>
+      </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
@@ -12365,6 +14353,9 @@
       <c r="D663" t="n">
         <v>4.528390791733039e-07</v>
       </c>
+      <c r="E663" t="n">
+        <v>0.0005041158292202924</v>
+      </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
@@ -12383,6 +14374,9 @@
       <c r="D664" t="n">
         <v>1.244803406237208e-06</v>
       </c>
+      <c r="E664" t="n">
+        <v>0.0006862792932263172</v>
+      </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
@@ -12401,6 +14395,9 @@
       <c r="D665" t="n">
         <v>1.610161809888255e-06</v>
       </c>
+      <c r="E665" t="n">
+        <v>0.000714367618556981</v>
+      </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
@@ -12419,6 +14416,9 @@
       <c r="D666" t="n">
         <v>5.792051704138836e-07</v>
       </c>
+      <c r="E666" t="n">
+        <v>0.0005140977260946757</v>
+      </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
@@ -12437,6 +14437,9 @@
       <c r="D667" t="n">
         <v>8.372480312828406e-07</v>
       </c>
+      <c r="E667" t="n">
+        <v>0.0005061508905295644</v>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
@@ -12455,6 +14458,9 @@
       <c r="D668" t="n">
         <v>2.409133581852879e-06</v>
       </c>
+      <c r="E668" t="n">
+        <v>0.0007628890231222105</v>
+      </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
@@ -12473,6 +14479,9 @@
       <c r="D669" t="n">
         <v>1.601602461190135e-06</v>
       </c>
+      <c r="E669" t="n">
+        <v>0.000714272637297504</v>
+      </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
@@ -12491,6 +14500,9 @@
       <c r="D670" t="n">
         <v>1.086871401541073e-06</v>
       </c>
+      <c r="E670" t="n">
+        <v>0.0006482383951445627</v>
+      </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
@@ -12509,6 +14521,9 @@
       <c r="D671" t="n">
         <v>1.164687992050535e-06</v>
       </c>
+      <c r="E671" t="n">
+        <v>0.0006606917713128368</v>
+      </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
@@ -12527,6 +14542,9 @@
       <c r="D672" t="n">
         <v>7.193056682964913e-07</v>
       </c>
+      <c r="E672" t="n">
+        <v>0.0005467283181853358</v>
+      </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
@@ -12545,6 +14563,9 @@
       <c r="D673" t="n">
         <v>1.904810939676021e-06</v>
       </c>
+      <c r="E673" t="n">
+        <v>0.0006153886050734647</v>
+      </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
@@ -12563,6 +14584,9 @@
       <c r="D674" t="n">
         <v>9.367333732714898e-07</v>
       </c>
+      <c r="E674" t="n">
+        <v>0.0005376778985179835</v>
+      </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
@@ -12581,6 +14605,9 @@
       <c r="D675" t="n">
         <v>2.966369931242145e-07</v>
       </c>
+      <c r="E675" t="n">
+        <v>0.0004325021384263251</v>
+      </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
@@ -12599,6 +14626,9 @@
       <c r="D676" t="n">
         <v>3.653152846351828e-07</v>
       </c>
+      <c r="E676" t="n">
+        <v>0.0005494168137312885</v>
+      </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
@@ -12617,6 +14647,9 @@
       <c r="D677" t="n">
         <v>2.59090394142918e-07</v>
       </c>
+      <c r="E677" t="n">
+        <v>0.0003973013989469291</v>
+      </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
@@ -12635,6 +14668,9 @@
       <c r="D678" t="n">
         <v>7.206555686142813e-07</v>
       </c>
+      <c r="E678" t="n">
+        <v>0.0005442970910507024</v>
+      </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
@@ -12653,6 +14689,9 @@
       <c r="D679" t="n">
         <v>3.699180488675996e-07</v>
       </c>
+      <c r="E679" t="n">
+        <v>0.0004310649895473087</v>
+      </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
@@ -12671,6 +14710,9 @@
       <c r="D680" t="n">
         <v>1.995418126724715e-06</v>
       </c>
+      <c r="E680" t="n">
+        <v>0.0006045359216757234</v>
+      </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
@@ -12689,6 +14731,9 @@
       <c r="D681" t="n">
         <v>4.33814173621261e-07</v>
       </c>
+      <c r="E681" t="n">
+        <v>0.0004902019247552077</v>
+      </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
@@ -12707,6 +14752,9 @@
       <c r="D682" t="n">
         <v>2.871175308234304e-07</v>
       </c>
+      <c r="E682" t="n">
+        <v>0.0004259942512311257</v>
+      </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
@@ -12725,6 +14773,9 @@
       <c r="D683" t="n">
         <v>3.342341595385674e-06</v>
       </c>
+      <c r="E683" t="n">
+        <v>0.0007003137931674918</v>
+      </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
@@ -12743,6 +14794,9 @@
       <c r="D684" t="n">
         <v>2.018976777419951e-06</v>
       </c>
+      <c r="E684" t="n">
+        <v>0.0006221898956239528</v>
+      </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
@@ -12761,6 +14815,9 @@
       <c r="D685" t="n">
         <v>6.182241704741369e-07</v>
       </c>
+      <c r="E685" t="n">
+        <v>0.0005008753308026967</v>
+      </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
@@ -12779,6 +14836,9 @@
       <c r="D686" t="n">
         <v>1.456550452345426e-06</v>
       </c>
+      <c r="E686" t="n">
+        <v>0.0007706823302913666</v>
+      </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
@@ -12797,6 +14857,9 @@
       <c r="D687" t="n">
         <v>4.294404313542623e-06</v>
       </c>
+      <c r="E687" t="n">
+        <v>0.0007305360707472791</v>
+      </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
@@ -12815,6 +14878,9 @@
       <c r="D688" t="n">
         <v>2.063517243961004e-06</v>
       </c>
+      <c r="E688" t="n">
+        <v>0.0006007404702195874</v>
+      </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
@@ -12833,6 +14899,9 @@
       <c r="D689" t="n">
         <v>2.572383099992665e-06</v>
       </c>
+      <c r="E689" t="n">
+        <v>0.0007331224814491588</v>
+      </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
@@ -12851,6 +14920,9 @@
       <c r="D690" t="n">
         <v>6.774192520088108e-07</v>
       </c>
+      <c r="E690" t="n">
+        <v>0.000504446660628451</v>
+      </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
@@ -12869,6 +14941,9 @@
       <c r="D691" t="n">
         <v>7.725526267009328e-07</v>
       </c>
+      <c r="E691" t="n">
+        <v>0.0005765695067483023</v>
+      </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
@@ -12887,6 +14962,9 @@
       <c r="D692" t="n">
         <v>2.960804659593662e-06</v>
       </c>
+      <c r="E692" t="n">
+        <v>0.0007450229153246958</v>
+      </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
@@ -12905,6 +14983,9 @@
       <c r="D693" t="n">
         <v>1.908989419961825e-06</v>
       </c>
+      <c r="E693" t="n">
+        <v>0.0005708609568615804</v>
+      </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
@@ -12923,6 +15004,9 @@
       <c r="D694" t="n">
         <v>1.578391422110187e-06</v>
       </c>
+      <c r="E694" t="n">
+        <v>0.0005967804178112724</v>
+      </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
@@ -12941,6 +15025,9 @@
       <c r="D695" t="n">
         <v>1.189347287388284e-06</v>
       </c>
+      <c r="E695" t="n">
+        <v>0.0006101946895687548</v>
+      </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
@@ -12959,6 +15046,9 @@
       <c r="D696" t="n">
         <v>3.716112597967216e-07</v>
       </c>
+      <c r="E696" t="n">
+        <v>0.0005127762570408214</v>
+      </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
@@ -12977,6 +15067,9 @@
       <c r="D697" t="n">
         <v>1.730101910107801e-06</v>
       </c>
+      <c r="E697" t="n">
+        <v>0.0005851787351398568</v>
+      </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
@@ -12995,6 +15088,9 @@
       <c r="D698" t="n">
         <v>2.325776222579314e-06</v>
       </c>
+      <c r="E698" t="n">
+        <v>0.0006919677624871333</v>
+      </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
@@ -13013,6 +15109,9 @@
       <c r="D699" t="n">
         <v>5.098457744780818e-06</v>
       </c>
+      <c r="E699" t="n">
+        <v>0.000813587105225545</v>
+      </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
@@ -13031,6 +15130,9 @@
       <c r="D700" t="n">
         <v>1.846110242793965e-07</v>
       </c>
+      <c r="E700" t="n">
+        <v>0.0004294651653817677</v>
+      </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
@@ -13049,6 +15151,9 @@
       <c r="D701" t="n">
         <v>1.705014116462867e-07</v>
       </c>
+      <c r="E701" t="n">
+        <v>0.0003343382208193908</v>
+      </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
@@ -13067,6 +15172,9 @@
       <c r="D702" t="n">
         <v>9.930566415471596e-07</v>
       </c>
+      <c r="E702" t="n">
+        <v>0.0004208960159025673</v>
+      </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
@@ -13085,6 +15193,9 @@
       <c r="D703" t="n">
         <v>1.142699601502706e-06</v>
       </c>
+      <c r="E703" t="n">
+        <v>0.0004543871576285581</v>
+      </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -13103,6 +15214,9 @@
       <c r="D704" t="n">
         <v>2.721169860631537e-06</v>
       </c>
+      <c r="E704" t="n">
+        <v>0.0006232618025513981</v>
+      </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
@@ -13121,6 +15235,9 @@
       <c r="D705" t="n">
         <v>6.480530877818477e-07</v>
       </c>
+      <c r="E705" t="n">
+        <v>0.0005426201591576032</v>
+      </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -13139,6 +15256,9 @@
       <c r="D706" t="n">
         <v>1.703229164600003e-07</v>
       </c>
+      <c r="E706" t="n">
+        <v>0.0003459988481327677</v>
+      </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -13157,6 +15277,9 @@
       <c r="D707" t="n">
         <v>2.832254269681579e-06</v>
       </c>
+      <c r="E707" t="n">
+        <v>0.0007176458327568294</v>
+      </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
@@ -13175,6 +15298,9 @@
       <c r="D708" t="n">
         <v>2.564239823683368e-06</v>
       </c>
+      <c r="E708" t="n">
+        <v>0.0006588057849521675</v>
+      </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
@@ -13193,6 +15319,9 @@
       <c r="D709" t="n">
         <v>6.229258299128036e-07</v>
       </c>
+      <c r="E709" t="n">
+        <v>0.0005478652856608679</v>
+      </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
@@ -13211,6 +15340,9 @@
       <c r="D710" t="n">
         <v>2.136790864316783e-06</v>
       </c>
+      <c r="E710" t="n">
+        <v>0.0006771971759204938</v>
+      </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
@@ -13229,6 +15361,9 @@
       <c r="D711" t="n">
         <v>3.268400129623735e-06</v>
       </c>
+      <c r="E711" t="n">
+        <v>0.0006855871091299237</v>
+      </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
@@ -13247,6 +15382,9 @@
       <c r="D712" t="n">
         <v>6.133080555716055e-07</v>
       </c>
+      <c r="E712" t="n">
+        <v>0.0005600716274884203</v>
+      </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
@@ -13265,6 +15403,9 @@
       <c r="D713" t="n">
         <v>1.456514984045776e-06</v>
       </c>
+      <c r="E713" t="n">
+        <v>0.0007006492011734875</v>
+      </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
@@ -13283,6 +15424,9 @@
       <c r="D714" t="n">
         <v>5.762413420674083e-07</v>
       </c>
+      <c r="E714" t="n">
+        <v>0.0005744633548645785</v>
+      </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
@@ -13301,6 +15445,9 @@
       <c r="D715" t="n">
         <v>9.834275051095312e-07</v>
       </c>
+      <c r="E715" t="n">
+        <v>0.0006441308080902862</v>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
@@ -13319,6 +15466,9 @@
       <c r="D716" t="n">
         <v>7.001922303180903e-07</v>
       </c>
+      <c r="E716" t="n">
+        <v>0.0006085132713409826</v>
+      </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
@@ -13337,6 +15487,9 @@
       <c r="D717" t="n">
         <v>7.346565769309902e-07</v>
       </c>
+      <c r="E717" t="n">
+        <v>0.0004663283122925113</v>
+      </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
@@ -13355,6 +15508,9 @@
       <c r="D718" t="n">
         <v>1.542505097008855e-06</v>
       </c>
+      <c r="E718" t="n">
+        <v>0.0007120906808927818</v>
+      </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
@@ -13373,6 +15529,9 @@
       <c r="D719" t="n">
         <v>1.107004441710828e-06</v>
       </c>
+      <c r="E719" t="n">
+        <v>0.0005313517964912259</v>
+      </c>
     </row>
     <row r="720">
       <c r="A720" t="inlineStr">
@@ -13391,6 +15550,9 @@
       <c r="D720" t="n">
         <v>5.504113919943816e-07</v>
       </c>
+      <c r="E720" t="n">
+        <v>0.0005048918908257648</v>
+      </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
@@ -13409,6 +15571,9 @@
       <c r="D721" t="n">
         <v>3.248254959644413e-07</v>
       </c>
+      <c r="E721" t="n">
+        <v>0.0004769168907192476</v>
+      </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
@@ -13427,6 +15592,9 @@
       <c r="D722" t="n">
         <v>1.338479134929901e-06</v>
       </c>
+      <c r="E722" t="n">
+        <v>0.0006251342134528028</v>
+      </c>
     </row>
     <row r="723">
       <c r="A723" t="inlineStr">
@@ -13445,6 +15613,9 @@
       <c r="D723" t="n">
         <v>1.240500989222865e-06</v>
       </c>
+      <c r="E723" t="n">
+        <v>0.0006556111594598629</v>
+      </c>
     </row>
     <row r="724">
       <c r="A724" t="inlineStr">
@@ -13463,6 +15634,9 @@
       <c r="D724" t="n">
         <v>1.249529459849529e-06</v>
       </c>
+      <c r="E724" t="n">
+        <v>0.0006897857121201649</v>
+      </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
@@ -13481,6 +15655,9 @@
       <c r="D725" t="n">
         <v>7.087904089308694e-07</v>
       </c>
+      <c r="E725" t="n">
+        <v>0.0005626800294931323</v>
+      </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
@@ -13499,6 +15676,9 @@
       <c r="D726" t="n">
         <v>3.014703004232828e-06</v>
       </c>
+      <c r="E726" t="n">
+        <v>0.0008119877180449478</v>
+      </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
@@ -13517,6 +15697,9 @@
       <c r="D727" t="n">
         <v>4.64219387601095e-07</v>
       </c>
+      <c r="E727" t="n">
+        <v>0.00052545077964714</v>
+      </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
@@ -13535,6 +15718,9 @@
       <c r="D728" t="n">
         <v>1.042651067991271e-06</v>
       </c>
+      <c r="E728" t="n">
+        <v>0.0006641858008688637</v>
+      </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
@@ -13553,6 +15739,9 @@
       <c r="D729" t="n">
         <v>3.46973102377476e-07</v>
       </c>
+      <c r="E729" t="n">
+        <v>0.0004423965698962997</v>
+      </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
@@ -13571,6 +15760,9 @@
       <c r="D730" t="n">
         <v>3.93270016609745e-06</v>
       </c>
+      <c r="E730" t="n">
+        <v>0.0008008306963281779</v>
+      </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
@@ -13589,6 +15781,9 @@
       <c r="D731" t="n">
         <v>4.112128377029616e-06</v>
       </c>
+      <c r="E731" t="n">
+        <v>0.0008037000457727101</v>
+      </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
@@ -13607,6 +15802,9 @@
       <c r="D732" t="n">
         <v>2.197595437605969e-06</v>
       </c>
+      <c r="E732" t="n">
+        <v>0.0007563756415245645</v>
+      </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
@@ -13625,6 +15823,9 @@
       <c r="D733" t="n">
         <v>6.770587345740041e-07</v>
       </c>
+      <c r="E733" t="n">
+        <v>0.0004690671721203221</v>
+      </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
@@ -13643,6 +15844,9 @@
       <c r="D734" t="n">
         <v>2.800239507883319e-06</v>
       </c>
+      <c r="E734" t="n">
+        <v>0.0006657162940196348</v>
+      </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
@@ -13661,6 +15865,9 @@
       <c r="D735" t="n">
         <v>2.061298913939331e-06</v>
       </c>
+      <c r="E735" t="n">
+        <v>0.0006063839390670404</v>
+      </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
@@ -13679,6 +15886,9 @@
       <c r="D736" t="n">
         <v>2.179909366943393e-06</v>
       </c>
+      <c r="E736" t="n">
+        <v>0.0006502121387795828</v>
+      </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
@@ -13697,6 +15907,9 @@
       <c r="D737" t="n">
         <v>3.297968620718982e-07</v>
       </c>
+      <c r="E737" t="n">
+        <v>0.0003708206181843232</v>
+      </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
@@ -13715,6 +15928,9 @@
       <c r="D738" t="n">
         <v>1.397280016229636e-05</v>
       </c>
+      <c r="E738" t="n">
+        <v>0.0008802366631828689</v>
+      </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
@@ -13733,6 +15949,9 @@
       <c r="D739" t="n">
         <v>3.131021011938013e-06</v>
       </c>
+      <c r="E739" t="n">
+        <v>0.000690334889304005</v>
+      </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
@@ -13751,6 +15970,9 @@
       <c r="D740" t="n">
         <v>1.062311550467488e-06</v>
       </c>
+      <c r="E740" t="n">
+        <v>0.0005890574260405555</v>
+      </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
@@ -13769,6 +15991,9 @@
       <c r="D741" t="n">
         <v>1.575855101399041e-06</v>
       </c>
+      <c r="E741" t="n">
+        <v>0.0006258411867153419</v>
+      </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
@@ -13787,6 +16012,9 @@
       <c r="D742" t="n">
         <v>1.828036416683663e-06</v>
       </c>
+      <c r="E742" t="n">
+        <v>0.0006776833233060721</v>
+      </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
@@ -13805,6 +16033,9 @@
       <c r="D743" t="n">
         <v>4.412588019015556e-07</v>
       </c>
+      <c r="E743" t="n">
+        <v>0.0004508649001118008</v>
+      </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
@@ -13823,6 +16054,9 @@
       <c r="D744" t="n">
         <v>7.462320438136804e-07</v>
       </c>
+      <c r="E744" t="n">
+        <v>0.0005052253727137897</v>
+      </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
@@ -13841,6 +16075,9 @@
       <c r="D745" t="n">
         <v>2.120736011469214e-06</v>
       </c>
+      <c r="E745" t="n">
+        <v>0.0006815245886722327</v>
+      </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
@@ -13859,6 +16096,9 @@
       <c r="D746" t="n">
         <v>1.102558569789455e-06</v>
       </c>
+      <c r="E746" t="n">
+        <v>0.0006587222713038042</v>
+      </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
@@ -13877,6 +16117,9 @@
       <c r="D747" t="n">
         <v>1.053004036820615e-06</v>
       </c>
+      <c r="E747" t="n">
+        <v>0.0006144370544930497</v>
+      </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
@@ -13895,6 +16138,9 @@
       <c r="D748" t="n">
         <v>8.11439387244228e-07</v>
       </c>
+      <c r="E748" t="n">
+        <v>0.0005922191368665492</v>
+      </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
@@ -13913,6 +16159,9 @@
       <c r="D749" t="n">
         <v>2.508830927340428e-06</v>
       </c>
+      <c r="E749" t="n">
+        <v>0.0006903821387756818</v>
+      </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
@@ -13931,6 +16180,9 @@
       <c r="D750" t="n">
         <v>9.753908797940299e-07</v>
       </c>
+      <c r="E750" t="n">
+        <v>0.0006227131968527092</v>
+      </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
@@ -13949,6 +16201,9 @@
       <c r="D751" t="n">
         <v>2.978716501740096e-06</v>
       </c>
+      <c r="E751" t="n">
+        <v>0.0007701376007581644</v>
+      </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
@@ -13967,6 +16222,9 @@
       <c r="D752" t="n">
         <v>4.023868670968242e-07</v>
       </c>
+      <c r="E752" t="n">
+        <v>0.0004169928432662186</v>
+      </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
@@ -13985,6 +16243,9 @@
       <c r="D753" t="n">
         <v>1.797665556691305e-07</v>
       </c>
+      <c r="E753" t="n">
+        <v>0.0003243735761651243</v>
+      </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
@@ -14003,6 +16264,9 @@
       <c r="D754" t="n">
         <v>2.950493160568713e-06</v>
       </c>
+      <c r="E754" t="n">
+        <v>0.0007476428958495941</v>
+      </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
@@ -14021,6 +16285,9 @@
       <c r="D755" t="n">
         <v>1.167858434051852e-06</v>
       </c>
+      <c r="E755" t="n">
+        <v>0.0006196204911426375</v>
+      </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
@@ -14039,6 +16306,9 @@
       <c r="D756" t="n">
         <v>1.094538513790238e-06</v>
       </c>
+      <c r="E756" t="n">
+        <v>0.0006203097605114923</v>
+      </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
@@ -14057,6 +16327,9 @@
       <c r="D757" t="n">
         <v>1.27772102024796e-06</v>
       </c>
+      <c r="E757" t="n">
+        <v>0.0006773441242462647</v>
+      </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
@@ -14075,6 +16348,9 @@
       <c r="D758" t="n">
         <v>3.128903946428945e-06</v>
       </c>
+      <c r="E758" t="n">
+        <v>0.0008248271768986895</v>
+      </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
@@ -14093,6 +16369,9 @@
       <c r="D759" t="n">
         <v>1.554783601776831e-06</v>
       </c>
+      <c r="E759" t="n">
+        <v>0.0005958312188208079</v>
+      </c>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
@@ -14111,6 +16390,9 @@
       <c r="D760" t="n">
         <v>9.443341644152229e-07</v>
       </c>
+      <c r="E760" t="n">
+        <v>0.0006129754400675243</v>
+      </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
@@ -14129,6 +16411,9 @@
       <c r="D761" t="n">
         <v>1.472453419857262e-06</v>
       </c>
+      <c r="E761" t="n">
+        <v>0.0005461446070296539</v>
+      </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
@@ -14147,6 +16432,9 @@
       <c r="D762" t="n">
         <v>3.9214639283812e-06</v>
       </c>
+      <c r="E762" t="n">
+        <v>0.0007691813435449474</v>
+      </c>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
@@ -14165,6 +16453,9 @@
       <c r="D763" t="n">
         <v>1.022954802348932e-06</v>
       </c>
+      <c r="E763" t="n">
+        <v>0.0005811306833935501</v>
+      </c>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
@@ -14183,6 +16474,9 @@
       <c r="D764" t="n">
         <v>3.043882255654983e-06</v>
       </c>
+      <c r="E764" t="n">
+        <v>0.0007899293134998663</v>
+      </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
@@ -14201,6 +16495,9 @@
       <c r="D765" t="n">
         <v>3.776298653202989e-06</v>
       </c>
+      <c r="E765" t="n">
+        <v>0.0008300536748255333</v>
+      </c>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
@@ -14219,6 +16516,9 @@
       <c r="D766" t="n">
         <v>2.172290682658975e-06</v>
       </c>
+      <c r="E766" t="n">
+        <v>0.0006877706361000203</v>
+      </c>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
@@ -14237,6 +16537,9 @@
       <c r="D767" t="n">
         <v>1.387591756122392e-06</v>
       </c>
+      <c r="E767" t="n">
+        <v>0.0007061369910543121</v>
+      </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
@@ -14255,6 +16558,9 @@
       <c r="D768" t="n">
         <v>2.28978510225126e-06</v>
       </c>
+      <c r="E768" t="n">
+        <v>0.0006546143021749603</v>
+      </c>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
@@ -14273,6 +16579,9 @@
       <c r="D769" t="n">
         <v>1.098183923951953e-06</v>
       </c>
+      <c r="E769" t="n">
+        <v>0.0005530701289963834</v>
+      </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
@@ -14291,6 +16600,9 @@
       <c r="D770" t="n">
         <v>4.040758208291522e-05</v>
       </c>
+      <c r="E770" t="n">
+        <v>0.0009668863105384938</v>
+      </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
@@ -14309,6 +16621,9 @@
       <c r="D771" t="n">
         <v>3.69631966286165e-06</v>
       </c>
+      <c r="E771" t="n">
+        <v>0.0008065135436419468</v>
+      </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
@@ -14327,6 +16642,9 @@
       <c r="D772" t="n">
         <v>1.728337151536437e-06</v>
       </c>
+      <c r="E772" t="n">
+        <v>0.000716296142456151</v>
+      </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
@@ -14345,6 +16663,9 @@
       <c r="D773" t="n">
         <v>2.292307603880427e-06</v>
       </c>
+      <c r="E773" t="n">
+        <v>0.0006717938313535143</v>
+      </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
@@ -14363,6 +16684,9 @@
       <c r="D774" t="n">
         <v>1.452672838377034e-06</v>
       </c>
+      <c r="E774" t="n">
+        <v>0.0005889369318512928</v>
+      </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
@@ -14381,6 +16705,9 @@
       <c r="D775" t="n">
         <v>2.030862301748267e-06</v>
       </c>
+      <c r="E775" t="n">
+        <v>0.0005601316148783784</v>
+      </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
@@ -14399,6 +16726,9 @@
       <c r="D776" t="n">
         <v>1.427660074421056e-06</v>
       </c>
+      <c r="E776" t="n">
+        <v>0.0006986849731920714</v>
+      </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
@@ -14417,6 +16747,9 @@
       <c r="D777" t="n">
         <v>1.1541823020951e-06</v>
       </c>
+      <c r="E777" t="n">
+        <v>0.0006266732736008199</v>
+      </c>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
@@ -14435,6 +16768,9 @@
       <c r="D778" t="n">
         <v>1.080333275413945e-06</v>
       </c>
+      <c r="E778" t="n">
+        <v>0.000588379931340438</v>
+      </c>
     </row>
     <row r="779">
       <c r="A779" t="inlineStr">
@@ -14453,6 +16789,9 @@
       <c r="D779" t="n">
         <v>4.66935787849951e-07</v>
       </c>
+      <c r="E779" t="n">
+        <v>0.0004913312701711342</v>
+      </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
@@ -14471,6 +16810,9 @@
       <c r="D780" t="n">
         <v>1.954654503320211e-06</v>
       </c>
+      <c r="E780" t="n">
+        <v>0.0006799212770168233</v>
+      </c>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
@@ -14489,6 +16831,9 @@
       <c r="D781" t="n">
         <v>5.60362065025619e-07</v>
       </c>
+      <c r="E781" t="n">
+        <v>0.0005306746628627107</v>
+      </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
@@ -14507,6 +16852,9 @@
       <c r="D782" t="n">
         <v>9.391270782257673e-07</v>
       </c>
+      <c r="E782" t="n">
+        <v>0.0006207030761151278</v>
+      </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
@@ -14525,6 +16873,9 @@
       <c r="D783" t="n">
         <v>2.068684528000944e-07</v>
       </c>
+      <c r="E783" t="n">
+        <v>0.0003250425770816046</v>
+      </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
@@ -14543,6 +16894,9 @@
       <c r="D784" t="n">
         <v>2.03694734599682e-06</v>
       </c>
+      <c r="E784" t="n">
+        <v>0.0007046021547595922</v>
+      </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
@@ -14561,6 +16915,9 @@
       <c r="D785" t="n">
         <v>1.107200490511623e-06</v>
       </c>
+      <c r="E785" t="n">
+        <v>0.0006714195166934056</v>
+      </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
@@ -14579,6 +16936,9 @@
       <c r="D786" t="n">
         <v>4.431003461832374e-06</v>
       </c>
+      <c r="E786" t="n">
+        <v>0.0008055401991936676</v>
+      </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
@@ -14597,6 +16957,9 @@
       <c r="D787" t="n">
         <v>1.936178530939919e-06</v>
       </c>
+      <c r="E787" t="n">
+        <v>0.0006882758117776468</v>
+      </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
@@ -14615,6 +16978,9 @@
       <c r="D788" t="n">
         <v>1.725356026409163e-06</v>
       </c>
+      <c r="E788" t="n">
+        <v>0.0007063027194654107</v>
+      </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
@@ -14633,6 +16999,9 @@
       <c r="D789" t="n">
         <v>4.1437086161626e-06</v>
       </c>
+      <c r="E789" t="n">
+        <v>0.0007149845165983227</v>
+      </c>
     </row>
     <row r="790">
       <c r="A790" t="inlineStr">
@@ -14651,6 +17020,9 @@
       <c r="D790" t="n">
         <v>5.043561446937252e-07</v>
       </c>
+      <c r="E790" t="n">
+        <v>0.0004897508314696561</v>
+      </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
@@ -14669,6 +17041,9 @@
       <c r="D791" t="n">
         <v>2.993949197364076e-06</v>
       </c>
+      <c r="E791" t="n">
+        <v>0.0007267851314885458</v>
+      </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
@@ -14687,6 +17062,9 @@
       <c r="D792" t="n">
         <v>2.635150458290199e-06</v>
       </c>
+      <c r="E792" t="n">
+        <v>0.0006992045791360892</v>
+      </c>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
@@ -14705,6 +17083,9 @@
       <c r="D793" t="n">
         <v>2.07222177572734e-06</v>
       </c>
+      <c r="E793" t="n">
+        <v>0.0007588187962074803</v>
+      </c>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
@@ -14723,6 +17104,9 @@
       <c r="D794" t="n">
         <v>4.885055236438909e-07</v>
       </c>
+      <c r="E794" t="n">
+        <v>0.0005261077785581963</v>
+      </c>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
@@ -14741,6 +17125,9 @@
       <c r="D795" t="n">
         <v>6.888066327437599e-07</v>
       </c>
+      <c r="E795" t="n">
+        <v>0.0004651163141044758</v>
+      </c>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
@@ -14759,6 +17146,9 @@
       <c r="D796" t="n">
         <v>1.411158748423353e-06</v>
       </c>
+      <c r="E796" t="n">
+        <v>0.0006410366862592104</v>
+      </c>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
@@ -14777,6 +17167,9 @@
       <c r="D797" t="n">
         <v>2.526309339076485e-06</v>
       </c>
+      <c r="E797" t="n">
+        <v>0.0007460763265218266</v>
+      </c>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
@@ -14795,6 +17188,9 @@
       <c r="D798" t="n">
         <v>5.405635987978486e-07</v>
       </c>
+      <c r="E798" t="n">
+        <v>0.0004986055556630968</v>
+      </c>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
@@ -14813,6 +17209,9 @@
       <c r="D799" t="n">
         <v>8.350970123246232e-07</v>
       </c>
+      <c r="E799" t="n">
+        <v>0.000649152953833735</v>
+      </c>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
@@ -14831,6 +17230,9 @@
       <c r="D800" t="n">
         <v>1.084841736807326e-06</v>
       </c>
+      <c r="E800" t="n">
+        <v>0.0006921291727320023</v>
+      </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
@@ -14849,6 +17251,9 @@
       <c r="D801" t="n">
         <v>3.50463148890426e-06</v>
       </c>
+      <c r="E801" t="n">
+        <v>0.0007576085709311896</v>
+      </c>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
@@ -14867,6 +17272,9 @@
       <c r="D802" t="n">
         <v>2.175157430618236e-06</v>
       </c>
+      <c r="E802" t="n">
+        <v>0.0007417273209621032</v>
+      </c>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
@@ -14885,6 +17293,9 @@
       <c r="D803" t="n">
         <v>2.084174314515319e-06</v>
       </c>
+      <c r="E803" t="n">
+        <v>0.000691273786788596</v>
+      </c>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
@@ -14903,6 +17314,9 @@
       <c r="D804" t="n">
         <v>1.614576729596937e-06</v>
       </c>
+      <c r="E804" t="n">
+        <v>0.0006364086074031307</v>
+      </c>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
@@ -14921,6 +17335,9 @@
       <c r="D805" t="n">
         <v>2.005272113391458e-06</v>
       </c>
+      <c r="E805" t="n">
+        <v>0.0007650208646468192</v>
+      </c>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
@@ -14939,6 +17356,9 @@
       <c r="D806" t="n">
         <v>1.224312209658264e-06</v>
       </c>
+      <c r="E806" t="n">
+        <v>0.0006631065186677188</v>
+      </c>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
@@ -14957,6 +17377,9 @@
       <c r="D807" t="n">
         <v>1.541640027292257e-06</v>
       </c>
+      <c r="E807" t="n">
+        <v>0.0006510351593958654</v>
+      </c>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
@@ -14975,6 +17398,9 @@
       <c r="D808" t="n">
         <v>8.400986513166546e-07</v>
       </c>
+      <c r="E808" t="n">
+        <v>0.0004985771405940533</v>
+      </c>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
@@ -14993,6 +17419,9 @@
       <c r="D809" t="n">
         <v>9.843002468072561e-06</v>
       </c>
+      <c r="E809" t="n">
+        <v>0.0008391383205517592</v>
+      </c>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
@@ -15011,6 +17440,9 @@
       <c r="D810" t="n">
         <v>6.129703523630599e-07</v>
       </c>
+      <c r="E810" t="n">
+        <v>0.000507132115481457</v>
+      </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
@@ -15029,6 +17461,9 @@
       <c r="D811" t="n">
         <v>1.825066564538329e-06</v>
       </c>
+      <c r="E811" t="n">
+        <v>0.0007610475612705825</v>
+      </c>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
@@ -15047,6 +17482,9 @@
       <c r="D812" t="n">
         <v>7.842504074642019e-07</v>
       </c>
+      <c r="E812" t="n">
+        <v>0.0005747475703073156</v>
+      </c>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
@@ -15065,6 +17503,9 @@
       <c r="D813" t="n">
         <v>7.453474817717199e-07</v>
       </c>
+      <c r="E813" t="n">
+        <v>0.0006159506671381976</v>
+      </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
@@ -15083,6 +17524,9 @@
       <c r="D814" t="n">
         <v>2.364034464992719e-06</v>
       </c>
+      <c r="E814" t="n">
+        <v>0.000794542695677032</v>
+      </c>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
@@ -15101,6 +17545,9 @@
       <c r="D815" t="n">
         <v>1.863515867000297e-06</v>
       </c>
+      <c r="E815" t="n">
+        <v>0.0007675727241927047</v>
+      </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
@@ -15119,6 +17566,9 @@
       <c r="D816" t="n">
         <v>1.348662238361472e-06</v>
       </c>
+      <c r="E816" t="n">
+        <v>0.0007021020630056421</v>
+      </c>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
@@ -15137,6 +17587,9 @@
       <c r="D817" t="n">
         <v>1.597607018044559e-06</v>
       </c>
+      <c r="E817" t="n">
+        <v>0.0005351902292642193</v>
+      </c>
     </row>
     <row r="818">
       <c r="A818" t="inlineStr">
@@ -15155,6 +17608,9 @@
       <c r="D818" t="n">
         <v>3.283512056067845e-07</v>
       </c>
+      <c r="E818" t="n">
+        <v>0.0004072332403790405</v>
+      </c>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
@@ -15173,6 +17629,9 @@
       <c r="D819" t="n">
         <v>4.237330511483105e-07</v>
       </c>
+      <c r="E819" t="n">
+        <v>0.0004748469786849275</v>
+      </c>
     </row>
     <row r="820">
       <c r="A820" t="inlineStr">
@@ -15191,6 +17650,9 @@
       <c r="D820" t="n">
         <v>2.766473508491708e-07</v>
       </c>
+      <c r="E820" t="n">
+        <v>0.0004325528922586724</v>
+      </c>
     </row>
     <row r="821">
       <c r="A821" t="inlineStr">
@@ -15209,6 +17671,9 @@
       <c r="D821" t="n">
         <v>7.233223824187636e-07</v>
       </c>
+      <c r="E821" t="n">
+        <v>0.0005848853962742873</v>
+      </c>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
@@ -15227,6 +17692,9 @@
       <c r="D822" t="n">
         <v>1.196119785573334e-06</v>
       </c>
+      <c r="E822" t="n">
+        <v>0.000701403994083862</v>
+      </c>
     </row>
     <row r="823">
       <c r="A823" t="inlineStr">
@@ -15245,6 +17713,9 @@
       <c r="D823" t="n">
         <v>1.454312736943769e-06</v>
       </c>
+      <c r="E823" t="n">
+        <v>0.0005575692088800212</v>
+      </c>
     </row>
     <row r="824">
       <c r="A824" t="inlineStr">
@@ -15263,6 +17734,9 @@
       <c r="D824" t="n">
         <v>4.852533031928171e-06</v>
       </c>
+      <c r="E824" t="n">
+        <v>0.000721997529354362</v>
+      </c>
     </row>
     <row r="825">
       <c r="A825" t="inlineStr">
@@ -15281,6 +17755,9 @@
       <c r="D825" t="n">
         <v>1.043695778587975e-06</v>
       </c>
+      <c r="E825" t="n">
+        <v>0.0005402936878696395</v>
+      </c>
     </row>
     <row r="826">
       <c r="A826" t="inlineStr">
@@ -15299,6 +17776,9 @@
       <c r="D826" t="n">
         <v>5.530957200306058e-06</v>
       </c>
+      <c r="E826" t="n">
+        <v>0.0007964716560423414</v>
+      </c>
     </row>
     <row r="827">
       <c r="A827" t="inlineStr">
@@ -15317,6 +17797,9 @@
       <c r="D827" t="n">
         <v>5.507845280933822e-06</v>
       </c>
+      <c r="E827" t="n">
+        <v>0.0007955365368605673</v>
+      </c>
     </row>
     <row r="828">
       <c r="A828" t="inlineStr">
@@ -15335,6 +17818,9 @@
       <c r="D828" t="n">
         <v>9.659044275620157e-07</v>
       </c>
+      <c r="E828" t="n">
+        <v>0.0006355613082794558</v>
+      </c>
     </row>
     <row r="829">
       <c r="A829" t="inlineStr">
@@ -15353,6 +17839,9 @@
       <c r="D829" t="n">
         <v>2.605352998740079e-06</v>
       </c>
+      <c r="E829" t="n">
+        <v>0.0007044797911593915</v>
+      </c>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
@@ -15371,6 +17860,9 @@
       <c r="D830" t="n">
         <v>1.776891329218585e-06</v>
       </c>
+      <c r="E830" t="n">
+        <v>0.0006705390976850043</v>
+      </c>
     </row>
     <row r="831">
       <c r="A831" t="inlineStr">
@@ -15389,6 +17881,9 @@
       <c r="D831" t="n">
         <v>3.603555545452228e-07</v>
       </c>
+      <c r="E831" t="n">
+        <v>0.0004661818733555686</v>
+      </c>
     </row>
     <row r="832">
       <c r="A832" t="inlineStr">
@@ -15407,6 +17902,9 @@
       <c r="D832" t="n">
         <v>3.781630624422441e-06</v>
       </c>
+      <c r="E832" t="n">
+        <v>0.0008413728772877093</v>
+      </c>
     </row>
     <row r="833">
       <c r="A833" t="inlineStr">
@@ -15425,6 +17923,9 @@
       <c r="D833" t="n">
         <v>1.347308824713293e-06</v>
       </c>
+      <c r="E833" t="n">
+        <v>0.0006611459991356838</v>
+      </c>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
@@ -15443,6 +17944,9 @@
       <c r="D834" t="n">
         <v>5.763639977406958e-07</v>
       </c>
+      <c r="E834" t="n">
+        <v>0.0005195952494665186</v>
+      </c>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
@@ -15461,6 +17965,9 @@
       <c r="D835" t="n">
         <v>4.019621349617309e-06</v>
       </c>
+      <c r="E835" t="n">
+        <v>0.0006885381551480065</v>
+      </c>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
@@ -15479,6 +17986,9 @@
       <c r="D836" t="n">
         <v>5.590465831430692e-07</v>
       </c>
+      <c r="E836" t="n">
+        <v>0.0004705755781355769</v>
+      </c>
     </row>
     <row r="837">
       <c r="A837" t="inlineStr">
@@ -15497,6 +18007,9 @@
       <c r="D837" t="n">
         <v>1.188791862173911e-06</v>
       </c>
+      <c r="E837" t="n">
+        <v>0.0006233216181767857</v>
+      </c>
     </row>
     <row r="838">
       <c r="A838" t="inlineStr">
@@ -15515,6 +18028,9 @@
       <c r="D838" t="n">
         <v>1.880762684357979e-06</v>
       </c>
+      <c r="E838" t="n">
+        <v>0.0007406553324217535</v>
+      </c>
     </row>
     <row r="839">
       <c r="A839" t="inlineStr">
@@ -15533,6 +18049,9 @@
       <c r="D839" t="n">
         <v>8.915102532482795e-07</v>
       </c>
+      <c r="E839" t="n">
+        <v>0.000589647674405818</v>
+      </c>
     </row>
     <row r="840">
       <c r="A840" t="inlineStr">
@@ -15551,6 +18070,9 @@
       <c r="D840" t="n">
         <v>1.653179163828449e-06</v>
       </c>
+      <c r="E840" t="n">
+        <v>0.000724791565253022</v>
+      </c>
     </row>
     <row r="841">
       <c r="A841" t="inlineStr">
@@ -15569,6 +18091,9 @@
       <c r="D841" t="n">
         <v>1.179462942092215e-06</v>
       </c>
+      <c r="E841" t="n">
+        <v>0.0006398715461932805</v>
+      </c>
     </row>
     <row r="842">
       <c r="A842" t="inlineStr">
@@ -15587,6 +18112,9 @@
       <c r="D842" t="n">
         <v>1.850624969362989e-06</v>
       </c>
+      <c r="E842" t="n">
+        <v>0.0007560700882125465</v>
+      </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
@@ -15605,6 +18133,9 @@
       <c r="D843" t="n">
         <v>1.998190688038875e-06</v>
       </c>
+      <c r="E843" t="n">
+        <v>0.0007228223020136429</v>
+      </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
@@ -15623,6 +18154,9 @@
       <c r="D844" t="n">
         <v>6.539193837297932e-07</v>
       </c>
+      <c r="E844" t="n">
+        <v>0.0005725536085874779</v>
+      </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
@@ -15641,6 +18175,9 @@
       <c r="D845" t="n">
         <v>5.603299837344135e-06</v>
       </c>
+      <c r="E845" t="n">
+        <v>0.000756311539319706</v>
+      </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
@@ -15659,6 +18196,9 @@
       <c r="D846" t="n">
         <v>7.8299589444549e-06</v>
       </c>
+      <c r="E846" t="n">
+        <v>0.0008599624653124954</v>
+      </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
@@ -15677,6 +18217,9 @@
       <c r="D847" t="n">
         <v>2.375214090139108e-05</v>
       </c>
+      <c r="E847" t="n">
+        <v>0.0009481472403230375</v>
+      </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
@@ -15695,6 +18238,9 @@
       <c r="D848" t="n">
         <v>6.3579911612896e-07</v>
       </c>
+      <c r="E848" t="n">
+        <v>0.0005520532502510057</v>
+      </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
@@ -15713,6 +18259,9 @@
       <c r="D849" t="n">
         <v>1.35071217439676e-06</v>
       </c>
+      <c r="E849" t="n">
+        <v>0.0006928490484910074</v>
+      </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
@@ -15731,6 +18280,9 @@
       <c r="D850" t="n">
         <v>2.185323485882492e-06</v>
       </c>
+      <c r="E850" t="n">
+        <v>0.0007600047578240485</v>
+      </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
@@ -15749,6 +18301,9 @@
       <c r="D851" t="n">
         <v>1.208932630648317e-06</v>
       </c>
+      <c r="E851" t="n">
+        <v>0.0005488922725561833</v>
+      </c>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
@@ -15767,6 +18322,9 @@
       <c r="D852" t="n">
         <v>2.291986016789884e-06</v>
       </c>
+      <c r="E852" t="n">
+        <v>0.0007629780367274344</v>
+      </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
@@ -15785,6 +18343,9 @@
       <c r="D853" t="n">
         <v>2.461665606219226e-06</v>
       </c>
+      <c r="E853" t="n">
+        <v>0.0007300714667543399</v>
+      </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
@@ -15803,6 +18364,9 @@
       <c r="D854" t="n">
         <v>6.738293412582223e-07</v>
       </c>
+      <c r="E854" t="n">
+        <v>0.0004735147971005171</v>
+      </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
@@ -15821,6 +18385,9 @@
       <c r="D855" t="n">
         <v>3.089490785731697e-07</v>
       </c>
+      <c r="E855" t="n">
+        <v>0.0003872559105319806</v>
+      </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
@@ -15839,6 +18406,9 @@
       <c r="D856" t="n">
         <v>9.946199039024527e-07</v>
       </c>
+      <c r="E856" t="n">
+        <v>0.0006135196327433794</v>
+      </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
@@ -15857,6 +18427,9 @@
       <c r="D857" t="n">
         <v>8.071422715883698e-07</v>
       </c>
+      <c r="E857" t="n">
+        <v>0.000571836354488352</v>
+      </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
@@ -15875,6 +18448,9 @@
       <c r="D858" t="n">
         <v>1.142311615286093e-06</v>
       </c>
+      <c r="E858" t="n">
+        <v>0.0006383804697731057</v>
+      </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
@@ -15893,6 +18469,9 @@
       <c r="D859" t="n">
         <v>9.331781121219798e-07</v>
       </c>
+      <c r="E859" t="n">
+        <v>0.0005125719170343283</v>
+      </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
@@ -15911,6 +18490,9 @@
       <c r="D860" t="n">
         <v>2.244252389671641e-06</v>
       </c>
+      <c r="E860" t="n">
+        <v>0.0007790831705338082</v>
+      </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
@@ -15929,6 +18511,9 @@
       <c r="D861" t="n">
         <v>2.315726970193263e-07</v>
       </c>
+      <c r="E861" t="n">
+        <v>0.0003831143930506225</v>
+      </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
@@ -15947,6 +18532,9 @@
       <c r="D862" t="n">
         <v>9.669139696398929e-07</v>
       </c>
+      <c r="E862" t="n">
+        <v>0.0006629841494592958</v>
+      </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
@@ -15965,6 +18553,9 @@
       <c r="D863" t="n">
         <v>6.127690204896343e-07</v>
       </c>
+      <c r="E863" t="n">
+        <v>0.0004685511976368339</v>
+      </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
@@ -15983,6 +18574,9 @@
       <c r="D864" t="n">
         <v>1.583017969728497e-06</v>
       </c>
+      <c r="E864" t="n">
+        <v>0.0006617185440370362</v>
+      </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
@@ -16001,6 +18595,9 @@
       <c r="D865" t="n">
         <v>1.315987805076607e-06</v>
       </c>
+      <c r="E865" t="n">
+        <v>0.0006394208128811772</v>
+      </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
@@ -16019,6 +18616,9 @@
       <c r="D866" t="n">
         <v>1.987471074599986e-06</v>
       </c>
+      <c r="E866" t="n">
+        <v>0.0006083958902832241</v>
+      </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
@@ -16037,6 +18637,9 @@
       <c r="D867" t="n">
         <v>3.504238579815731e-06</v>
       </c>
+      <c r="E867" t="n">
+        <v>0.0007029527412800083</v>
+      </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
@@ -16055,6 +18658,9 @@
       <c r="D868" t="n">
         <v>1.210254764911279e-06</v>
       </c>
+      <c r="E868" t="n">
+        <v>0.0006727835623763322</v>
+      </c>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
@@ -16073,6 +18679,9 @@
       <c r="D869" t="n">
         <v>1.074577918756205e-06</v>
       </c>
+      <c r="E869" t="n">
+        <v>0.0007025317782937336</v>
+      </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
@@ -16091,6 +18700,9 @@
       <c r="D870" t="n">
         <v>2.253881107141861e-06</v>
       </c>
+      <c r="E870" t="n">
+        <v>0.0007926279167174579</v>
+      </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
@@ -16109,6 +18721,9 @@
       <c r="D871" t="n">
         <v>1.229276656635341e-06</v>
       </c>
+      <c r="E871" t="n">
+        <v>0.0006551160273921209</v>
+      </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
@@ -16127,6 +18742,9 @@
       <c r="D872" t="n">
         <v>2.249959014762361e-06</v>
       </c>
+      <c r="E872" t="n">
+        <v>0.0007258853423868031</v>
+      </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
@@ -16145,6 +18763,9 @@
       <c r="D873" t="n">
         <v>9.042007423175738e-07</v>
       </c>
+      <c r="E873" t="n">
+        <v>0.0005955717118828229</v>
+      </c>
     </row>
     <row r="874">
       <c r="A874" t="inlineStr">
@@ -16163,6 +18784,9 @@
       <c r="D874" t="n">
         <v>1.892636119891509e-07</v>
       </c>
+      <c r="E874" t="n">
+        <v>0.0003388292436834088</v>
+      </c>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
@@ -16181,6 +18805,9 @@
       <c r="D875" t="n">
         <v>1.483941614267802e-06</v>
       </c>
+      <c r="E875" t="n">
+        <v>0.0007043940599989007</v>
+      </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
@@ -16199,6 +18826,9 @@
       <c r="D876" t="n">
         <v>1.087212196186163e-06</v>
       </c>
+      <c r="E876" t="n">
+        <v>0.0006499354167085707</v>
+      </c>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
@@ -16217,6 +18847,9 @@
       <c r="D877" t="n">
         <v>4.725234899619477e-07</v>
       </c>
+      <c r="E877" t="n">
+        <v>0.0004842379722050725</v>
+      </c>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
@@ -16235,6 +18868,9 @@
       <c r="D878" t="n">
         <v>1.656265225531794e-06</v>
       </c>
+      <c r="E878" t="n">
+        <v>0.0006059795338038259</v>
+      </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
@@ -16253,6 +18889,9 @@
       <c r="D879" t="n">
         <v>2.37714627709585e-07</v>
       </c>
+      <c r="E879" t="n">
+        <v>0.0003337090703781608</v>
+      </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
@@ -16271,6 +18910,9 @@
       <c r="D880" t="n">
         <v>1.507795192809635e-05</v>
       </c>
+      <c r="E880" t="n">
+        <v>0.0008368420687619995</v>
+      </c>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
@@ -16289,6 +18931,9 @@
       <c r="D881" t="n">
         <v>1.391250240309525e-05</v>
       </c>
+      <c r="E881" t="n">
+        <v>0.0008044827035645761</v>
+      </c>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
@@ -16307,6 +18952,9 @@
       <c r="D882" t="n">
         <v>7.07980824031835e-07</v>
       </c>
+      <c r="E882" t="n">
+        <v>0.000561395002652774</v>
+      </c>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
@@ -16325,6 +18973,9 @@
       <c r="D883" t="n">
         <v>5.296169567948835e-07</v>
       </c>
+      <c r="E883" t="n">
+        <v>0.0005248777978695485</v>
+      </c>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
@@ -16343,6 +18994,9 @@
       <c r="D884" t="n">
         <v>2.400785269308553e-06</v>
       </c>
+      <c r="E884" t="n">
+        <v>0.0007565948348250201</v>
+      </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
@@ -16361,6 +19015,9 @@
       <c r="D885" t="n">
         <v>1.570967262198239e-06</v>
       </c>
+      <c r="E885" t="n">
+        <v>0.0006397610680081357</v>
+      </c>
     </row>
     <row r="886">
       <c r="A886" t="inlineStr">
@@ -16379,6 +19036,9 @@
       <c r="D886" t="n">
         <v>2.188101356878866e-06</v>
       </c>
+      <c r="E886" t="n">
+        <v>0.0007446927320255481</v>
+      </c>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
@@ -16397,6 +19057,9 @@
       <c r="D887" t="n">
         <v>3.066567783847816e-06</v>
       </c>
+      <c r="E887" t="n">
+        <v>0.0007354514929801154</v>
+      </c>
     </row>
     <row r="888">
       <c r="A888" t="inlineStr">
@@ -16415,6 +19078,9 @@
       <c r="D888" t="n">
         <v>1.006152404659601e-06</v>
       </c>
+      <c r="E888" t="n">
+        <v>0.0006658943853211315</v>
+      </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
@@ -16433,6 +19099,9 @@
       <c r="D889" t="n">
         <v>9.63769547143575e-07</v>
       </c>
+      <c r="E889" t="n">
+        <v>0.0006266331276810957</v>
+      </c>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">
@@ -16451,6 +19120,9 @@
       <c r="D890" t="n">
         <v>1.40829780597074e-06</v>
       </c>
+      <c r="E890" t="n">
+        <v>0.0006767546545964138</v>
+      </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
@@ -16469,6 +19141,9 @@
       <c r="D891" t="n">
         <v>1.710333809375838e-06</v>
       </c>
+      <c r="E891" t="n">
+        <v>0.0007301098762367992</v>
+      </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
@@ -16487,6 +19162,9 @@
       <c r="D892" t="n">
         <v>1.575577130089743e-06</v>
       </c>
+      <c r="E892" t="n">
+        <v>0.0007576479725998941</v>
+      </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
@@ -16505,6 +19183,9 @@
       <c r="D893" t="n">
         <v>1.565118520490086e-06</v>
       </c>
+      <c r="E893" t="n">
+        <v>0.0007122788619504776</v>
+      </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
@@ -16523,6 +19204,9 @@
       <c r="D894" t="n">
         <v>6.967639415200349e-07</v>
       </c>
+      <c r="E894" t="n">
+        <v>0.0005526087104197868</v>
+      </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
@@ -16541,6 +19225,9 @@
       <c r="D895" t="n">
         <v>4.108593432348527e-06</v>
       </c>
+      <c r="E895" t="n">
+        <v>0.0008292570125684532</v>
+      </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
@@ -16559,6 +19246,9 @@
       <c r="D896" t="n">
         <v>1.11360503363838e-06</v>
       </c>
+      <c r="E896" t="n">
+        <v>0.0006709840604975759</v>
+      </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
@@ -16577,6 +19267,9 @@
       <c r="D897" t="n">
         <v>3.570616978700263e-06</v>
       </c>
+      <c r="E897" t="n">
+        <v>0.0006905901280338966</v>
+      </c>
     </row>
     <row r="898">
       <c r="A898" t="inlineStr">
@@ -16595,6 +19288,9 @@
       <c r="D898" t="n">
         <v>1.436003749751545e-06</v>
       </c>
+      <c r="E898" t="n">
+        <v>0.0006974095360552882</v>
+      </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
@@ -16613,6 +19309,9 @@
       <c r="D899" t="n">
         <v>1.52195572064384e-06</v>
       </c>
+      <c r="E899" t="n">
+        <v>0.0006774349435167017</v>
+      </c>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
@@ -16631,6 +19330,9 @@
       <c r="D900" t="n">
         <v>1.163816650627405e-06</v>
       </c>
+      <c r="E900" t="n">
+        <v>0.00057270541204268</v>
+      </c>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
@@ -16649,6 +19351,9 @@
       <c r="D901" t="n">
         <v>2.326740247843867e-06</v>
       </c>
+      <c r="E901" t="n">
+        <v>0.0007500951920174621</v>
+      </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
@@ -16667,6 +19372,9 @@
       <c r="D902" t="n">
         <v>1.008956352207696e-06</v>
       </c>
+      <c r="E902" t="n">
+        <v>0.0006040143706870111</v>
+      </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
@@ -16685,6 +19393,9 @@
       <c r="D903" t="n">
         <v>2.353989046366377e-06</v>
       </c>
+      <c r="E903" t="n">
+        <v>0.0006928052815028378</v>
+      </c>
     </row>
     <row r="904">
       <c r="A904" t="inlineStr">
@@ -16703,6 +19414,9 @@
       <c r="D904" t="n">
         <v>2.540075126537454e-06</v>
       </c>
+      <c r="E904" t="n">
+        <v>0.0007539080456180415</v>
+      </c>
     </row>
     <row r="905">
       <c r="A905" t="inlineStr">
@@ -16721,6 +19435,9 @@
       <c r="D905" t="n">
         <v>1.859191037516042e-06</v>
       </c>
+      <c r="E905" t="n">
+        <v>0.0007173332225480112</v>
+      </c>
     </row>
     <row r="906">
       <c r="A906" t="inlineStr">
@@ -16739,6 +19456,9 @@
       <c r="D906" t="n">
         <v>4.692937520782484e-07</v>
       </c>
+      <c r="E906" t="n">
+        <v>0.0004949061811272196</v>
+      </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
@@ -16757,6 +19477,9 @@
       <c r="D907" t="n">
         <v>2.754483602890154e-06</v>
       </c>
+      <c r="E907" t="n">
+        <v>0.0007484415118489141</v>
+      </c>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
@@ -16775,6 +19498,9 @@
       <c r="D908" t="n">
         <v>6.198863288452749e-07</v>
       </c>
+      <c r="E908" t="n">
+        <v>0.000589584810111781</v>
+      </c>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
@@ -16793,6 +19519,9 @@
       <c r="D909" t="n">
         <v>8.808017056732532e-07</v>
       </c>
+      <c r="E909" t="n">
+        <v>0.0005814896147586685</v>
+      </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
@@ -16811,6 +19540,9 @@
       <c r="D910" t="n">
         <v>5.202720054820407e-07</v>
       </c>
+      <c r="E910" t="n">
+        <v>0.0005081124777081154</v>
+      </c>
     </row>
     <row r="911">
       <c r="A911" t="inlineStr">
@@ -16829,6 +19561,9 @@
       <c r="D911" t="n">
         <v>1.404728726212244e-06</v>
       </c>
+      <c r="E911" t="n">
+        <v>0.0007015785334629498</v>
+      </c>
     </row>
     <row r="912">
       <c r="A912" t="inlineStr">
@@ -16847,6 +19582,9 @@
       <c r="D912" t="n">
         <v>2.298335918822468e-06</v>
       </c>
+      <c r="E912" t="n">
+        <v>0.0007840143296174579</v>
+      </c>
     </row>
     <row r="913">
       <c r="A913" t="inlineStr">
@@ -16865,6 +19603,9 @@
       <c r="D913" t="n">
         <v>1.273984270353937e-06</v>
       </c>
+      <c r="E913" t="n">
+        <v>0.0006609431767215045</v>
+      </c>
     </row>
     <row r="914">
       <c r="A914" t="inlineStr">
@@ -16883,6 +19624,9 @@
       <c r="D914" t="n">
         <v>8.872972772096548e-07</v>
       </c>
+      <c r="E914" t="n">
+        <v>0.0005093874211896716</v>
+      </c>
     </row>
     <row r="915">
       <c r="A915" t="inlineStr">
@@ -16901,6 +19645,9 @@
       <c r="D915" t="n">
         <v>2.908057889299587e-06</v>
       </c>
+      <c r="E915" t="n">
+        <v>0.000807408724582502</v>
+      </c>
     </row>
     <row r="916">
       <c r="A916" t="inlineStr">
@@ -16919,6 +19666,9 @@
       <c r="D916" t="n">
         <v>1.890670358110006e-06</v>
       </c>
+      <c r="E916" t="n">
+        <v>0.0007370404941672805</v>
+      </c>
     </row>
     <row r="917">
       <c r="A917" t="inlineStr">
@@ -16937,6 +19687,9 @@
       <c r="D917" t="n">
         <v>1.307856606584707e-06</v>
       </c>
+      <c r="E917" t="n">
+        <v>0.0006535288678732551</v>
+      </c>
     </row>
     <row r="918">
       <c r="A918" t="inlineStr">
@@ -16955,6 +19708,9 @@
       <c r="D918" t="n">
         <v>1.312808586337734e-06</v>
       </c>
+      <c r="E918" t="n">
+        <v>0.0006772182533667187</v>
+      </c>
     </row>
     <row r="919">
       <c r="A919" t="inlineStr">
@@ -16973,6 +19729,9 @@
       <c r="D919" t="n">
         <v>7.801125625016143e-07</v>
       </c>
+      <c r="E919" t="n">
+        <v>0.0005579343061209517</v>
+      </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
@@ -16991,6 +19750,9 @@
       <c r="D920" t="n">
         <v>1.955628069754493e-06</v>
       </c>
+      <c r="E920" t="n">
+        <v>0.0006196981616118295</v>
+      </c>
     </row>
     <row r="921">
       <c r="A921" t="inlineStr">
@@ -17009,6 +19771,9 @@
       <c r="D921" t="n">
         <v>1.105444345619303e-06</v>
       </c>
+      <c r="E921" t="n">
+        <v>0.0005628554621587415</v>
+      </c>
     </row>
     <row r="922">
       <c r="A922" t="inlineStr">
@@ -17027,6 +19792,9 @@
       <c r="D922" t="n">
         <v>3.377920141980298e-07</v>
       </c>
+      <c r="E922" t="n">
+        <v>0.0004375104058942613</v>
+      </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
@@ -17045,6 +19813,9 @@
       <c r="D923" t="n">
         <v>5.389823672258271e-07</v>
       </c>
+      <c r="E923" t="n">
+        <v>0.00056178590768905</v>
+      </c>
     </row>
     <row r="924">
       <c r="A924" t="inlineStr">
@@ -17063,6 +19834,9 @@
       <c r="D924" t="n">
         <v>2.826027690751407e-07</v>
       </c>
+      <c r="E924" t="n">
+        <v>0.0004017535201636187</v>
+      </c>
     </row>
     <row r="925">
       <c r="A925" t="inlineStr">
@@ -17081,6 +19855,9 @@
       <c r="D925" t="n">
         <v>7.672170328994866e-07</v>
       </c>
+      <c r="E925" t="n">
+        <v>0.000548355184101078</v>
+      </c>
     </row>
     <row r="926">
       <c r="A926" t="inlineStr">
@@ -17099,6 +19876,9 @@
       <c r="D926" t="n">
         <v>4.030861070155659e-07</v>
       </c>
+      <c r="E926" t="n">
+        <v>0.0004376188178734479</v>
+      </c>
     </row>
     <row r="927">
       <c r="A927" t="inlineStr">
@@ -17117,6 +19897,9 @@
       <c r="D927" t="n">
         <v>2.188004521466509e-06</v>
       </c>
+      <c r="E927" t="n">
+        <v>0.0006350457841910696</v>
+      </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
@@ -17135,6 +19918,9 @@
       <c r="D928" t="n">
         <v>4.812565119223078e-07</v>
       </c>
+      <c r="E928" t="n">
+        <v>0.0004996809583881118</v>
+      </c>
     </row>
     <row r="929">
       <c r="A929" t="inlineStr">
@@ -17153,6 +19939,9 @@
       <c r="D929" t="n">
         <v>3.137805868383239e-07</v>
       </c>
+      <c r="E929" t="n">
+        <v>0.0004308611371378359</v>
+      </c>
     </row>
     <row r="930">
       <c r="A930" t="inlineStr">
@@ -17171,6 +19960,9 @@
       <c r="D930" t="n">
         <v>3.803860896689597e-06</v>
       </c>
+      <c r="E930" t="n">
+        <v>0.0007553266009765102</v>
+      </c>
     </row>
     <row r="931">
       <c r="A931" t="inlineStr">
@@ -17189,6 +19981,9 @@
       <c r="D931" t="n">
         <v>2.273362337478032e-06</v>
       </c>
+      <c r="E931" t="n">
+        <v>0.0006598840263751525</v>
+      </c>
     </row>
     <row r="932">
       <c r="A932" t="inlineStr">
@@ -17207,6 +20002,9 @@
       <c r="D932" t="n">
         <v>6.553851577410443e-07</v>
       </c>
+      <c r="E932" t="n">
+        <v>0.0005064768688307604</v>
+      </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
@@ -17225,6 +20023,9 @@
       <c r="D933" t="n">
         <v>1.878744950515438e-06</v>
       </c>
+      <c r="E933" t="n">
+        <v>0.0007916869215158431</v>
+      </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
@@ -17243,6 +20044,9 @@
       <c r="D934" t="n">
         <v>6.645692904111762e-06</v>
       </c>
+      <c r="E934" t="n">
+        <v>0.0008220295765476323</v>
+      </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
@@ -17261,6 +20065,9 @@
       <c r="D935" t="n">
         <v>2.143678289375e-06</v>
       </c>
+      <c r="E935" t="n">
+        <v>0.0006048691978808771</v>
+      </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
@@ -17279,6 +20086,9 @@
       <c r="D936" t="n">
         <v>2.861338971446663e-06</v>
       </c>
+      <c r="E936" t="n">
+        <v>0.0007593332216453771</v>
+      </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
@@ -17297,6 +20107,9 @@
       <c r="D937" t="n">
         <v>8.132224446907103e-07</v>
       </c>
+      <c r="E937" t="n">
+        <v>0.0005281096227027394</v>
+      </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
@@ -17315,6 +20128,9 @@
       <c r="D938" t="n">
         <v>8.967693553638808e-07</v>
       </c>
+      <c r="E938" t="n">
+        <v>0.0005824943449030156</v>
+      </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
@@ -17333,6 +20149,9 @@
       <c r="D939" t="n">
         <v>3.818126636279919e-06</v>
       </c>
+      <c r="E939" t="n">
+        <v>0.00081414518288039</v>
+      </c>
     </row>
     <row r="940">
       <c r="A940" t="inlineStr">
@@ -17351,6 +20170,9 @@
       <c r="D940" t="n">
         <v>1.948349344400019e-06</v>
       </c>
+      <c r="E940" t="n">
+        <v>0.0005739457761600064</v>
+      </c>
     </row>
     <row r="941">
       <c r="A941" t="inlineStr">
@@ -17369,6 +20191,9 @@
       <c r="D941" t="n">
         <v>1.902395292406173e-06</v>
       </c>
+      <c r="E941" t="n">
+        <v>0.0006368099755116064</v>
+      </c>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
@@ -17387,6 +20212,9 @@
       <c r="D942" t="n">
         <v>1.260643926870744e-06</v>
       </c>
+      <c r="E942" t="n">
+        <v>0.0006161829731447806</v>
+      </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
@@ -17405,6 +20233,9 @@
       <c r="D943" t="n">
         <v>5.516982534650623e-07</v>
       </c>
+      <c r="E943" t="n">
+        <v>0.0005371025151495088</v>
+      </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
@@ -17423,6 +20254,9 @@
       <c r="D944" t="n">
         <v>1.771207103852324e-06</v>
       </c>
+      <c r="E944" t="n">
+        <v>0.0005888250527821174</v>
+      </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
@@ -17441,6 +20275,9 @@
       <c r="D945" t="n">
         <v>2.588443659938185e-06</v>
       </c>
+      <c r="E945" t="n">
+        <v>0.0007331405849531179</v>
+      </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
@@ -17459,6 +20296,9 @@
       <c r="D946" t="n">
         <v>2.288435086579581e-05</v>
       </c>
+      <c r="E946" t="n">
+        <v>0.0009233688014344511</v>
+      </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
@@ -17477,6 +20317,9 @@
       <c r="D947" t="n">
         <v>1.050301100728406e-06</v>
       </c>
+      <c r="E947" t="n">
+        <v>0.000663123932524511</v>
+      </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
@@ -17495,6 +20338,9 @@
       <c r="D948" t="n">
         <v>1.862275821144876e-07</v>
       </c>
+      <c r="E948" t="n">
+        <v>0.0003376443949980676</v>
+      </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
@@ -17513,6 +20359,9 @@
       <c r="D949" t="n">
         <v>1.205556984961124e-06</v>
       </c>
+      <c r="E949" t="n">
+        <v>0.0004293444251796716</v>
+      </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
@@ -17531,6 +20380,9 @@
       <c r="D950" t="n">
         <v>1.354915398342536e-06</v>
       </c>
+      <c r="E950" t="n">
+        <v>0.0004621497361519272</v>
+      </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
@@ -17549,6 +20401,9 @@
       <c r="D951" t="n">
         <v>2.945435945159601e-06</v>
       </c>
+      <c r="E951" t="n">
+        <v>0.0006523674202420336</v>
+      </c>
     </row>
     <row r="952">
       <c r="A952" t="inlineStr">
@@ -17567,6 +20422,9 @@
       <c r="D952" t="n">
         <v>6.942498070529659e-07</v>
       </c>
+      <c r="E952" t="n">
+        <v>0.0005496552343320174</v>
+      </c>
     </row>
     <row r="953">
       <c r="A953" t="inlineStr">
@@ -17585,6 +20443,9 @@
       <c r="D953" t="n">
         <v>1.852796921945922e-07</v>
       </c>
+      <c r="E953" t="n">
+        <v>0.0003488267065551396</v>
+      </c>
     </row>
     <row r="954">
       <c r="A954" t="inlineStr">
@@ -17603,6 +20464,9 @@
       <c r="D954" t="n">
         <v>3.21760484380123e-06</v>
       </c>
+      <c r="E954" t="n">
+        <v>0.0007578142778610649</v>
+      </c>
     </row>
     <row r="955">
       <c r="A955" t="inlineStr">
@@ -17621,6 +20485,9 @@
       <c r="D955" t="n">
         <v>2.876191188228818e-06</v>
       </c>
+      <c r="E955" t="n">
+        <v>0.0007003935387270852</v>
+      </c>
     </row>
     <row r="956">
       <c r="A956" t="inlineStr">
@@ -17639,6 +20506,9 @@
       <c r="D956" t="n">
         <v>6.911928475224922e-07</v>
       </c>
+      <c r="E956" t="n">
+        <v>0.0005606213013966998</v>
+      </c>
     </row>
     <row r="957">
       <c r="A957" t="inlineStr">
@@ -17657,6 +20527,9 @@
       <c r="D957" t="n">
         <v>2.653804656639548e-06</v>
       </c>
+      <c r="E957" t="n">
+        <v>0.0007248610948021098</v>
+      </c>
     </row>
     <row r="958">
       <c r="A958" t="inlineStr">
@@ -17675,6 +20548,9 @@
       <c r="D958" t="n">
         <v>3.632860263552716e-06</v>
       </c>
+      <c r="E958" t="n">
+        <v>0.0007285955969453632</v>
+      </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">
@@ -17693,6 +20569,9 @@
       <c r="D959" t="n">
         <v>6.911627540771218e-07</v>
       </c>
+      <c r="E959" t="n">
+        <v>0.000570290162566931</v>
+      </c>
     </row>
     <row r="960">
       <c r="A960" t="inlineStr">
@@ -17711,6 +20590,9 @@
       <c r="D960" t="n">
         <v>2.009148974803301e-06</v>
       </c>
+      <c r="E960" t="n">
+        <v>0.0007485259733624155</v>
+      </c>
     </row>
     <row r="961">
       <c r="A961" t="inlineStr">
@@ -17729,6 +20611,9 @@
       <c r="D961" t="n">
         <v>6.45544303559848e-07</v>
       </c>
+      <c r="E961" t="n">
+        <v>0.0005765737054563156</v>
+      </c>
     </row>
     <row r="962">
       <c r="A962" t="inlineStr">
@@ -17747,6 +20632,9 @@
       <c r="D962" t="n">
         <v>1.223255781642546e-06</v>
       </c>
+      <c r="E962" t="n">
+        <v>0.0006500838057294357</v>
+      </c>
     </row>
     <row r="963">
       <c r="A963" t="inlineStr">
@@ -17765,6 +20653,9 @@
       <c r="D963" t="n">
         <v>8.944050941851631e-07</v>
       </c>
+      <c r="E963" t="n">
+        <v>0.0006305721868098135</v>
+      </c>
     </row>
     <row r="964">
       <c r="A964" t="inlineStr">
@@ -17783,6 +20674,9 @@
       <c r="D964" t="n">
         <v>7.728745092635677e-07</v>
       </c>
+      <c r="E964" t="n">
+        <v>0.0004698115922097085</v>
+      </c>
     </row>
     <row r="965">
       <c r="A965" t="inlineStr">
@@ -17801,6 +20695,9 @@
       <c r="D965" t="n">
         <v>1.768500572098785e-06</v>
       </c>
+      <c r="E965" t="n">
+        <v>0.0007193425903066387</v>
+      </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
@@ -17819,6 +20716,9 @@
       <c r="D966" t="n">
         <v>1.176900398043775e-06</v>
       </c>
+      <c r="E966" t="n">
+        <v>0.0005353850033797261</v>
+      </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
@@ -17837,6 +20737,9 @@
       <c r="D967" t="n">
         <v>6.022868969042842e-07</v>
       </c>
+      <c r="E967" t="n">
+        <v>0.0005079424898638342</v>
+      </c>
     </row>
     <row r="968">
       <c r="A968" t="inlineStr">
@@ -17855,6 +20758,9 @@
       <c r="D968" t="n">
         <v>4.137221845507163e-07</v>
       </c>
+      <c r="E968" t="n">
+        <v>0.0004819687867235662</v>
+      </c>
     </row>
     <row r="969">
       <c r="A969" t="inlineStr">
@@ -17873,6 +20779,9 @@
       <c r="D969" t="n">
         <v>1.428054744510293e-06</v>
       </c>
+      <c r="E969" t="n">
+        <v>0.0006296809412171558</v>
+      </c>
     </row>
     <row r="970">
       <c r="A970" t="inlineStr">
@@ -17891,6 +20800,9 @@
       <c r="D970" t="n">
         <v>1.984986363239772e-06</v>
       </c>
+      <c r="E970" t="n">
+        <v>0.0007446706907714207</v>
+      </c>
     </row>
     <row r="971">
       <c r="A971" t="inlineStr">
@@ -17909,6 +20821,9 @@
       <c r="D971" t="n">
         <v>1.417576760348491e-06</v>
       </c>
+      <c r="E971" t="n">
+        <v>0.0007011472715707178</v>
+      </c>
     </row>
     <row r="972">
       <c r="A972" t="inlineStr">
@@ -17927,6 +20842,9 @@
       <c r="D972" t="n">
         <v>7.99936655996293e-07</v>
       </c>
+      <c r="E972" t="n">
+        <v>0.0005787745655044473</v>
+      </c>
     </row>
     <row r="973">
       <c r="A973" t="inlineStr">
@@ -17945,6 +20863,9 @@
       <c r="D973" t="n">
         <v>3.387621204515187e-06</v>
       </c>
+      <c r="E973" t="n">
+        <v>0.0008361758478881846</v>
+      </c>
     </row>
     <row r="974">
       <c r="A974" t="inlineStr">
@@ -17963,6 +20884,9 @@
       <c r="D974" t="n">
         <v>6.722522947201166e-07</v>
       </c>
+      <c r="E974" t="n">
+        <v>0.0005706550586431003</v>
+      </c>
     </row>
     <row r="975">
       <c r="A975" t="inlineStr">
@@ -17981,6 +20905,9 @@
       <c r="D975" t="n">
         <v>1.162319458160703e-06</v>
       </c>
+      <c r="E975" t="n">
+        <v>0.0006755908267342933</v>
+      </c>
     </row>
     <row r="976">
       <c r="A976" t="inlineStr">
@@ -17999,6 +20926,9 @@
       <c r="D976" t="n">
         <v>3.760773650125133e-07</v>
       </c>
+      <c r="E976" t="n">
+        <v>0.0004449414030108473</v>
+      </c>
     </row>
     <row r="977">
       <c r="A977" t="inlineStr">
@@ -18017,6 +20947,9 @@
       <c r="D977" t="n">
         <v>5.151877163677765e-06</v>
       </c>
+      <c r="E977" t="n">
+        <v>0.000855880176571061</v>
+      </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
@@ -18035,6 +20968,9 @@
       <c r="D978" t="n">
         <v>5.402421483526213e-06</v>
       </c>
+      <c r="E978" t="n">
+        <v>0.0008698962276750435</v>
+      </c>
     </row>
     <row r="979">
       <c r="A979" t="inlineStr">
@@ -18053,6 +20989,9 @@
       <c r="D979" t="n">
         <v>3.944799286674537e-06</v>
       </c>
+      <c r="E979" t="n">
+        <v>0.0008448918865734653</v>
+      </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
@@ -18071,6 +21010,9 @@
       <c r="D980" t="n">
         <v>7.081374183180103e-07</v>
       </c>
+      <c r="E980" t="n">
+        <v>0.0004721180158131294</v>
+      </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
@@ -18089,6 +21031,9 @@
       <c r="D981" t="n">
         <v>3.04293232565623e-06</v>
       </c>
+      <c r="E981" t="n">
+        <v>0.0006982928988839113</v>
+      </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
@@ -18107,6 +21052,9 @@
       <c r="D982" t="n">
         <v>2.317906259813463e-06</v>
       </c>
+      <c r="E982" t="n">
+        <v>0.0006381708192772947</v>
+      </c>
     </row>
     <row r="983">
       <c r="A983" t="inlineStr">
@@ -18125,6 +21073,9 @@
       <c r="D983" t="n">
         <v>2.50546266366155e-06</v>
       </c>
+      <c r="E983" t="n">
+        <v>0.000686404067972515</v>
+      </c>
     </row>
     <row r="984">
       <c r="A984" t="inlineStr">
@@ -18143,6 +21094,9 @@
       <c r="D984" t="n">
         <v>3.498682015142068e-07</v>
       </c>
+      <c r="E984" t="n">
+        <v>0.0003754950193389667</v>
+      </c>
     </row>
     <row r="985">
       <c r="A985" t="inlineStr">
@@ -18161,6 +21115,9 @@
       <c r="D985" t="n">
         <v>3.784925258840226e-05</v>
       </c>
+      <c r="E985" t="n">
+        <v>0.0009560284552254149</v>
+      </c>
     </row>
     <row r="986">
       <c r="A986" t="inlineStr">
@@ -18179,6 +21136,9 @@
       <c r="D986" t="n">
         <v>3.488557048887162e-06</v>
       </c>
+      <c r="E986" t="n">
+        <v>0.0007466448411265236</v>
+      </c>
     </row>
     <row r="987">
       <c r="A987" t="inlineStr">
@@ -18197,6 +21157,9 @@
       <c r="D987" t="n">
         <v>1.126336735019913e-06</v>
       </c>
+      <c r="E987" t="n">
+        <v>0.0005939735318448053</v>
+      </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
@@ -18215,6 +21178,9 @@
       <c r="D988" t="n">
         <v>1.790582565673099e-06</v>
       </c>
+      <c r="E988" t="n">
+        <v>0.0006652087509081861</v>
+      </c>
     </row>
     <row r="989">
       <c r="A989" t="inlineStr">
@@ -18232,6 +21198,9 @@
       </c>
       <c r="D989" t="n">
         <v>1.950021369337891e-06</v>
+      </c>
+      <c r="E989" t="n">
+        <v>0.0006827894208929838</v>
       </c>
     </row>
   </sheetData>
